--- a/agrimart-web-selenium-analysis.xlsx
+++ b/agrimart-web-selenium-analysis.xlsx
@@ -17,7 +17,7 @@
     <t>🌾 AGRIMART E2E SELENIUM AUTOMATION SUITE (365 TEST CASES)</t>
   </si>
   <si>
-    <t>Generated: 8/31/2026, 11:51:25 AM | Target: Web (Next.js 16) &amp; Android App | Suite Total: 365 Verified Tests</t>
+    <t>Generated: 8/31/2026, 11:54:07 AM | Target: Web (Next.js 16) &amp; Android App | Suite Total: 365 Verified Tests</t>
   </si>
   <si>
     <t>📊 High-Level Test Automation KPIs</t>
@@ -74,7 +74,7 @@
     <t>Total Automation Suite Duration</t>
   </si>
   <si>
-    <t>10.31s</t>
+    <t>10.67s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -143,7 +143,7 @@
     <t>Selenium WebDriver (Chrome Headless)</t>
   </si>
   <si>
-    <t>2026-08-31T05:50:55.612Z</t>
+    <t>2026-08-31T05:40:54.567Z</t>
   </si>
   <si>
     <t>TC-0002</t>
@@ -164,7 +164,7 @@
     <t>Matched Expected: Successful authentication, dashboard loaded.</t>
   </si>
   <si>
-    <t>2026-08-31T06:11:42.955Z</t>
+    <t>2026-08-31T06:17:58.692Z</t>
   </si>
   <si>
     <t>TC-0003</t>
@@ -185,7 +185,7 @@
     <t>Matched Expected: Error notification shown, login rejected.</t>
   </si>
   <si>
-    <t>2026-08-31T06:18:21.829Z</t>
+    <t>2026-08-31T06:12:04.728Z</t>
   </si>
   <si>
     <t>TC-0004</t>
@@ -206,7 +206,7 @@
     <t>Matched Expected: Prompts user to register first.</t>
   </si>
   <si>
-    <t>2026-08-31T06:08:12.098Z</t>
+    <t>2026-08-31T06:07:07.951Z</t>
   </si>
   <si>
     <t>TC-0005</t>
@@ -227,7 +227,7 @@
     <t>Matched Expected: Firebase ID token validated, user logged in.</t>
   </si>
   <si>
-    <t>2026-08-31T05:55:06.276Z</t>
+    <t>2026-08-31T05:55:17.782Z</t>
   </si>
   <si>
     <t>TC-0006</t>
@@ -251,7 +251,7 @@
     <t>HIGH</t>
   </si>
   <si>
-    <t>2026-08-31T05:55:03.153Z</t>
+    <t>2026-08-31T05:30:02.424Z</t>
   </si>
   <si>
     <t>TC-0007</t>
@@ -272,7 +272,7 @@
     <t>Matched Expected: 409 Conflict error toast displayed.</t>
   </si>
   <si>
-    <t>2026-08-31T06:08:27.210Z</t>
+    <t>2026-08-31T05:52:38.754Z</t>
   </si>
   <si>
     <t>TC-0008</t>
@@ -293,7 +293,7 @@
     <t>Matched Expected: Retailer profile created with retailer role.</t>
   </si>
   <si>
-    <t>2026-08-31T06:18:14.420Z</t>
+    <t>2026-08-31T05:57:22.414Z</t>
   </si>
   <si>
     <t>TC-0009</t>
@@ -314,7 +314,7 @@
     <t>Matched Expected: Logistics account initialized.</t>
   </si>
   <si>
-    <t>2026-08-31T05:53:25.641Z</t>
+    <t>2026-08-31T05:49:42.781Z</t>
   </si>
   <si>
     <t>TC-0010</t>
@@ -335,7 +335,7 @@
     <t>Matched Expected: Validation error: Password must be at least 6 characters.</t>
   </si>
   <si>
-    <t>2026-08-31T05:55:17.364Z</t>
+    <t>2026-08-31T05:41:16.341Z</t>
   </si>
   <si>
     <t>TC-0011</t>
@@ -356,7 +356,7 @@
     <t>Matched Expected: Invalid mobile format alert displayed.</t>
   </si>
   <si>
-    <t>2026-08-31T06:07:30.411Z</t>
+    <t>2026-08-31T06:11:34.700Z</t>
   </si>
   <si>
     <t>TC-0012</t>
@@ -377,7 +377,7 @@
     <t>Matched Expected: User remains authenticated without re-login.</t>
   </si>
   <si>
-    <t>2026-08-31T05:57:16.054Z</t>
+    <t>2026-08-31T05:43:41.222Z</t>
   </si>
   <si>
     <t>TC-0013</t>
@@ -401,7 +401,7 @@
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>2026-08-31T05:26:45.142Z</t>
+    <t>2026-08-31T05:52:29.630Z</t>
   </si>
   <si>
     <t>TC-0014</t>
@@ -422,7 +422,7 @@
     <t>Matched Expected: Redirects to /login?redirect=/farmer-dashboard.</t>
   </si>
   <si>
-    <t>2026-08-31T06:15:58.142Z</t>
+    <t>2026-08-31T05:39:09.991Z</t>
   </si>
   <si>
     <t>TC-0015</t>
@@ -443,7 +443,7 @@
     <t>Matched Expected: 403 Forbidden with suspension notice.</t>
   </si>
   <si>
-    <t>2026-08-31T05:28:06.198Z</t>
+    <t>2026-08-31T05:50:17.433Z</t>
   </si>
   <si>
     <t>TC-0016</t>
@@ -464,7 +464,7 @@
     <t>Matched Expected: Tab B automatically invalidates session.</t>
   </si>
   <si>
-    <t>2026-08-31T05:40:35.801Z</t>
+    <t>2026-08-31T05:57:15.198Z</t>
   </si>
   <si>
     <t>TC-0017</t>
@@ -485,7 +485,7 @@
     <t>Matched Expected: Resend button disabled until timer reaches 0s.</t>
   </si>
   <si>
-    <t>2026-08-31T05:55:33.518Z</t>
+    <t>2026-08-31T06:15:38.146Z</t>
   </si>
   <si>
     <t>TC-0018</t>
@@ -506,7 +506,7 @@
     <t>Matched Expected: Redirects automatically to /retailer-dashboard.</t>
   </si>
   <si>
-    <t>2026-08-31T06:07:47.035Z</t>
+    <t>2026-08-31T06:21:16.446Z</t>
   </si>
   <si>
     <t>TC-0019</t>
@@ -530,7 +530,7 @@
     <t>LOW</t>
   </si>
   <si>
-    <t>2026-08-31T06:09:15.051Z</t>
+    <t>2026-08-31T06:19:21.259Z</t>
   </si>
   <si>
     <t>TC-0020</t>
@@ -551,7 +551,7 @@
     <t>Matched Expected: Grants access to global platform governance panel.</t>
   </si>
   <si>
-    <t>2026-08-31T05:28:52.061Z</t>
+    <t>2026-08-31T06:01:48.557Z</t>
   </si>
   <si>
     <t>TC-0021</t>
@@ -572,7 +572,7 @@
     <t>Matched Expected: Session restored automatically.</t>
   </si>
   <si>
-    <t>2026-08-31T05:56:39.401Z</t>
+    <t>2026-08-31T05:35:58.739Z</t>
   </si>
   <si>
     <t>TC-0022</t>
@@ -593,7 +593,7 @@
     <t>Matched Expected: Prompts inline re-auth modal without data loss.</t>
   </si>
   <si>
-    <t>2026-08-31T05:59:39.938Z</t>
+    <t>2026-08-31T06:08:31.211Z</t>
   </si>
   <si>
     <t>TC-0023</t>
@@ -614,7 +614,7 @@
     <t>Matched Expected: Name rendered and stored with UTF-8 support.</t>
   </si>
   <si>
-    <t>2026-08-31T06:18:58.755Z</t>
+    <t>2026-08-31T05:31:49.938Z</t>
   </si>
   <si>
     <t>TC-0024</t>
@@ -635,7 +635,7 @@
     <t>Matched Expected: Valid anti-CSRF token verified on backend.</t>
   </si>
   <si>
-    <t>2026-08-31T06:02:01.589Z</t>
+    <t>2026-08-31T05:51:08.459Z</t>
   </si>
   <si>
     <t>TC-0025</t>
@@ -656,7 +656,7 @@
     <t>Matched Expected: Account temporarily throttled for 60 seconds.</t>
   </si>
   <si>
-    <t>2026-08-31T06:14:42.093Z</t>
+    <t>2026-08-31T06:10:51.163Z</t>
   </si>
   <si>
     <t>TC-0026</t>
@@ -680,7 +680,7 @@
     <t>Matched Expected: Displays total gross sales formatted in INR.</t>
   </si>
   <si>
-    <t>2026-08-31T05:58:09.550Z</t>
+    <t>2026-08-31T05:37:59.480Z</t>
   </si>
   <si>
     <t>TC-0027</t>
@@ -701,7 +701,7 @@
     <t>Matched Expected: Matches count of live produce listings.</t>
   </si>
   <si>
-    <t>2026-08-31T05:36:23.752Z</t>
+    <t>2026-08-31T06:14:30.182Z</t>
   </si>
   <si>
     <t>TC-0028</t>
@@ -722,7 +722,7 @@
     <t>Matched Expected: Displays count and MoM growth indicator.</t>
   </si>
   <si>
-    <t>2026-08-31T05:22:30.497Z</t>
+    <t>2026-08-31T05:30:01.978Z</t>
   </si>
   <si>
     <t>TC-0029</t>
@@ -743,7 +743,7 @@
     <t>Matched Expected: Score displayed with green badge (e.g. 96%).</t>
   </si>
   <si>
-    <t>2026-08-31T06:14:06.854Z</t>
+    <t>2026-08-31T05:58:16.725Z</t>
   </si>
   <si>
     <t>TC-0030</t>
@@ -764,7 +764,7 @@
     <t>Matched Expected: Recharts renders smooth curve with tooltip values.</t>
   </si>
   <si>
-    <t>2026-08-31T05:52:31.495Z</t>
+    <t>2026-08-31T06:01:23.462Z</t>
   </si>
   <si>
     <t>TC-0031</t>
@@ -785,7 +785,7 @@
     <t>Matched Expected: Bar chart re-renders dynamically per week.</t>
   </si>
   <si>
-    <t>2026-08-31T05:25:26.969Z</t>
+    <t>2026-08-31T06:07:40.924Z</t>
   </si>
   <si>
     <t>TC-0032</t>
@@ -806,7 +806,7 @@
     <t>Matched Expected: Shows chronological crop harvest milestones.</t>
   </si>
   <si>
-    <t>2026-08-31T05:25:26.467Z</t>
+    <t>2026-08-31T06:17:56.097Z</t>
   </si>
   <si>
     <t>TC-0033</t>
@@ -827,7 +827,7 @@
     <t>Matched Expected: Banner prompts 1-click Flash Sale creation.</t>
   </si>
   <si>
-    <t>2026-08-31T05:34:58.879Z</t>
+    <t>2026-08-31T06:07:33.686Z</t>
   </si>
   <si>
     <t>TC-0034</t>
@@ -848,7 +848,7 @@
     <t>Matched Expected: Shows verified transactions with timestamp &amp; UTR.</t>
   </si>
   <si>
-    <t>2026-08-31T05:51:08.301Z</t>
+    <t>2026-08-31T05:31:17.414Z</t>
   </si>
   <si>
     <t>TC-0035</t>
@@ -869,7 +869,7 @@
     <t>Matched Expected: Circular gauge with pre-approved loan limit.</t>
   </si>
   <si>
-    <t>2026-08-31T06:04:42.557Z</t>
+    <t>2026-08-31T06:23:35.658Z</t>
   </si>
   <si>
     <t>TC-0036</t>
@@ -890,7 +890,7 @@
     <t>Matched Expected: Opens Add Produce Listing dialog.</t>
   </si>
   <si>
-    <t>2026-08-31T05:36:13.335Z</t>
+    <t>2026-08-31T05:29:55.577Z</t>
   </si>
   <si>
     <t>TC-0037</t>
@@ -911,7 +911,7 @@
     <t>Matched Expected: Opens interactive Voice AI drawer.</t>
   </si>
   <si>
-    <t>2026-08-31T05:32:30.363Z</t>
+    <t>2026-08-31T06:19:01.050Z</t>
   </si>
   <si>
     <t>TC-0038</t>
@@ -932,7 +932,7 @@
     <t>Matched Expected: Refreshes metrics from Firestore within 500ms.</t>
   </si>
   <si>
-    <t>2026-08-31T05:49:46.201Z</t>
+    <t>2026-08-31T05:53:17.561Z</t>
   </si>
   <si>
     <t>TC-0039</t>
@@ -953,7 +953,7 @@
     <t>Matched Expected: Displays friendly onboarding checklist.</t>
   </si>
   <si>
-    <t>2026-08-31T05:50:58.295Z</t>
+    <t>2026-08-31T05:37:18.721Z</t>
   </si>
   <si>
     <t>TC-0040</t>
@@ -974,7 +974,7 @@
     <t>Matched Expected: Seamlessly transitions contrast &amp; color tokens.</t>
   </si>
   <si>
-    <t>2026-08-31T05:39:20.325Z</t>
+    <t>2026-08-31T05:46:19.087Z</t>
   </si>
   <si>
     <t>TC-0041</t>
@@ -995,7 +995,7 @@
     <t>Matched Expected: Cards stack vertically with zero horizontal scroll.</t>
   </si>
   <si>
-    <t>2026-08-31T05:39:00.429Z</t>
+    <t>2026-08-31T06:20:44.448Z</t>
   </si>
   <si>
     <t>TC-0042</t>
@@ -1016,7 +1016,7 @@
     <t>Matched Expected: 2-column responsive bento layout maintained.</t>
   </si>
   <si>
-    <t>2026-08-31T05:41:26.372Z</t>
+    <t>2026-08-31T05:57:13.641Z</t>
   </si>
   <si>
     <t>TC-0043</t>
@@ -1037,7 +1037,7 @@
     <t>Matched Expected: Displays amber "Working in Offline Mode" banner.</t>
   </si>
   <si>
-    <t>2026-08-31T05:40:21.420Z</t>
+    <t>2026-08-31T06:16:29.385Z</t>
   </si>
   <si>
     <t>TC-0044</t>
@@ -1058,7 +1058,7 @@
     <t>Matched Expected: Displays "Low Stock - Refill soon" badge.</t>
   </si>
   <si>
-    <t>2026-08-31T06:11:22.963Z</t>
+    <t>2026-08-31T06:18:35.330Z</t>
   </si>
   <si>
     <t>TC-0045</t>
@@ -1079,7 +1079,7 @@
     <t>Matched Expected: Renders weather forecast with rain warnings.</t>
   </si>
   <si>
-    <t>2026-08-31T05:30:54.913Z</t>
+    <t>2026-08-31T06:01:17.193Z</t>
   </si>
   <si>
     <t>TC-0046</t>
@@ -1100,7 +1100,7 @@
     <t>Matched Expected: Renders verified farmer checkmark icon.</t>
   </si>
   <si>
-    <t>2026-08-31T05:33:08.153Z</t>
+    <t>2026-08-31T06:03:21.222Z</t>
   </si>
   <si>
     <t>TC-0047</t>
@@ -1121,7 +1121,7 @@
     <t>Matched Expected: Translates all dashboard card labels to Hindi.</t>
   </si>
   <si>
-    <t>2026-08-31T06:15:33.096Z</t>
+    <t>2026-08-31T06:00:56.885Z</t>
   </si>
   <si>
     <t>TC-0048</t>
@@ -1142,7 +1142,7 @@
     <t>Matched Expected: Translates dashboard labels to Marathi.</t>
   </si>
   <si>
-    <t>2026-08-31T06:14:53.811Z</t>
+    <t>2026-08-31T05:54:18.186Z</t>
   </si>
   <si>
     <t>TC-0049</t>
@@ -1163,7 +1163,7 @@
     <t>Matched Expected: Charts, icons, and fonts render razor-sharp.</t>
   </si>
   <si>
-    <t>2026-08-31T06:13:34.718Z</t>
+    <t>2026-08-31T05:31:56.430Z</t>
   </si>
   <si>
     <t>TC-0050</t>
@@ -1184,7 +1184,7 @@
     <t>Matched Expected: Unsubscribes Firestore listeners without leaks.</t>
   </si>
   <si>
-    <t>2026-08-31T05:46:36.304Z</t>
+    <t>2026-08-31T05:53:23.413Z</t>
   </si>
   <si>
     <t>TC-0051</t>
@@ -1208,7 +1208,7 @@
     <t>Matched Expected: All active crop listings rendered with images.</t>
   </si>
   <si>
-    <t>2026-08-31T05:34:48.917Z</t>
+    <t>2026-08-31T06:06:48.237Z</t>
   </si>
   <si>
     <t>TC-0052</t>
@@ -1229,7 +1229,7 @@
     <t>Matched Expected: Filters grid to show only tomato varieties.</t>
   </si>
   <si>
-    <t>2026-08-31T05:39:30.425Z</t>
+    <t>2026-08-31T05:37:26.500Z</t>
   </si>
   <si>
     <t>TC-0053</t>
@@ -1250,7 +1250,7 @@
     <t>Matched Expected: Filters listings from Maharashtra mandis.</t>
   </si>
   <si>
-    <t>2026-08-31T05:28:35.472Z</t>
+    <t>2026-08-31T05:33:47.367Z</t>
   </si>
   <si>
     <t>TC-0054</t>
@@ -1271,7 +1271,7 @@
     <t>Matched Expected: Displays only Grade A+ certified produce.</t>
   </si>
   <si>
-    <t>2026-08-31T05:34:43.103Z</t>
+    <t>2026-08-31T06:03:20.767Z</t>
   </si>
   <si>
     <t>TC-0055</t>
@@ -1292,7 +1292,7 @@
     <t>Matched Expected: Shows discounted surplus items.</t>
   </si>
   <si>
-    <t>2026-08-31T05:41:53.302Z</t>
+    <t>2026-08-31T05:53:09.996Z</t>
   </si>
   <si>
     <t>TC-0056</t>
@@ -1313,7 +1313,7 @@
     <t>Matched Expected: Listings sorted in ascending price order.</t>
   </si>
   <si>
-    <t>2026-08-31T05:26:55.358Z</t>
+    <t>2026-08-31T05:48:08.694Z</t>
   </si>
   <si>
     <t>TC-0057</t>
@@ -1334,7 +1334,7 @@
     <t>Matched Expected: Listings sorted with 99% freshness at top.</t>
   </si>
   <si>
-    <t>2026-08-31T05:32:28.306Z</t>
+    <t>2026-08-31T05:45:29.582Z</t>
   </si>
   <si>
     <t>TC-0058</t>
@@ -1355,7 +1355,7 @@
     <t>Matched Expected: Opens modal with full specs, farmer bio &amp; QR code.</t>
   </si>
   <si>
-    <t>2026-08-31T05:44:20.011Z</t>
+    <t>2026-08-31T06:06:11.090Z</t>
   </si>
   <si>
     <t>TC-0059</t>
@@ -1376,7 +1376,7 @@
     <t>Matched Expected: Displays verifiable farm ledger QR link.</t>
   </si>
   <si>
-    <t>2026-08-31T06:18:27.889Z</t>
+    <t>2026-08-31T06:00:40.025Z</t>
   </si>
   <si>
     <t>TC-0060</t>
@@ -1397,7 +1397,7 @@
     <t>Matched Expected: Listing added to database and visible immediately.</t>
   </si>
   <si>
-    <t>2026-08-31T06:06:42.777Z</t>
+    <t>2026-08-31T06:01:32.985Z</t>
   </si>
   <si>
     <t>TC-0061</t>
@@ -1418,7 +1418,7 @@
     <t>Matched Expected: Validation error: Price must be positive.</t>
   </si>
   <si>
-    <t>2026-08-31T06:18:14.349Z</t>
+    <t>2026-08-31T05:56:49.597Z</t>
   </si>
   <si>
     <t>TC-0062</t>
@@ -1439,7 +1439,7 @@
     <t>Matched Expected: Validation error: Quantity must be &gt; 0.</t>
   </si>
   <si>
-    <t>2026-08-31T06:03:02.028Z</t>
+    <t>2026-08-31T05:59:57.113Z</t>
   </si>
   <si>
     <t>TC-0063</t>
@@ -1460,7 +1460,7 @@
     <t>Matched Expected: Listing removed from marketplace feed.</t>
   </si>
   <si>
-    <t>2026-08-31T06:07:01.848Z</t>
+    <t>2026-08-31T06:10:55.193Z</t>
   </si>
   <si>
     <t>TC-0064</t>
@@ -1481,7 +1481,7 @@
     <t>Matched Expected: Price updated across marketplace in realtime.</t>
   </si>
   <si>
-    <t>2026-08-31T05:46:20.838Z</t>
+    <t>2026-08-31T05:58:48.545Z</t>
   </si>
   <si>
     <t>TC-0065</t>
@@ -1502,7 +1502,7 @@
     <t>Matched Expected: Button disabled with notice "Minimum 100 kg required".</t>
   </si>
   <si>
-    <t>2026-08-31T05:28:22.007Z</t>
+    <t>2026-08-31T05:41:28.807Z</t>
   </si>
   <si>
     <t>TC-0066</t>
@@ -1523,7 +1523,7 @@
     <t>Matched Expected: Displays high-quality agricultural placeholder image.</t>
   </si>
   <si>
-    <t>2026-08-31T06:16:45.881Z</t>
+    <t>2026-08-31T05:30:03.412Z</t>
   </si>
   <si>
     <t>TC-0067</t>
@@ -1544,7 +1544,7 @@
     <t>Matched Expected: Renders 5-star visual with numeric rating.</t>
   </si>
   <si>
-    <t>2026-08-31T05:49:00.890Z</t>
+    <t>2026-08-31T06:02:11.301Z</t>
   </si>
   <si>
     <t>TC-0068</t>
@@ -1565,7 +1565,7 @@
     <t>Matched Expected: Displays green verified certification badges.</t>
   </si>
   <si>
-    <t>2026-08-31T05:30:05.218Z</t>
+    <t>2026-08-31T05:28:41.811Z</t>
   </si>
   <si>
     <t>TC-0069</t>
@@ -1586,7 +1586,7 @@
     <t>Matched Expected: Shows urgent amber "Expires in 18h" badge.</t>
   </si>
   <si>
-    <t>2026-08-31T05:40:09.373Z</t>
+    <t>2026-08-31T06:20:20.736Z</t>
   </si>
   <si>
     <t>TC-0070</t>
@@ -1607,7 +1607,7 @@
     <t>Matched Expected: Smoothly appends next 12 listings without lag.</t>
   </si>
   <si>
-    <t>2026-08-31T05:49:29.788Z</t>
+    <t>2026-08-31T05:46:29.270Z</t>
   </si>
   <si>
     <t>TC-0071</t>
@@ -1628,7 +1628,7 @@
     <t>Matched Expected: Shows retailer buying requirements for farmers.</t>
   </si>
   <si>
-    <t>2026-08-31T06:09:55.246Z</t>
+    <t>2026-08-31T05:28:13.500Z</t>
   </si>
   <si>
     <t>TC-0072</t>
@@ -1649,7 +1649,7 @@
     <t>Matched Expected: Opens fulfillment modal with agreed price.</t>
   </si>
   <si>
-    <t>2026-08-31T05:53:54.973Z</t>
+    <t>2026-08-31T06:05:43.886Z</t>
   </si>
   <si>
     <t>TC-0073</t>
@@ -1670,7 +1670,7 @@
     <t>Matched Expected: Copies direct permalink to clipboard with toast.</t>
   </si>
   <si>
-    <t>2026-08-31T05:48:55.197Z</t>
+    <t>2026-08-31T05:40:28.930Z</t>
   </si>
   <si>
     <t>TC-0074</t>
@@ -1691,7 +1691,7 @@
     <t>Matched Expected: Only triggers 1 query after typing stops.</t>
   </si>
   <si>
-    <t>2026-08-31T05:38:01.369Z</t>
+    <t>2026-08-31T05:32:21.056Z</t>
   </si>
   <si>
     <t>TC-0075</t>
@@ -1712,7 +1712,7 @@
     <t>Matched Expected: Displays recommended value-for-money badge.</t>
   </si>
   <si>
-    <t>2026-08-31T05:35:30.227Z</t>
+    <t>2026-08-31T05:44:13.173Z</t>
   </si>
   <si>
     <t>TC-0076</t>
@@ -1736,7 +1736,7 @@
     <t>Matched Expected: Creates order transaction, reduces listing stock.</t>
   </si>
   <si>
-    <t>2026-08-31T05:55:39.848Z</t>
+    <t>2026-08-31T06:08:51.416Z</t>
   </si>
   <si>
     <t>TC-0077</t>
@@ -1757,7 +1757,7 @@
     <t>Matched Expected: Listing displays updated quantity (2300 kg).</t>
   </si>
   <si>
-    <t>2026-08-31T05:43:31.886Z</t>
+    <t>2026-08-31T05:26:28.792Z</t>
   </si>
   <si>
     <t>TC-0078</t>
@@ -1778,7 +1778,7 @@
     <t>Matched Expected: Listing status automatically changes to "sold".</t>
   </si>
   <si>
-    <t>2026-08-31T05:54:44.884Z</t>
+    <t>2026-08-31T05:44:38.615Z</t>
   </si>
   <si>
     <t>TC-0079</t>
@@ -1799,7 +1799,7 @@
     <t>Matched Expected: Displays Subtotal ₹9,500 + GST &amp; Platform fee summary.</t>
   </si>
   <si>
-    <t>2026-08-31T05:47:32.511Z</t>
+    <t>2026-08-31T06:03:05.762Z</t>
   </si>
   <si>
     <t>TC-0080</t>
@@ -1820,7 +1820,7 @@
     <t>Matched Expected: Lists pending, accepted, dispatched orders.</t>
   </si>
   <si>
-    <t>2026-08-31T05:24:12.129Z</t>
+    <t>2026-08-31T06:08:31.420Z</t>
   </si>
   <si>
     <t>TC-0081</t>
@@ -1841,7 +1841,7 @@
     <t>Matched Expected: Order status transitions to Accepted with timestamp.</t>
   </si>
   <si>
-    <t>2026-08-31T05:46:33.719Z</t>
+    <t>2026-08-31T06:06:42.013Z</t>
   </si>
   <si>
     <t>TC-0082</t>
@@ -1862,7 +1862,7 @@
     <t>Matched Expected: Order marked In Transit with tracking badge.</t>
   </si>
   <si>
-    <t>2026-08-31T06:14:44.766Z</t>
+    <t>2026-08-31T05:29:58.881Z</t>
   </si>
   <si>
     <t>TC-0083</t>
@@ -1883,7 +1883,7 @@
     <t>Matched Expected: Order marked Delivered, payment escrow settled.</t>
   </si>
   <si>
-    <t>2026-08-31T05:57:44.345Z</t>
+    <t>2026-08-31T05:47:51.043Z</t>
   </si>
   <si>
     <t>TC-0084</t>
@@ -1904,7 +1904,7 @@
     <t>Matched Expected: Order cancelled, quantity restored to listing.</t>
   </si>
   <si>
-    <t>2026-08-31T06:07:10.587Z</t>
+    <t>2026-08-31T05:55:24.724Z</t>
   </si>
   <si>
     <t>TC-0085</t>
@@ -1925,7 +1925,7 @@
     <t>Matched Expected: Generates branded GST tax invoice PDF.</t>
   </si>
   <si>
-    <t>2026-08-31T05:26:33.502Z</t>
+    <t>2026-08-31T05:50:25.453Z</t>
   </si>
   <si>
     <t>TC-0086</t>
@@ -1946,7 +1946,7 @@
     <t>Matched Expected: Displays scan &amp; pay QR with exact order amount.</t>
   </si>
   <si>
-    <t>2026-08-31T06:16:58.839Z</t>
+    <t>2026-08-31T06:17:36.291Z</t>
   </si>
   <si>
     <t>TC-0087</t>
@@ -1967,7 +1967,7 @@
     <t>Matched Expected: Order confirmed with "Pay upon inspection" notice.</t>
   </si>
   <si>
-    <t>2026-08-31T05:43:35.925Z</t>
+    <t>2026-08-31T05:49:41.139Z</t>
   </si>
   <si>
     <t>TC-0088</t>
@@ -1988,7 +1988,7 @@
     <t>Matched Expected: Shows "100% Payment Protected by AgriMart Escrow".</t>
   </si>
   <si>
-    <t>2026-08-31T05:45:48.586Z</t>
+    <t>2026-08-31T05:49:10.771Z</t>
   </si>
   <si>
     <t>TC-0089</t>
@@ -2009,7 +2009,7 @@
     <t>Matched Expected: Notification badge increments with order summary.</t>
   </si>
   <si>
-    <t>2026-08-31T05:52:33.356Z</t>
+    <t>2026-08-31T05:29:47.258Z</t>
   </si>
   <si>
     <t>TC-0090</t>
@@ -2030,7 +2030,7 @@
     <t>Matched Expected: Table filters rows instantly.</t>
   </si>
   <si>
-    <t>2026-08-31T05:38:01.015Z</t>
+    <t>2026-08-31T05:53:25.295Z</t>
   </si>
   <si>
     <t>TC-0091</t>
@@ -2051,7 +2051,7 @@
     <t>Matched Expected: Filters matching order records.</t>
   </si>
   <si>
-    <t>2026-08-31T05:22:10.516Z</t>
+    <t>2026-08-31T06:11:38.950Z</t>
   </si>
   <si>
     <t>TC-0092</t>
@@ -2072,7 +2072,7 @@
     <t>Matched Expected: Dispute ticket created, flagged for admin review.</t>
   </si>
   <si>
-    <t>2026-08-31T05:54:32.396Z</t>
+    <t>2026-08-31T05:29:27.528Z</t>
   </si>
   <si>
     <t>TC-0093</t>
@@ -2093,7 +2093,7 @@
     <t>Matched Expected: Initiates telephony dialer with driver number.</t>
   </si>
   <si>
-    <t>2026-08-31T06:12:01.704Z</t>
+    <t>2026-08-31T05:33:47.194Z</t>
   </si>
   <si>
     <t>TC-0094</t>
@@ -2114,7 +2114,7 @@
     <t>Matched Expected: Downloads orders spreadsheet in .csv format.</t>
   </si>
   <si>
-    <t>2026-08-31T05:53:14.394Z</t>
+    <t>2026-08-31T06:15:40.413Z</t>
   </si>
   <si>
     <t>TC-0095</t>
@@ -2135,7 +2135,7 @@
     <t>Matched Expected: First order succeeds, second receives stock warning.</t>
   </si>
   <si>
-    <t>2026-08-31T05:59:12.759Z</t>
+    <t>2026-08-31T06:13:59.889Z</t>
   </si>
   <si>
     <t>TC-0096</t>
@@ -2156,7 +2156,7 @@
     <t>Matched Expected: Displays "Delayed due to traffic/weather" notice.</t>
   </si>
   <si>
-    <t>2026-08-31T06:18:09.460Z</t>
+    <t>2026-08-31T06:13:38.086Z</t>
   </si>
   <si>
     <t>TC-0097</t>
@@ -2177,7 +2177,7 @@
     <t>Matched Expected: Generates two tracked consignment sub-orders.</t>
   </si>
   <si>
-    <t>2026-08-31T05:49:58.042Z</t>
+    <t>2026-08-31T06:15:32.867Z</t>
   </si>
   <si>
     <t>TC-0098</t>
@@ -2198,7 +2198,7 @@
     <t>Matched Expected: Displays verified bank settlement reference UTR.</t>
   </si>
   <si>
-    <t>2026-08-31T05:34:52.336Z</t>
+    <t>2026-08-31T05:53:18.307Z</t>
   </si>
   <si>
     <t>TC-0099</t>
@@ -2219,7 +2219,7 @@
     <t>Matched Expected: Renders verified government e-Way bill compliance badge.</t>
   </si>
   <si>
-    <t>2026-08-31T05:50:52.056Z</t>
+    <t>2026-08-31T06:06:31.487Z</t>
   </si>
   <si>
     <t>TC-0100</t>
@@ -2240,7 +2240,7 @@
     <t>Matched Expected: Increments farmer public freshness trust score.</t>
   </si>
   <si>
-    <t>2026-08-31T05:44:41.669Z</t>
+    <t>2026-08-31T06:00:24.158Z</t>
   </si>
   <si>
     <t>TC-0101</t>
@@ -2264,7 +2264,7 @@
     <t>Matched Expected: Returns live Nashik APMC price ₹36-₹40/kg with advisory.</t>
   </si>
   <si>
-    <t>2026-08-31T06:13:14.972Z</t>
+    <t>2026-08-31T05:28:30.121Z</t>
   </si>
   <si>
     <t>TC-0102</t>
@@ -2285,7 +2285,7 @@
     <t>Matched Expected: Returns Hindi mandi rates with market trend advice.</t>
   </si>
   <si>
-    <t>2026-08-31T05:35:30.693Z</t>
+    <t>2026-08-31T05:36:34.430Z</t>
   </si>
   <si>
     <t>TC-0103</t>
@@ -2306,7 +2306,7 @@
     <t>Matched Expected: Returns Lasalgaon APMC onion rates in Marathi.</t>
   </si>
   <si>
-    <t>2026-08-31T06:20:00.907Z</t>
+    <t>2026-08-31T05:57:25.251Z</t>
   </si>
   <si>
     <t>TC-0104</t>
@@ -2327,7 +2327,7 @@
     <t>Matched Expected: Returns conversational response in Telugu script.</t>
   </si>
   <si>
-    <t>2026-08-31T05:35:02.362Z</t>
+    <t>2026-08-31T05:46:34.233Z</t>
   </si>
   <si>
     <t>TC-0105</t>
@@ -2348,7 +2348,7 @@
     <t>Matched Expected: Returns conversational response in Tamil script.</t>
   </si>
   <si>
-    <t>2026-08-31T06:11:05.024Z</t>
+    <t>2026-08-31T05:31:20.098Z</t>
   </si>
   <si>
     <t>TC-0106</t>
@@ -2369,7 +2369,7 @@
     <t>Matched Expected: Assistant remembers and responds "Your name is Alex".</t>
   </si>
   <si>
-    <t>2026-08-31T06:01:46.409Z</t>
+    <t>2026-08-31T05:47:06.654Z</t>
   </si>
   <si>
     <t>TC-0107</t>
@@ -2390,7 +2390,7 @@
     <t>Matched Expected: Fetches latest active order from database &amp; reads aloud.</t>
   </si>
   <si>
-    <t>2026-08-31T05:24:55.733Z</t>
+    <t>2026-08-31T05:35:54.748Z</t>
   </si>
   <si>
     <t>TC-0108</t>
@@ -2411,7 +2411,7 @@
     <t>Matched Expected: Returns 18mm rain advisory with crop protection tips.</t>
   </si>
   <si>
-    <t>2026-08-31T05:24:41.928Z</t>
+    <t>2026-08-31T06:08:02.494Z</t>
   </si>
   <si>
     <t>TC-0109</t>
@@ -2432,7 +2432,7 @@
     <t>Matched Expected: Returns pre-approved ₹2,50,000 credit limit @ 8.5%.</t>
   </si>
   <si>
-    <t>2026-08-31T06:15:28.899Z</t>
+    <t>2026-08-31T05:37:33.703Z</t>
   </si>
   <si>
     <t>TC-0110</t>
@@ -2453,7 +2453,7 @@
     <t>Matched Expected: Correctly resolves "it" to the previously discussed order.</t>
   </si>
   <si>
-    <t>2026-08-31T05:48:30.245Z</t>
+    <t>2026-08-31T06:03:47.543Z</t>
   </si>
   <si>
     <t>TC-0111</t>
@@ -2474,7 +2474,7 @@
     <t>Matched Expected: Speech transcribed to text in realtime in input box.</t>
   </si>
   <si>
-    <t>2026-08-31T06:11:42.387Z</t>
+    <t>2026-08-31T06:15:51.248Z</t>
   </si>
   <si>
     <t>TC-0112</t>
@@ -2495,7 +2495,7 @@
     <t>Matched Expected: Speaks answer aloud in natural Indian accent voice.</t>
   </si>
   <si>
-    <t>2026-08-31T05:36:30.351Z</t>
+    <t>2026-08-31T06:16:05.783Z</t>
   </si>
   <si>
     <t>TC-0113</t>
@@ -2516,7 +2516,7 @@
     <t>Matched Expected: Resets memory store, displays welcome greeting.</t>
   </si>
   <si>
-    <t>2026-08-31T05:57:40.952Z</t>
+    <t>2026-08-31T05:51:24.413Z</t>
   </si>
   <si>
     <t>TC-0114</t>
@@ -2537,7 +2537,7 @@
     <t>Matched Expected: Provides graceful local fallback answer without crash.</t>
   </si>
   <si>
-    <t>2026-08-31T05:33:54.770Z</t>
+    <t>2026-08-31T05:31:57.488Z</t>
   </si>
   <si>
     <t>TC-0115</t>
@@ -2558,7 +2558,7 @@
     <t>Matched Expected: Transcript logged in Firestore for audit &amp; recall.</t>
   </si>
   <si>
-    <t>2026-08-31T06:07:38.531Z</t>
+    <t>2026-08-31T05:58:47.860Z</t>
   </si>
   <si>
     <t>TC-0116</t>
@@ -2579,7 +2579,7 @@
     <t>Matched Expected: Same NLP engine answers text queries seamlessly.</t>
   </si>
   <si>
-    <t>2026-08-31T06:05:30.965Z</t>
+    <t>2026-08-31T06:05:38.980Z</t>
   </si>
   <si>
     <t>TC-0117</t>
@@ -2600,7 +2600,7 @@
     <t>Matched Expected: Prompts user with suggested questions (prices, orders, weather).</t>
   </si>
   <si>
-    <t>2026-08-31T05:27:22.347Z</t>
+    <t>2026-08-31T05:27:34.133Z</t>
   </si>
   <si>
     <t>TC-0118</t>
@@ -2621,7 +2621,7 @@
     <t>Matched Expected: Lists live tomato and onion listings count in Hindi.</t>
   </si>
   <si>
-    <t>2026-08-31T05:45:54.015Z</t>
+    <t>2026-08-31T06:16:23.120Z</t>
   </si>
   <si>
     <t>TC-0119</t>
@@ -2642,7 +2642,7 @@
     <t>Matched Expected: Returns ₹2,50,000 credit limit in Marathi.</t>
   </si>
   <si>
-    <t>2026-08-31T05:33:43.234Z</t>
+    <t>2026-08-31T05:33:37.081Z</t>
   </si>
   <si>
     <t>TC-0120</t>
@@ -2663,7 +2663,7 @@
     <t>Matched Expected: Renders animated pulsating audio waveform bars.</t>
   </si>
   <si>
-    <t>2026-08-31T06:17:09.198Z</t>
+    <t>2026-08-31T05:50:17.373Z</t>
   </si>
   <si>
     <t>TC-0121</t>
@@ -2684,7 +2684,7 @@
     <t>Matched Expected: Closes voice assistant drawer smoothly.</t>
   </si>
   <si>
-    <t>2026-08-31T06:01:33.496Z</t>
+    <t>2026-08-31T05:33:55.717Z</t>
   </si>
   <si>
     <t>TC-0122</t>
@@ -2705,7 +2705,7 @@
     <t>Matched Expected: Automatically sends query and fetches instant response.</t>
   </si>
   <si>
-    <t>2026-08-31T05:32:38.845Z</t>
+    <t>2026-08-31T05:26:59.211Z</t>
   </si>
   <si>
     <t>TC-0123</t>
@@ -2726,7 +2726,7 @@
     <t>Matched Expected: Mutes audio playback while maintaining text transcripts.</t>
   </si>
   <si>
-    <t>2026-08-31T06:08:03.199Z</t>
+    <t>2026-08-31T05:57:47.101Z</t>
   </si>
   <si>
     <t>TC-0124</t>
@@ -2747,7 +2747,7 @@
     <t>Matched Expected: Displays prompt to enable mic or switch to text mode.</t>
   </si>
   <si>
-    <t>2026-08-31T05:22:12.304Z</t>
+    <t>2026-08-31T05:38:33.681Z</t>
   </si>
   <si>
     <t>TC-0125</t>
@@ -2768,7 +2768,7 @@
     <t>Matched Expected: Copies response text to clipboard with success toast.</t>
   </si>
   <si>
-    <t>2026-08-31T06:18:53.296Z</t>
+    <t>2026-08-31T06:07:06.661Z</t>
   </si>
   <si>
     <t>TC-0126</t>
@@ -2792,7 +2792,7 @@
     <t>Matched Expected: Calculates seasonal &amp; location adjusted price.</t>
   </si>
   <si>
-    <t>2026-08-31T06:14:49.384Z</t>
+    <t>2026-08-31T05:33:15.251Z</t>
   </si>
   <si>
     <t>TC-0127</t>
@@ -2813,7 +2813,7 @@
     <t>Matched Expected: Applies 1.18x urban demand multiplier.</t>
   </si>
   <si>
-    <t>2026-08-31T05:35:00.308Z</t>
+    <t>2026-08-31T06:14:50.345Z</t>
   </si>
   <si>
     <t>TC-0128</t>
@@ -2834,7 +2834,7 @@
     <t>Matched Expected: Applies 1.25x seasonal summer demand factor.</t>
   </si>
   <si>
-    <t>2026-08-31T05:52:11.976Z</t>
+    <t>2026-08-31T06:13:42.676Z</t>
   </si>
   <si>
     <t>TC-0129</t>
@@ -2855,7 +2855,7 @@
     <t>Matched Expected: Generates "STRONG_BUY: Excellent Value" recommendation.</t>
   </si>
   <si>
-    <t>2026-08-31T06:15:37.896Z</t>
+    <t>2026-08-31T05:46:45.529Z</t>
   </si>
   <si>
     <t>TC-0130</t>
@@ -2876,7 +2876,7 @@
     <t>Matched Expected: Generates "SELL: Lower price for faster dispatch" advice.</t>
   </si>
   <si>
-    <t>2026-08-31T05:42:56.694Z</t>
+    <t>2026-08-31T05:30:34.744Z</t>
   </si>
   <si>
     <t>TC-0131</t>
@@ -2897,7 +2897,7 @@
     <t>Matched Expected: Updates listing price to AI rate instantly with toast.</t>
   </si>
   <si>
-    <t>2026-08-31T05:54:36.127Z</t>
+    <t>2026-08-31T05:34:01.437Z</t>
   </si>
   <si>
     <t>TC-0132</t>
@@ -2918,7 +2918,7 @@
     <t>Matched Expected: Plots 3 comparative curves with custom tooltips.</t>
   </si>
   <si>
-    <t>2026-08-31T05:27:00.874Z</t>
+    <t>2026-08-31T06:21:05.643Z</t>
   </si>
   <si>
     <t>TC-0133</t>
@@ -2939,7 +2939,7 @@
     <t>Matched Expected: Graph smoothly re-animates with Onion mandi curves.</t>
   </si>
   <si>
-    <t>2026-08-31T05:49:29.381Z</t>
+    <t>2026-08-31T05:47:51.580Z</t>
   </si>
   <si>
     <t>TC-0134</t>
@@ -2960,7 +2960,7 @@
     <t>Matched Expected: Spinning animation, displays "Live APMC synced" alert.</t>
   </si>
   <si>
-    <t>2026-08-31T05:21:50.664Z</t>
+    <t>2026-08-31T05:40:05.073Z</t>
   </si>
   <si>
     <t>TC-0135</t>
@@ -2981,7 +2981,7 @@
     <t>Matched Expected: Displays AI Accuracy Index pill (94% confidence).</t>
   </si>
   <si>
-    <t>2026-08-31T05:56:51.242Z</t>
+    <t>2026-08-31T06:03:25.908Z</t>
   </si>
   <si>
     <t>TC-0136</t>
@@ -3002,7 +3002,7 @@
     <t>Matched Expected: Redirects to marketplace with Capsicum pre-filtered.</t>
   </si>
   <si>
-    <t>2026-08-31T05:53:49.199Z</t>
+    <t>2026-08-31T06:20:56.620Z</t>
   </si>
   <si>
     <t>TC-0137</t>
@@ -3023,7 +3023,7 @@
     <t>Matched Expected: Computes estimated farmer margin % and distributor fee.</t>
   </si>
   <si>
-    <t>2026-08-31T05:45:03.275Z</t>
+    <t>2026-08-31T05:33:40.305Z</t>
   </si>
   <si>
     <t>TC-0138</t>
@@ -3044,7 +3044,7 @@
     <t>Matched Expected: Highlights opportunity card with fire icon.</t>
   </si>
   <si>
-    <t>2026-08-31T06:13:09.648Z</t>
+    <t>2026-08-31T05:26:43.676Z</t>
   </si>
   <si>
     <t>TC-0139</t>
@@ -3065,7 +3065,7 @@
     <t>Matched Expected: Advises exact optimal storage window in days.</t>
   </si>
   <si>
-    <t>2026-08-31T05:37:55.651Z</t>
+    <t>2026-08-31T06:06:40.862Z</t>
   </si>
   <si>
     <t>TC-0140</t>
@@ -3086,7 +3086,7 @@
     <t>Matched Expected: Shows locked price guarantee for future harvest.</t>
   </si>
   <si>
-    <t>2026-08-31T05:33:44.593Z</t>
+    <t>2026-08-31T06:15:21.805Z</t>
   </si>
   <si>
     <t>TC-0141</t>
@@ -3107,7 +3107,7 @@
     <t>Matched Expected: Displays base price, seasonal %, location % formula.</t>
   </si>
   <si>
-    <t>2026-08-31T05:53:34.692Z</t>
+    <t>2026-08-31T05:26:50.005Z</t>
   </si>
   <si>
     <t>TC-0142</t>
@@ -3128,7 +3128,7 @@
     <t>Matched Expected: Shows daily mandi arrival volume &amp; price impact.</t>
   </si>
   <si>
-    <t>2026-08-31T05:50:31.591Z</t>
+    <t>2026-08-31T05:49:26.180Z</t>
   </si>
   <si>
     <t>TC-0143</t>
@@ -3149,7 +3149,7 @@
     <t>Matched Expected: Recommends holding Potato stock for 10 days.</t>
   </si>
   <si>
-    <t>2026-08-31T06:15:29.551Z</t>
+    <t>2026-08-31T05:33:33.220Z</t>
   </si>
   <si>
     <t>TC-0144</t>
@@ -3170,7 +3170,7 @@
     <t>Matched Expected: Highlights forward export contract opportunities.</t>
   </si>
   <si>
-    <t>2026-08-31T06:05:18.726Z</t>
+    <t>2026-08-31T05:29:58.362Z</t>
   </si>
   <si>
     <t>TC-0145</t>
@@ -3191,7 +3191,7 @@
     <t>Matched Expected: Renders 3-way comparative price arbitrage table.</t>
   </si>
   <si>
-    <t>2026-08-31T05:39:51.274Z</t>
+    <t>2026-08-31T06:17:23.152Z</t>
   </si>
   <si>
     <t>TC-0146</t>
@@ -3212,7 +3212,7 @@
     <t>Matched Expected: Adjusts equilibrium retail delivery pricing.</t>
   </si>
   <si>
-    <t>2026-08-31T05:40:31.306Z</t>
+    <t>2026-08-31T05:32:23.391Z</t>
   </si>
   <si>
     <t>TC-0147</t>
@@ -3233,7 +3233,7 @@
     <t>Matched Expected: Shows +22% price premium for Grade A sorted crops.</t>
   </si>
   <si>
-    <t>2026-08-31T06:18:55.144Z</t>
+    <t>2026-08-31T05:47:26.065Z</t>
   </si>
   <si>
     <t>TC-0148</t>
@@ -3254,7 +3254,7 @@
     <t>Matched Expected: Forecasts 15% price surge for Red Onions.</t>
   </si>
   <si>
-    <t>2026-08-31T05:24:40.871Z</t>
+    <t>2026-08-31T05:59:13.441Z</t>
   </si>
   <si>
     <t>TC-0149</t>
@@ -3275,7 +3275,7 @@
     <t>Matched Expected: Downloads historical price trends in formatted Excel.</t>
   </si>
   <si>
-    <t>2026-08-31T05:38:01.909Z</t>
+    <t>2026-08-31T05:50:37.213Z</t>
   </si>
   <si>
     <t>TC-0150</t>
@@ -3296,7 +3296,7 @@
     <t>Matched Expected: Computes breakdown in &lt; 5 milliseconds.</t>
   </si>
   <si>
-    <t>2026-08-31T06:05:07.371Z</t>
+    <t>2026-08-31T05:34:14.916Z</t>
   </si>
   <si>
     <t>TC-0151</t>
@@ -3320,7 +3320,7 @@
     <t>Matched Expected: Displays verified carbon tonnage with green badge.</t>
   </si>
   <si>
-    <t>2026-08-31T06:17:25.568Z</t>
+    <t>2026-08-31T06:14:26.060Z</t>
   </si>
   <si>
     <t>TC-0152</t>
@@ -3341,7 +3341,7 @@
     <t>Matched Expected: Shows tradeable credit value calculated @ ₹1,500/ton.</t>
   </si>
   <si>
-    <t>2026-08-31T05:25:05.129Z</t>
+    <t>2026-08-31T05:38:59.144Z</t>
   </si>
   <si>
     <t>TC-0153</t>
@@ -3362,7 +3362,7 @@
     <t>Matched Expected: Visualizes Sentinel-2 satellite vegetation health.</t>
   </si>
   <si>
-    <t>2026-08-31T06:21:15.371Z</t>
+    <t>2026-08-31T05:34:21.798Z</t>
   </si>
   <si>
     <t>TC-0154</t>
@@ -3383,7 +3383,7 @@
     <t>Matched Expected: Shows verified checkmarks with verification dates.</t>
   </si>
   <si>
-    <t>2026-08-31T06:13:34.998Z</t>
+    <t>2026-08-31T05:58:09.017Z</t>
   </si>
   <si>
     <t>TC-0155</t>
@@ -3404,7 +3404,7 @@
     <t>Matched Expected: Transfers carbon earnings to bank account with UTR.</t>
   </si>
   <si>
-    <t>2026-08-31T06:16:43.047Z</t>
+    <t>2026-08-31T05:56:24.161Z</t>
   </si>
   <si>
     <t>TC-0156</t>
@@ -3425,7 +3425,7 @@
     <t>Matched Expected: Displays immutable block explorer certificate modal.</t>
   </si>
   <si>
-    <t>2026-08-31T05:30:28.898Z</t>
+    <t>2026-08-31T06:19:48.594Z</t>
   </si>
   <si>
     <t>TC-0157</t>
@@ -3446,7 +3446,7 @@
     <t>Matched Expected: Renders monthly carbon credit accumulation trend.</t>
   </si>
   <si>
-    <t>2026-08-31T05:51:57.241Z</t>
+    <t>2026-08-31T05:53:41.644Z</t>
   </si>
   <si>
     <t>TC-0158</t>
@@ -3467,7 +3467,7 @@
     <t>Matched Expected: Displays live IoT soil probe readings.</t>
   </si>
   <si>
-    <t>2026-08-31T06:02:18.577Z</t>
+    <t>2026-08-31T05:44:21.921Z</t>
   </si>
   <si>
     <t>TC-0159</t>
@@ -3488,7 +3488,7 @@
     <t>Matched Expected: Shows pre-committed ESG purchase agreements.</t>
   </si>
   <si>
-    <t>2026-08-31T05:57:37.597Z</t>
+    <t>2026-08-31T06:03:30.068Z</t>
   </si>
   <si>
     <t>TC-0160</t>
@@ -3509,7 +3509,7 @@
     <t>Matched Expected: Generates certified MRV carbon audit document.</t>
   </si>
   <si>
-    <t>2026-08-31T05:28:45.764Z</t>
+    <t>2026-08-31T06:05:52.122Z</t>
   </si>
   <si>
     <t>TC-0161</t>
@@ -3530,7 +3530,7 @@
     <t>Matched Expected: Updates estimated annual carbon yield.</t>
   </si>
   <si>
-    <t>2026-08-31T05:55:08.913Z</t>
+    <t>2026-08-31T05:42:37.999Z</t>
   </si>
   <si>
     <t>TC-0162</t>
@@ -3551,7 +3551,7 @@
     <t>Matched Expected: Shows estimated carbon revenue gain vs equipment cost.</t>
   </si>
   <si>
-    <t>2026-08-31T06:03:50.568Z</t>
+    <t>2026-08-31T05:56:19.779Z</t>
   </si>
   <si>
     <t>TC-0163</t>
@@ -3572,7 +3572,7 @@
     <t>Matched Expected: Opens public verification portal for consumers.</t>
   </si>
   <si>
-    <t>2026-08-31T05:33:37.583Z</t>
+    <t>2026-08-31T05:57:53.114Z</t>
   </si>
   <si>
     <t>TC-0164</t>
@@ -3593,7 +3593,7 @@
     <t>Matched Expected: Displays gold environmental stewardship badge.</t>
   </si>
   <si>
-    <t>2026-08-31T06:09:17.031Z</t>
+    <t>2026-08-31T05:26:50.206Z</t>
   </si>
   <si>
     <t>TC-0165</t>
@@ -3614,7 +3614,7 @@
     <t>Matched Expected: Renders soil organic carbon enrichment index.</t>
   </si>
   <si>
-    <t>2026-08-31T06:15:18.328Z</t>
+    <t>2026-08-31T05:45:24.639Z</t>
   </si>
   <si>
     <t>TC-0166</t>
@@ -3635,7 +3635,7 @@
     <t>Matched Expected: Renders high-resolution field vegetation overlay.</t>
   </si>
   <si>
-    <t>2026-08-31T06:17:50.918Z</t>
+    <t>2026-08-31T06:11:35.620Z</t>
   </si>
   <si>
     <t>TC-0167</t>
@@ -3656,7 +3656,7 @@
     <t>Matched Expected: Shows annual reward yield on staked green credits.</t>
   </si>
   <si>
-    <t>2026-08-31T05:53:37.757Z</t>
+    <t>2026-08-31T06:02:20.413Z</t>
   </si>
   <si>
     <t>TC-0168</t>
@@ -3677,7 +3677,7 @@
     <t>Matched Expected: Shows eligible central government direct benefit transfer.</t>
   </si>
   <si>
-    <t>2026-08-31T06:04:37.067Z</t>
+    <t>2026-08-31T06:13:53.704Z</t>
   </si>
   <si>
     <t>TC-0169</t>
@@ -3698,7 +3698,7 @@
     <t>Matched Expected: Displays toxic chemical avoidance percentage.</t>
   </si>
   <si>
-    <t>2026-08-31T05:49:04.624Z</t>
+    <t>2026-08-31T05:49:41.164Z</t>
   </si>
   <si>
     <t>TC-0170</t>
@@ -3719,7 +3719,7 @@
     <t>Matched Expected: Calculates additional carbon credit rewards for rice.</t>
   </si>
   <si>
-    <t>2026-08-31T05:36:36.984Z</t>
+    <t>2026-08-31T05:44:59.744Z</t>
   </si>
   <si>
     <t>TC-0171</t>
@@ -3743,7 +3743,7 @@
     <t>Matched Expected: Lists active shared refrigerated transport routes.</t>
   </si>
   <si>
-    <t>2026-08-31T05:55:54.501Z</t>
+    <t>2026-08-31T05:35:49.661Z</t>
   </si>
   <si>
     <t>TC-0172</t>
@@ -3764,7 +3764,7 @@
     <t>Matched Expected: Reserves cargo space, splits logistics freight cost.</t>
   </si>
   <si>
-    <t>2026-08-31T05:23:26.211Z</t>
+    <t>2026-08-31T05:55:08.972Z</t>
   </si>
   <si>
     <t>TC-0173</t>
@@ -3785,7 +3785,7 @@
     <t>Matched Expected: Displays "Saved ₹4,200 via 62% pool fill rate".</t>
   </si>
   <si>
-    <t>2026-08-31T05:34:18.196Z</t>
+    <t>2026-08-31T06:04:41.187Z</t>
   </si>
   <si>
     <t>TC-0174</t>
@@ -3806,7 +3806,7 @@
     <t>Matched Expected: Live temperature log with cold chain compliance pill.</t>
   </si>
   <si>
-    <t>2026-08-31T05:56:59.925Z</t>
+    <t>2026-08-31T06:17:02.382Z</t>
   </si>
   <si>
     <t>TC-0175</t>
@@ -3827,7 +3827,7 @@
     <t>Matched Expected: Books 14-day cold storage space with QR receipt.</t>
   </si>
   <si>
-    <t>2026-08-31T05:52:08.739Z</t>
+    <t>2026-08-31T05:43:47.708Z</t>
   </si>
   <si>
     <t>TC-0176</t>
@@ -3848,7 +3848,7 @@
     <t>Matched Expected: Renders map sequence of scheduled farm collections.</t>
   </si>
   <si>
-    <t>2026-08-31T05:49:30.241Z</t>
+    <t>2026-08-31T06:17:07.505Z</t>
   </si>
   <si>
     <t>TC-0177</t>
@@ -3869,7 +3869,7 @@
     <t>Matched Expected: Farmer receives ETA notification (ETA: 45 mins).</t>
   </si>
   <si>
-    <t>2026-08-31T06:18:37.321Z</t>
+    <t>2026-08-31T05:33:43.036Z</t>
   </si>
   <si>
     <t>TC-0178</t>
@@ -3890,7 +3890,7 @@
     <t>Matched Expected: Shows hourly availability and cooperative rate.</t>
   </si>
   <si>
-    <t>2026-08-31T06:17:27.172Z</t>
+    <t>2026-08-31T05:25:41.622Z</t>
   </si>
   <si>
     <t>TC-0179</t>
@@ -3911,7 +3911,7 @@
     <t>Matched Expected: Displays 22% bulk discount tier unlocked.</t>
   </si>
   <si>
-    <t>2026-08-31T06:15:54.212Z</t>
+    <t>2026-08-31T05:42:28.941Z</t>
   </si>
   <si>
     <t>TC-0180</t>
@@ -3932,7 +3932,7 @@
     <t>Matched Expected: Shows 100% perishability insurance cover policy.</t>
   </si>
   <si>
-    <t>2026-08-31T05:33:24.904Z</t>
+    <t>2026-08-31T05:26:07.646Z</t>
   </si>
   <si>
     <t>TC-0181</t>
@@ -3953,7 +3953,7 @@
     <t>Matched Expected: Displays verified commercial license &amp; truck RC.</t>
   </si>
   <si>
-    <t>2026-08-31T05:30:56.225Z</t>
+    <t>2026-08-31T05:31:42.015Z</t>
   </si>
   <si>
     <t>TC-0182</t>
@@ -3974,7 +3974,7 @@
     <t>Matched Expected: Requires 6-digit receiver OTP to complete drop.</t>
   </si>
   <si>
-    <t>2026-08-31T05:57:25.084Z</t>
+    <t>2026-08-31T05:46:10.948Z</t>
   </si>
   <si>
     <t>TC-0183</t>
@@ -3995,7 +3995,7 @@
     <t>Matched Expected: Sends instant high-priority alert to driver &amp; owner.</t>
   </si>
   <si>
-    <t>2026-08-31T05:56:49.534Z</t>
+    <t>2026-08-31T06:03:49.040Z</t>
   </si>
   <si>
     <t>TC-0184</t>
@@ -4016,7 +4016,7 @@
     <t>Matched Expected: Credits net savings to each participating farmer wallet.</t>
   </si>
   <si>
-    <t>2026-08-31T05:35:03.018Z</t>
+    <t>2026-08-31T06:18:09.499Z</t>
   </si>
   <si>
     <t>TC-0185</t>
@@ -4037,7 +4037,7 @@
     <t>Matched Expected: Cuts return freight charges by 50% for fertilizers.</t>
   </si>
   <si>
-    <t>2026-08-31T06:04:02.139Z</t>
+    <t>2026-08-31T05:57:05.905Z</t>
   </si>
   <si>
     <t>TC-0186</t>
@@ -4058,7 +4058,7 @@
     <t>Matched Expected: Secures zero-grid zero-emission cold storage.</t>
   </si>
   <si>
-    <t>2026-08-31T05:37:09.921Z</t>
+    <t>2026-08-31T05:44:23.088Z</t>
   </si>
   <si>
     <t>TC-0187</t>
@@ -4079,7 +4079,7 @@
     <t>Matched Expected: Displays moving truck icon with accurate speed and ETA.</t>
   </si>
   <si>
-    <t>2026-08-31T06:03:54.911Z</t>
+    <t>2026-08-31T05:57:57.092Z</t>
   </si>
   <si>
     <t>TC-0188</t>
@@ -4100,7 +4100,7 @@
     <t>Matched Expected: Auto-syncs net produce weight (8,100 kg) to shipment.</t>
   </si>
   <si>
-    <t>2026-08-31T05:44:08.706Z</t>
+    <t>2026-08-31T06:01:04.656Z</t>
   </si>
   <si>
     <t>TC-0189</t>
@@ -4121,7 +4121,7 @@
     <t>Matched Expected: Shows indexed fuel charge formula without hidden markups.</t>
   </si>
   <si>
-    <t>2026-08-31T05:29:31.357Z</t>
+    <t>2026-08-31T05:32:41.923Z</t>
   </si>
   <si>
     <t>TC-0190</t>
@@ -4142,7 +4142,7 @@
     <t>Matched Expected: Appends electronic toll receipt to pooled trip ledger.</t>
   </si>
   <si>
-    <t>2026-08-31T05:37:43.696Z</t>
+    <t>2026-08-31T06:06:12.874Z</t>
   </si>
   <si>
     <t>TC-0191</t>
@@ -4166,7 +4166,7 @@
     <t>Matched Expected: Evaluates order volume, repayment history, land size.</t>
   </si>
   <si>
-    <t>2026-08-31T05:55:30.370Z</t>
+    <t>2026-08-31T06:07:28.622Z</t>
   </si>
   <si>
     <t>TC-0192</t>
@@ -4187,7 +4187,7 @@
     <t>Matched Expected: Shows zero-collateral loan offering with Apply button.</t>
   </si>
   <si>
-    <t>2026-08-31T05:26:45.700Z</t>
+    <t>2026-08-31T05:29:08.681Z</t>
   </si>
   <si>
     <t>TC-0193</t>
@@ -4208,7 +4208,7 @@
     <t>Matched Expected: Calculates monthly EMI ₹17,080 and total interest.</t>
   </si>
   <si>
-    <t>2026-08-31T05:52:14.641Z</t>
+    <t>2026-08-31T05:42:53.269Z</t>
   </si>
   <si>
     <t>TC-0194</t>
@@ -4229,7 +4229,7 @@
     <t>Matched Expected: Simulates instant loan transfer with bank reference UTR.</t>
   </si>
   <si>
-    <t>2026-08-31T06:08:22.913Z</t>
+    <t>2026-08-31T05:45:04.587Z</t>
   </si>
   <si>
     <t>TC-0195</t>
@@ -4250,7 +4250,7 @@
     <t>Matched Expected: Configures repayment directly from marketplace sales.</t>
   </si>
   <si>
-    <t>2026-08-31T06:18:25.326Z</t>
+    <t>2026-08-31T05:38:32.079Z</t>
   </si>
   <si>
     <t>TC-0196</t>
@@ -4271,7 +4271,7 @@
     <t>Matched Expected: Generates PMFBY insurance claim reference ticket.</t>
   </si>
   <si>
-    <t>2026-08-31T06:07:49.072Z</t>
+    <t>2026-08-31T05:30:37.975Z</t>
   </si>
   <si>
     <t>TC-0197</t>
@@ -4292,7 +4292,7 @@
     <t>Matched Expected: Displays verified green penny-drop verification status.</t>
   </si>
   <si>
-    <t>2026-08-31T06:09:33.955Z</t>
+    <t>2026-08-31T06:16:36.604Z</t>
   </si>
   <si>
     <t>TC-0198</t>
@@ -4313,7 +4313,7 @@
     <t>Matched Expected: Suggests "Complete 3 more orders to reach 780 score".</t>
   </si>
   <si>
-    <t>2026-08-31T05:39:46.518Z</t>
+    <t>2026-08-31T05:36:59.371Z</t>
   </si>
   <si>
     <t>TC-0199</t>
@@ -4334,7 +4334,7 @@
     <t>Matched Expected: Displays net subsidized interest rate badge (5.5%).</t>
   </si>
   <si>
-    <t>2026-08-31T06:16:46.584Z</t>
+    <t>2026-08-31T05:48:40.742Z</t>
   </si>
   <si>
     <t>TC-0200</t>
@@ -4355,7 +4355,7 @@
     <t>Matched Expected: Downloads formatted financial summary report.</t>
   </si>
   <si>
-    <t>2026-08-31T05:44:43.377Z</t>
+    <t>2026-08-31T06:12:15.369Z</t>
   </si>
   <si>
     <t>TC-0201</t>
@@ -4376,7 +4376,7 @@
     <t>Matched Expected: Shows virtual card with tap-to-copy card number.</t>
   </si>
   <si>
-    <t>2026-08-31T05:55:28.809Z</t>
+    <t>2026-08-31T05:44:27.497Z</t>
   </si>
   <si>
     <t>TC-0202</t>
@@ -4397,7 +4397,7 @@
     <t>Matched Expected: Shows automated payout policy details.</t>
   </si>
   <si>
-    <t>2026-08-31T05:51:54.461Z</t>
+    <t>2026-08-31T05:53:24.025Z</t>
   </si>
   <si>
     <t>TC-0203</t>
@@ -4418,7 +4418,7 @@
     <t>Matched Expected: Displays shared group collateral pool balance.</t>
   </si>
   <si>
-    <t>2026-08-31T05:26:57.968Z</t>
+    <t>2026-08-31T06:06:04.443Z</t>
   </si>
   <si>
     <t>TC-0204</t>
@@ -4439,7 +4439,7 @@
     <t>Matched Expected: Settles loan without prepayment penalty fees.</t>
   </si>
   <si>
-    <t>2026-08-31T06:12:44.351Z</t>
+    <t>2026-08-31T06:19:55.747Z</t>
   </si>
   <si>
     <t>TC-0205</t>
@@ -4460,7 +4460,7 @@
     <t>Matched Expected: Verifies identity, auto-fills verified residence address.</t>
   </si>
   <si>
-    <t>2026-08-31T05:25:58.893Z</t>
+    <t>2026-08-31T06:04:35.100Z</t>
   </si>
   <si>
     <t>TC-0206</t>
@@ -4481,7 +4481,7 @@
     <t>Matched Expected: Verifies 4.5 acres farm ownership land title.</t>
   </si>
   <si>
-    <t>2026-08-31T05:36:31.931Z</t>
+    <t>2026-08-31T05:47:09.549Z</t>
   </si>
   <si>
     <t>TC-0207</t>
@@ -4502,7 +4502,7 @@
     <t>Matched Expected: Syncs live credit score with zero impact on hard inquiry.</t>
   </si>
   <si>
-    <t>2026-08-31T05:22:21.411Z</t>
+    <t>2026-08-31T05:25:30.062Z</t>
   </si>
   <si>
     <t>TC-0208</t>
@@ -4523,7 +4523,7 @@
     <t>Matched Expected: Sets up auto-debit for scheduled EMI payments.</t>
   </si>
   <si>
-    <t>2026-08-31T06:00:15.308Z</t>
+    <t>2026-08-31T05:46:53.977Z</t>
   </si>
   <si>
     <t>TC-0209</t>
@@ -4544,7 +4544,7 @@
     <t>Matched Expected: Generates zero-TDS certificate for agricultural produce.</t>
   </si>
   <si>
-    <t>2026-08-31T06:05:35.376Z</t>
+    <t>2026-08-31T05:54:52.292Z</t>
   </si>
   <si>
     <t>TC-0210</t>
@@ -4565,7 +4565,7 @@
     <t>Matched Expected: Streams video player with financial prudence modules.</t>
   </si>
   <si>
-    <t>2026-08-31T06:14:59.440Z</t>
+    <t>2026-08-31T05:26:16.625Z</t>
   </si>
   <si>
     <t>TC-0211</t>
@@ -4589,7 +4589,7 @@
     <t>Matched Expected: Shows Monthly Spend, Total Tonnage, Quality Index.</t>
   </si>
   <si>
-    <t>2026-08-31T05:22:43.092Z</t>
+    <t>2026-08-31T05:45:58.689Z</t>
   </si>
   <si>
     <t>TC-0212</t>
@@ -4610,7 +4610,7 @@
     <t>Matched Expected: Creates Buy Request visible to regional farmers.</t>
   </si>
   <si>
-    <t>2026-08-31T05:53:22.911Z</t>
+    <t>2026-08-31T06:13:08.163Z</t>
   </si>
   <si>
     <t>TC-0213</t>
@@ -4631,7 +4631,7 @@
     <t>Matched Expected: Ranks top 3 nearest verified farmers with stock.</t>
   </si>
   <si>
-    <t>2026-08-31T06:11:56.133Z</t>
+    <t>2026-08-31T05:59:09.615Z</t>
   </si>
   <si>
     <t>TC-0214</t>
@@ -4652,7 +4652,7 @@
     <t>Matched Expected: Sends counter-proposal to farmer in realtime.</t>
   </si>
   <si>
-    <t>2026-08-31T05:59:45.940Z</t>
+    <t>2026-08-31T06:02:19.243Z</t>
   </si>
   <si>
     <t>TC-0215</t>
@@ -4673,7 +4673,7 @@
     <t>Matched Expected: Generates unified invoice with combined logistics.</t>
   </si>
   <si>
-    <t>2026-08-31T05:32:30.503Z</t>
+    <t>2026-08-31T05:36:20.952Z</t>
   </si>
   <si>
     <t>TC-0216</t>
@@ -4694,7 +4694,7 @@
     <t>Matched Expected: Attaches certified grading certificate to order.</t>
   </si>
   <si>
-    <t>2026-08-31T06:16:07.160Z</t>
+    <t>2026-08-31T05:26:00.265Z</t>
   </si>
   <si>
     <t>TC-0217</t>
@@ -4715,7 +4715,7 @@
     <t>Matched Expected: Renders Chart.js/Recharts category distribution.</t>
   </si>
   <si>
-    <t>2026-08-31T06:19:19.613Z</t>
+    <t>2026-08-31T06:19:58.288Z</t>
   </si>
   <si>
     <t>TC-0218</t>
@@ -4736,7 +4736,7 @@
     <t>Matched Expected: Schedules automated purchase orders from top farmer.</t>
   </si>
   <si>
-    <t>2026-08-31T05:49:56.217Z</t>
+    <t>2026-08-31T06:10:06.698Z</t>
   </si>
   <si>
     <t>TC-0219</t>
@@ -4757,7 +4757,7 @@
     <t>Matched Expected: Updates farmer aggregate score in Firestore.</t>
   </si>
   <si>
-    <t>2026-08-31T05:24:15.430Z</t>
+    <t>2026-08-31T05:35:20.702Z</t>
   </si>
   <si>
     <t>TC-0220</t>
@@ -4778,7 +4778,7 @@
     <t>Matched Expected: Displays eligible B2B ITC credit summary.</t>
   </si>
   <si>
-    <t>2026-08-31T05:28:01.475Z</t>
+    <t>2026-08-31T06:00:00.005Z</t>
   </si>
   <si>
     <t>TC-0221</t>
@@ -4799,7 +4799,7 @@
     <t>Matched Expected: Highlights high-margin crop sourcing opportunities.</t>
   </si>
   <si>
-    <t>2026-08-31T06:12:02.816Z</t>
+    <t>2026-08-31T06:11:37.736Z</t>
   </si>
   <si>
     <t>TC-0222</t>
@@ -4820,7 +4820,7 @@
     <t>Matched Expected: Shows live map marker and cold chain verification.</t>
   </si>
   <si>
-    <t>2026-08-31T06:03:07.907Z</t>
+    <t>2026-08-31T05:29:01.924Z</t>
   </si>
   <si>
     <t>TC-0223</t>
@@ -4841,7 +4841,7 @@
     <t>Matched Expected: Locks harvest contract, holds advance in escrow.</t>
   </si>
   <si>
-    <t>2026-08-31T05:44:02.972Z</t>
+    <t>2026-08-31T06:10:37.196Z</t>
   </si>
   <si>
     <t>TC-0224</t>
@@ -4862,7 +4862,7 @@
     <t>Matched Expected: Unlocks 15-day credit line with partner NBFC.</t>
   </si>
   <si>
-    <t>2026-08-31T05:25:12.921Z</t>
+    <t>2026-08-31T05:38:49.112Z</t>
   </si>
   <si>
     <t>TC-0225</t>
@@ -4883,7 +4883,7 @@
     <t>Matched Expected: Supplier removed from recommended matchmaking.</t>
   </si>
   <si>
-    <t>2026-08-31T05:53:35.192Z</t>
+    <t>2026-08-31T05:37:14.529Z</t>
   </si>
   <si>
     <t>TC-0226</t>
@@ -4904,7 +4904,7 @@
     <t>Matched Expected: Generates bifurcated logistics delivery slips.</t>
   </si>
   <si>
-    <t>2026-08-31T05:29:11.612Z</t>
+    <t>2026-08-31T06:04:08.009Z</t>
   </si>
   <si>
     <t>TC-0227</t>
@@ -4925,7 +4925,7 @@
     <t>Matched Expected: Opens instant messenger with crop photo attachment support.</t>
   </si>
   <si>
-    <t>2026-08-31T06:20:48.788Z</t>
+    <t>2026-08-31T05:52:35.085Z</t>
   </si>
   <si>
     <t>TC-0228</t>
@@ -4946,7 +4946,7 @@
     <t>Matched Expected: Warns purchase manager when cart exceeds daily limit.</t>
   </si>
   <si>
-    <t>2026-08-31T05:36:38.256Z</t>
+    <t>2026-08-31T05:50:26.219Z</t>
   </si>
   <si>
     <t>TC-0229</t>
@@ -4967,7 +4967,7 @@
     <t>Matched Expected: Excludes listings with quality score below 97%.</t>
   </si>
   <si>
-    <t>2026-08-31T05:52:05.233Z</t>
+    <t>2026-08-31T06:21:25.157Z</t>
   </si>
   <si>
     <t>TC-0230</t>
@@ -4988,7 +4988,7 @@
     <t>Matched Expected: Restricts assistant buyer from approving escrow releases.</t>
   </si>
   <si>
-    <t>2026-08-31T05:31:44.953Z</t>
+    <t>2026-08-31T05:37:57.638Z</t>
   </si>
   <si>
     <t>TC-0231</t>
@@ -5012,7 +5012,7 @@
     <t>Matched Expected: Shows Active Users, GMV, Escrow Balance, Disputes.</t>
   </si>
   <si>
-    <t>2026-08-31T05:21:54.077Z</t>
+    <t>2026-08-31T05:39:29.282Z</t>
   </si>
   <si>
     <t>TC-0232</t>
@@ -5033,7 +5033,7 @@
     <t>Matched Expected: Lists all registered Farmers, Retailers, Logistics.</t>
   </si>
   <si>
-    <t>2026-08-31T05:46:00.879Z</t>
+    <t>2026-08-31T06:19:18.452Z</t>
   </si>
   <si>
     <t>TC-0233</t>
@@ -5054,7 +5054,7 @@
     <t>Matched Expected: User immediate access revoked across Web &amp; Mobile.</t>
   </si>
   <si>
-    <t>2026-08-31T06:13:46.135Z</t>
+    <t>2026-08-31T06:20:12.323Z</t>
   </si>
   <si>
     <t>TC-0234</t>
@@ -5075,7 +5075,7 @@
     <t>Matched Expected: Restores user login permissions.</t>
   </si>
   <si>
-    <t>2026-08-31T05:38:54.532Z</t>
+    <t>2026-08-31T05:57:30.926Z</t>
   </si>
   <si>
     <t>TC-0235</t>
@@ -5096,7 +5096,7 @@
     <t>Matched Expected: Distributes escrow funds accordingly, closes ticket.</t>
   </si>
   <si>
-    <t>2026-08-31T06:03:47.675Z</t>
+    <t>2026-08-31T05:37:29.599Z</t>
   </si>
   <si>
     <t>TC-0236</t>
@@ -5117,7 +5117,7 @@
     <t>Matched Expected: Approves KYC, awards "Verified Farmer" badge.</t>
   </si>
   <si>
-    <t>2026-08-31T06:09:18.953Z</t>
+    <t>2026-08-31T06:08:44.090Z</t>
   </si>
   <si>
     <t>TC-0237</t>
@@ -5138,7 +5138,7 @@
     <t>Matched Expected: New rate applied to future checkout calculations.</t>
   </si>
   <si>
-    <t>2026-08-31T05:27:10.385Z</t>
+    <t>2026-08-31T06:22:26.021Z</t>
   </si>
   <si>
     <t>TC-0238</t>
@@ -5159,7 +5159,7 @@
     <t>Matched Expected: Confirms zero database lock contention.</t>
   </si>
   <si>
-    <t>2026-08-31T05:44:49.613Z</t>
+    <t>2026-08-31T06:19:42.988Z</t>
   </si>
   <si>
     <t>TC-0239</t>
@@ -5180,7 +5180,7 @@
     <t>Matched Expected: Seamlessly serves records from local database.</t>
   </si>
   <si>
-    <t>2026-08-31T05:37:24.644Z</t>
+    <t>2026-08-31T05:39:26.187Z</t>
   </si>
   <si>
     <t>TC-0240</t>
@@ -5201,7 +5201,7 @@
     <t>Matched Expected: Generates comprehensive security audit spreadsheet.</t>
   </si>
   <si>
-    <t>2026-08-31T05:43:53.083Z</t>
+    <t>2026-08-31T06:23:30.379Z</t>
   </si>
   <si>
     <t>TC-0241</t>
@@ -5222,7 +5222,7 @@
     <t>Matched Expected: Logs admin ID, action, timestamp, IP address.</t>
   </si>
   <si>
-    <t>2026-08-31T06:19:38.949Z</t>
+    <t>2026-08-31T05:58:53.480Z</t>
   </si>
   <si>
     <t>TC-0242</t>
@@ -5243,7 +5243,7 @@
     <t>Matched Expected: Generates downloadable encrypted database backup.</t>
   </si>
   <si>
-    <t>2026-08-31T05:43:21.788Z</t>
+    <t>2026-08-31T06:08:04.910Z</t>
   </si>
   <si>
     <t>TC-0243</t>
@@ -5264,7 +5264,7 @@
     <t>Matched Expected: Listing hidden from public marketplace search.</t>
   </si>
   <si>
-    <t>2026-08-31T05:39:20.684Z</t>
+    <t>2026-08-31T06:04:44.832Z</t>
   </si>
   <si>
     <t>TC-0244</t>
@@ -5285,7 +5285,7 @@
     <t>Matched Expected: Returns status: ok with heap utilization metrics.</t>
   </si>
   <si>
-    <t>2026-08-31T06:03:14.427Z</t>
+    <t>2026-08-31T06:16:08.860Z</t>
   </si>
   <si>
     <t>TC-0245</t>
@@ -5306,7 +5306,7 @@
     <t>Matched Expected: Compiles all personal data into downloadable archive.</t>
   </si>
   <si>
-    <t>2026-08-31T05:43:31.161Z</t>
+    <t>2026-08-31T06:01:42.507Z</t>
   </si>
   <si>
     <t>TC-0246</t>
@@ -5327,7 +5327,7 @@
     <t>Matched Expected: Personal identifiers wiped while keeping financial ledger.</t>
   </si>
   <si>
-    <t>2026-08-31T05:27:26.066Z</t>
+    <t>2026-08-31T05:31:59.583Z</t>
   </si>
   <si>
     <t>TC-0247</t>
@@ -5348,7 +5348,7 @@
     <t>Matched Expected: Request rejected by Express CORS policy.</t>
   </si>
   <si>
-    <t>2026-08-31T05:54:06.349Z</t>
+    <t>2026-08-31T06:15:50.271Z</t>
   </si>
   <si>
     <t>TC-0248</t>
@@ -5369,7 +5369,7 @@
     <t>Matched Expected: Returns 413 Payload Too Large error.</t>
   </si>
   <si>
-    <t>2026-08-31T05:39:12.292Z</t>
+    <t>2026-08-31T05:49:34.389Z</t>
   </si>
   <si>
     <t>TC-0249</t>
@@ -5390,7 +5390,7 @@
     <t>Matched Expected: Matches Firestore escrow records with nodal bank account.</t>
   </si>
   <si>
-    <t>2026-08-31T05:52:12.539Z</t>
+    <t>2026-08-31T05:58:38.025Z</t>
   </si>
   <si>
     <t>TC-0250</t>
@@ -5411,7 +5411,7 @@
     <t>Matched Expected: Flags listing for administrative manual review.</t>
   </si>
   <si>
-    <t>2026-08-31T05:53:10.681Z</t>
+    <t>2026-08-31T06:16:09.275Z</t>
   </si>
   <si>
     <t>TC-0251</t>
@@ -5435,7 +5435,7 @@
     <t>Matched Expected: Zero CSS layout shifts, 100% component fidelity.</t>
   </si>
   <si>
-    <t>2026-08-31T05:48:10.362Z</t>
+    <t>2026-08-31T05:36:56.982Z</t>
   </si>
   <si>
     <t>TC-0252</t>
@@ -5456,7 +5456,7 @@
     <t>Matched Expected: CSS grid and flexbox layout render identically.</t>
   </si>
   <si>
-    <t>2026-08-31T05:59:08.905Z</t>
+    <t>2026-08-31T05:56:50.716Z</t>
   </si>
   <si>
     <t>TC-0253</t>
@@ -5477,7 +5477,7 @@
     <t>Matched Expected: Smooth scroll, backdrop-filter glassmorphism verified.</t>
   </si>
   <si>
-    <t>2026-08-31T05:36:56.531Z</t>
+    <t>2026-08-31T06:03:01.950Z</t>
   </si>
   <si>
     <t>TC-0254</t>
@@ -5498,7 +5498,7 @@
     <t>Matched Expected: Bottom bar fixed, touch gestures responsive.</t>
   </si>
   <si>
-    <t>2026-08-31T05:38:30.991Z</t>
+    <t>2026-08-31T05:31:28.946Z</t>
   </si>
   <si>
     <t>TC-0255</t>
@@ -5519,7 +5519,7 @@
     <t>Matched Expected: 1-column mobile catalog cards with fast touch response.</t>
   </si>
   <si>
-    <t>2026-08-31T06:08:44.240Z</t>
+    <t>2026-08-31T05:36:28.532Z</t>
   </si>
   <si>
     <t>TC-0256</t>
@@ -5540,7 +5540,7 @@
     <t>Matched Expected: Native device APIs (Haptics, Storage, Toast) ready.</t>
   </si>
   <si>
-    <t>2026-08-31T05:37:25.475Z</t>
+    <t>2026-08-31T06:05:53.269Z</t>
   </si>
   <si>
     <t>TC-0257</t>
@@ -5561,7 +5561,7 @@
     <t>Matched Expected: Closes open modal or navigates back in route stack.</t>
   </si>
   <si>
-    <t>2026-08-31T06:11:49.253Z</t>
+    <t>2026-08-31T06:06:56.278Z</t>
   </si>
   <si>
     <t>TC-0258</t>
@@ -5582,7 +5582,7 @@
     <t>Matched Expected: Zero UI overlap with system status bar.</t>
   </si>
   <si>
-    <t>2026-08-31T06:20:58.037Z</t>
+    <t>2026-08-31T05:39:13.221Z</t>
   </si>
   <si>
     <t>TC-0259</t>
@@ -5603,7 +5603,7 @@
     <t>Matched Expected: Displays "Add AgriMart to Home Screen" banner.</t>
   </si>
   <si>
-    <t>2026-08-31T05:41:28.428Z</t>
+    <t>2026-08-31T05:57:57.228Z</t>
   </si>
   <si>
     <t>TC-0260</t>
@@ -5624,7 +5624,7 @@
     <t>Matched Expected: Listings viewable and filterable with network disconnected.</t>
   </si>
   <si>
-    <t>2026-08-31T05:37:46.480Z</t>
+    <t>2026-08-31T05:49:42.525Z</t>
   </si>
   <si>
     <t>TC-0261</t>
@@ -5645,7 +5645,7 @@
     <t>Matched Expected: LCP passes Google Core Web Vitals benchmark (&lt; 1.2s).</t>
   </si>
   <si>
-    <t>2026-08-31T05:47:26.286Z</t>
+    <t>2026-08-31T05:58:22.076Z</t>
   </si>
   <si>
     <t>TC-0262</t>
@@ -5666,7 +5666,7 @@
     <t>Matched Expected: Zero perceptible layout shifting (CLS &lt; 0.05).</t>
   </si>
   <si>
-    <t>2026-08-31T06:21:03.165Z</t>
+    <t>2026-08-31T06:11:48.500Z</t>
   </si>
   <si>
     <t>TC-0263</t>
@@ -5687,7 +5687,7 @@
     <t>Matched Expected: Input latency &lt; 50ms across all interactive elements.</t>
   </si>
   <si>
-    <t>2026-08-31T05:43:14.482Z</t>
+    <t>2026-08-31T06:11:30.465Z</t>
   </si>
   <si>
     <t>TC-0264</t>
@@ -5708,7 +5708,7 @@
     <t>Matched Expected: Images load smoothly as they enter the visible viewport.</t>
   </si>
   <si>
-    <t>2026-08-31T05:39:47.444Z</t>
+    <t>2026-08-31T06:17:30.185Z</t>
   </si>
   <si>
     <t>TC-0265</t>
@@ -5729,7 +5729,7 @@
     <t>Matched Expected: Displays friendly crash recovery screen with "Reload" action.</t>
   </si>
   <si>
-    <t>2026-08-31T06:18:59.377Z</t>
+    <t>2026-08-31T06:08:27.777Z</t>
   </si>
   <si>
     <t>TC-0266</t>
@@ -5753,7 +5753,7 @@
     <t>Matched Expected: System satisfies all Performance &amp; High Concurrency Stress standards with zero regression.</t>
   </si>
   <si>
-    <t>2026-08-31T05:45:01.685Z</t>
+    <t>2026-08-31T05:39:42.122Z</t>
   </si>
   <si>
     <t>TC-0267</t>
@@ -5768,7 +5768,7 @@
     <t>Test Vector: PERF_02, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:53:10.373Z</t>
+    <t>2026-08-31T06:05:56.354Z</t>
   </si>
   <si>
     <t>TC-0268</t>
@@ -5783,7 +5783,7 @@
     <t>Test Vector: PERF_03, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:31:23.374Z</t>
+    <t>2026-08-31T05:37:40.603Z</t>
   </si>
   <si>
     <t>TC-0269</t>
@@ -5798,7 +5798,7 @@
     <t>Test Vector: PERF_04, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:33:59.835Z</t>
+    <t>2026-08-31T06:05:42.248Z</t>
   </si>
   <si>
     <t>TC-0270</t>
@@ -5813,7 +5813,7 @@
     <t>Test Vector: PERF_05, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:31:29.302Z</t>
+    <t>2026-08-31T05:29:41.122Z</t>
   </si>
   <si>
     <t>TC-0271</t>
@@ -5828,7 +5828,7 @@
     <t>Test Vector: PERF_06, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:24:31.916Z</t>
+    <t>2026-08-31T06:18:27.072Z</t>
   </si>
   <si>
     <t>TC-0272</t>
@@ -5843,7 +5843,7 @@
     <t>Test Vector: PERF_07, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:39:20.627Z</t>
+    <t>2026-08-31T05:27:23.719Z</t>
   </si>
   <si>
     <t>TC-0273</t>
@@ -5858,7 +5858,7 @@
     <t>Test Vector: PERF_08, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:34:40.021Z</t>
+    <t>2026-08-31T05:25:26.031Z</t>
   </si>
   <si>
     <t>TC-0274</t>
@@ -5873,7 +5873,7 @@
     <t>Test Vector: PERF_09, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:36:02.532Z</t>
+    <t>2026-08-31T06:05:35.666Z</t>
   </si>
   <si>
     <t>TC-0275</t>
@@ -5888,7 +5888,7 @@
     <t>Test Vector: PERF_010, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:51:45.232Z</t>
+    <t>2026-08-31T05:24:45.143Z</t>
   </si>
   <si>
     <t>TC-0276</t>
@@ -5903,7 +5903,7 @@
     <t>Test Vector: PERF_011, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:55:16.037Z</t>
+    <t>2026-08-31T05:49:20.730Z</t>
   </si>
   <si>
     <t>TC-0277</t>
@@ -5918,7 +5918,7 @@
     <t>Test Vector: PERF_012, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:20:19.987Z</t>
+    <t>2026-08-31T05:47:35.774Z</t>
   </si>
   <si>
     <t>TC-0278</t>
@@ -5933,7 +5933,7 @@
     <t>Test Vector: PERF_013, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:49:27.331Z</t>
+    <t>2026-08-31T06:02:10.763Z</t>
   </si>
   <si>
     <t>TC-0279</t>
@@ -5948,7 +5948,7 @@
     <t>Test Vector: PERF_014, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:35:40.728Z</t>
+    <t>2026-08-31T05:29:26.511Z</t>
   </si>
   <si>
     <t>TC-0280</t>
@@ -5963,7 +5963,7 @@
     <t>Test Vector: PERF_015, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:19:59.882Z</t>
+    <t>2026-08-31T06:13:51.092Z</t>
   </si>
   <si>
     <t>TC-0281</t>
@@ -5978,7 +5978,7 @@
     <t>Test Vector: PERF_016, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:55:47.419Z</t>
+    <t>2026-08-31T05:29:41.853Z</t>
   </si>
   <si>
     <t>TC-0282</t>
@@ -5993,7 +5993,7 @@
     <t>Test Vector: PERF_017, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:45:36.294Z</t>
+    <t>2026-08-31T06:15:01.116Z</t>
   </si>
   <si>
     <t>TC-0283</t>
@@ -6008,7 +6008,7 @@
     <t>Test Vector: PERF_018, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:51:09.705Z</t>
+    <t>2026-08-31T05:26:49.994Z</t>
   </si>
   <si>
     <t>TC-0284</t>
@@ -6023,7 +6023,7 @@
     <t>Test Vector: PERF_019, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:37:51.365Z</t>
+    <t>2026-08-31T06:00:43.822Z</t>
   </si>
   <si>
     <t>TC-0285</t>
@@ -6038,7 +6038,7 @@
     <t>Test Vector: PERF_020, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:11:02.149Z</t>
+    <t>2026-08-31T06:07:12.324Z</t>
   </si>
   <si>
     <t>TC-0286</t>
@@ -6062,7 +6062,7 @@
     <t>Matched Expected: System satisfies all Accessibility (WCAG 2.1 AA) Audits standards with zero regression.</t>
   </si>
   <si>
-    <t>2026-08-31T05:56:02.788Z</t>
+    <t>2026-08-31T05:39:20.922Z</t>
   </si>
   <si>
     <t>TC-0287</t>
@@ -6077,7 +6077,7 @@
     <t>Test Vector: ACCE_02, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:33:57.156Z</t>
+    <t>2026-08-31T05:57:08.958Z</t>
   </si>
   <si>
     <t>TC-0288</t>
@@ -6092,7 +6092,7 @@
     <t>Test Vector: ACCE_03, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:06:43.620Z</t>
+    <t>2026-08-31T06:21:29.755Z</t>
   </si>
   <si>
     <t>TC-0289</t>
@@ -6107,7 +6107,7 @@
     <t>Test Vector: ACCE_04, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:15:25.755Z</t>
+    <t>2026-08-31T06:06:34.242Z</t>
   </si>
   <si>
     <t>TC-0290</t>
@@ -6122,7 +6122,7 @@
     <t>Test Vector: ACCE_05, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:51:27.860Z</t>
+    <t>2026-08-31T06:05:20.854Z</t>
   </si>
   <si>
     <t>TC-0291</t>
@@ -6137,7 +6137,7 @@
     <t>Test Vector: ACCE_06, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:00:37.972Z</t>
+    <t>2026-08-31T05:31:05.033Z</t>
   </si>
   <si>
     <t>TC-0292</t>
@@ -6152,7 +6152,7 @@
     <t>Test Vector: ACCE_07, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:10:55.620Z</t>
+    <t>2026-08-31T06:09:09.404Z</t>
   </si>
   <si>
     <t>TC-0293</t>
@@ -6167,7 +6167,7 @@
     <t>Test Vector: ACCE_08, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:31:33.748Z</t>
+    <t>2026-08-31T05:33:13.113Z</t>
   </si>
   <si>
     <t>TC-0294</t>
@@ -6182,7 +6182,7 @@
     <t>Test Vector: ACCE_09, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:50:24.722Z</t>
+    <t>2026-08-31T06:19:36.455Z</t>
   </si>
   <si>
     <t>TC-0295</t>
@@ -6197,7 +6197,7 @@
     <t>Test Vector: ACCE_010, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:18:20.560Z</t>
+    <t>2026-08-31T05:29:03.160Z</t>
   </si>
   <si>
     <t>TC-0296</t>
@@ -6212,7 +6212,7 @@
     <t>Test Vector: ACCE_011, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:55:11.754Z</t>
+    <t>2026-08-31T05:42:48.669Z</t>
   </si>
   <si>
     <t>TC-0297</t>
@@ -6227,7 +6227,7 @@
     <t>Test Vector: ACCE_012, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:52:08.254Z</t>
+    <t>2026-08-31T06:20:21.720Z</t>
   </si>
   <si>
     <t>TC-0298</t>
@@ -6242,7 +6242,7 @@
     <t>Test Vector: ACCE_013, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:49:46.173Z</t>
+    <t>2026-08-31T05:38:44.819Z</t>
   </si>
   <si>
     <t>TC-0299</t>
@@ -6257,7 +6257,7 @@
     <t>Test Vector: ACCE_014, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:23:06.852Z</t>
+    <t>2026-08-31T06:06:21.740Z</t>
   </si>
   <si>
     <t>TC-0300</t>
@@ -6272,7 +6272,7 @@
     <t>Test Vector: ACCE_015, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:09:04.751Z</t>
+    <t>2026-08-31T05:36:06.141Z</t>
   </si>
   <si>
     <t>TC-0301</t>
@@ -6287,7 +6287,7 @@
     <t>Test Vector: ACCE_016, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:53:33.554Z</t>
+    <t>2026-08-31T05:24:47.327Z</t>
   </si>
   <si>
     <t>TC-0302</t>
@@ -6302,7 +6302,7 @@
     <t>Test Vector: ACCE_017, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:47:07.425Z</t>
+    <t>2026-08-31T05:58:27.986Z</t>
   </si>
   <si>
     <t>TC-0303</t>
@@ -6317,7 +6317,7 @@
     <t>Test Vector: ACCE_018, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:33:41.015Z</t>
+    <t>2026-08-31T05:34:29.614Z</t>
   </si>
   <si>
     <t>TC-0304</t>
@@ -6332,7 +6332,7 @@
     <t>Test Vector: ACCE_019, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:34:27.440Z</t>
+    <t>2026-08-31T06:13:59.861Z</t>
   </si>
   <si>
     <t>TC-0305</t>
@@ -6347,7 +6347,7 @@
     <t>Test Vector: ACCE_020, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:12:44.784Z</t>
+    <t>2026-08-31T05:36:45.152Z</t>
   </si>
   <si>
     <t>TC-0306</t>
@@ -6371,7 +6371,7 @@
     <t>Matched Expected: System satisfies all Data Encryption &amp; TLS Handshakes standards with zero regression.</t>
   </si>
   <si>
-    <t>2026-08-31T06:20:22.861Z</t>
+    <t>2026-08-31T06:13:45.903Z</t>
   </si>
   <si>
     <t>TC-0307</t>
@@ -6386,7 +6386,7 @@
     <t>Test Vector: DATA_02, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:09:17.399Z</t>
+    <t>2026-08-31T06:10:09.509Z</t>
   </si>
   <si>
     <t>TC-0308</t>
@@ -6401,7 +6401,7 @@
     <t>Test Vector: DATA_03, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:04:48.949Z</t>
+    <t>2026-08-31T05:54:20.015Z</t>
   </si>
   <si>
     <t>TC-0309</t>
@@ -6416,7 +6416,7 @@
     <t>Test Vector: DATA_04, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:25:46.229Z</t>
+    <t>2026-08-31T06:18:46.348Z</t>
   </si>
   <si>
     <t>TC-0310</t>
@@ -6431,7 +6431,7 @@
     <t>Test Vector: DATA_05, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:16:17.161Z</t>
+    <t>2026-08-31T05:29:16.646Z</t>
   </si>
   <si>
     <t>TC-0311</t>
@@ -6446,7 +6446,7 @@
     <t>Test Vector: DATA_06, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:47:40.340Z</t>
+    <t>2026-08-31T05:59:58.345Z</t>
   </si>
   <si>
     <t>TC-0312</t>
@@ -6461,7 +6461,7 @@
     <t>Test Vector: DATA_07, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:41:50.272Z</t>
+    <t>2026-08-31T05:26:34.730Z</t>
   </si>
   <si>
     <t>TC-0313</t>
@@ -6476,7 +6476,7 @@
     <t>Test Vector: DATA_08, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:10:49.553Z</t>
+    <t>2026-08-31T06:03:38.075Z</t>
   </si>
   <si>
     <t>TC-0314</t>
@@ -6491,7 +6491,7 @@
     <t>Test Vector: DATA_09, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:04:26.955Z</t>
+    <t>2026-08-31T05:53:05.308Z</t>
   </si>
   <si>
     <t>TC-0315</t>
@@ -6506,7 +6506,7 @@
     <t>Test Vector: DATA_010, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:02:54.075Z</t>
+    <t>2026-08-31T06:20:53.959Z</t>
   </si>
   <si>
     <t>TC-0316</t>
@@ -6521,7 +6521,7 @@
     <t>Test Vector: DATA_011, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:52:19.869Z</t>
+    <t>2026-08-31T05:31:13.514Z</t>
   </si>
   <si>
     <t>TC-0317</t>
@@ -6536,7 +6536,7 @@
     <t>Test Vector: DATA_012, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:03:38.111Z</t>
+    <t>2026-08-31T05:45:39.035Z</t>
   </si>
   <si>
     <t>TC-0318</t>
@@ -6551,7 +6551,7 @@
     <t>Test Vector: DATA_013, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:15:53.067Z</t>
+    <t>2026-08-31T05:42:43.186Z</t>
   </si>
   <si>
     <t>TC-0319</t>
@@ -6566,7 +6566,7 @@
     <t>Test Vector: DATA_014, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:44:33.731Z</t>
+    <t>2026-08-31T05:42:43.904Z</t>
   </si>
   <si>
     <t>TC-0320</t>
@@ -6581,7 +6581,7 @@
     <t>Test Vector: DATA_015, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:05:31.361Z</t>
+    <t>2026-08-31T05:35:50.183Z</t>
   </si>
   <si>
     <t>TC-0321</t>
@@ -6596,7 +6596,7 @@
     <t>Test Vector: DATA_016, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:38:37.422Z</t>
+    <t>2026-08-31T05:51:28.155Z</t>
   </si>
   <si>
     <t>TC-0322</t>
@@ -6611,7 +6611,7 @@
     <t>Test Vector: DATA_017, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:19:40.964Z</t>
+    <t>2026-08-31T06:03:37.178Z</t>
   </si>
   <si>
     <t>TC-0323</t>
@@ -6626,7 +6626,7 @@
     <t>Test Vector: DATA_018, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:11:02.441Z</t>
+    <t>2026-08-31T05:50:57.608Z</t>
   </si>
   <si>
     <t>TC-0324</t>
@@ -6641,7 +6641,7 @@
     <t>Test Vector: DATA_019, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:34:08.286Z</t>
+    <t>2026-08-31T06:22:48.541Z</t>
   </si>
   <si>
     <t>TC-0325</t>
@@ -6656,7 +6656,7 @@
     <t>Test Vector: DATA_020, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:11:01.408Z</t>
+    <t>2026-08-31T05:54:12.646Z</t>
   </si>
   <si>
     <t>TC-0326</t>
@@ -6680,7 +6680,7 @@
     <t>Matched Expected: System satisfies all Capacitor Native Android Hardware Tests standards with zero regression.</t>
   </si>
   <si>
-    <t>2026-08-31T05:48:44.807Z</t>
+    <t>2026-08-31T06:18:16.484Z</t>
   </si>
   <si>
     <t>TC-0327</t>
@@ -6695,7 +6695,7 @@
     <t>Test Vector: CAPA_02, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:48:50.622Z</t>
+    <t>2026-08-31T05:36:16.465Z</t>
   </si>
   <si>
     <t>TC-0328</t>
@@ -6710,7 +6710,7 @@
     <t>Test Vector: CAPA_03, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:18:40.978Z</t>
+    <t>2026-08-31T05:30:33.026Z</t>
   </si>
   <si>
     <t>TC-0329</t>
@@ -6725,7 +6725,7 @@
     <t>Test Vector: CAPA_04, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:43:23.024Z</t>
+    <t>2026-08-31T05:53:09.594Z</t>
   </si>
   <si>
     <t>TC-0330</t>
@@ -6740,7 +6740,7 @@
     <t>Test Vector: CAPA_05, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:30:21.485Z</t>
+    <t>2026-08-31T05:32:46.886Z</t>
   </si>
   <si>
     <t>TC-0331</t>
@@ -6755,7 +6755,7 @@
     <t>Test Vector: CAPA_06, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:38:00.241Z</t>
+    <t>2026-08-31T05:53:35.488Z</t>
   </si>
   <si>
     <t>TC-0332</t>
@@ -6770,7 +6770,7 @@
     <t>Test Vector: CAPA_07, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:59:06.831Z</t>
+    <t>2026-08-31T05:25:04.887Z</t>
   </si>
   <si>
     <t>TC-0333</t>
@@ -6785,7 +6785,7 @@
     <t>Test Vector: CAPA_08, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:31:28.149Z</t>
+    <t>2026-08-31T05:25:00.569Z</t>
   </si>
   <si>
     <t>TC-0334</t>
@@ -6800,7 +6800,7 @@
     <t>Test Vector: CAPA_09, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:24:12.687Z</t>
+    <t>2026-08-31T05:36:54.329Z</t>
   </si>
   <si>
     <t>TC-0335</t>
@@ -6815,7 +6815,7 @@
     <t>Test Vector: CAPA_010, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:11:06.195Z</t>
+    <t>2026-08-31T05:54:16.285Z</t>
   </si>
   <si>
     <t>TC-0336</t>
@@ -6830,7 +6830,7 @@
     <t>Test Vector: CAPA_011, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:16:46.905Z</t>
+    <t>2026-08-31T05:50:25.460Z</t>
   </si>
   <si>
     <t>TC-0337</t>
@@ -6845,7 +6845,7 @@
     <t>Test Vector: CAPA_012, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:27:30.310Z</t>
+    <t>2026-08-31T06:02:46.315Z</t>
   </si>
   <si>
     <t>TC-0338</t>
@@ -6860,7 +6860,7 @@
     <t>Test Vector: CAPA_013, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:25:54.416Z</t>
+    <t>2026-08-31T05:44:47.763Z</t>
   </si>
   <si>
     <t>TC-0339</t>
@@ -6875,7 +6875,7 @@
     <t>Test Vector: CAPA_014, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:05:01.256Z</t>
+    <t>2026-08-31T05:46:13.120Z</t>
   </si>
   <si>
     <t>TC-0340</t>
@@ -6890,7 +6890,7 @@
     <t>Test Vector: CAPA_015, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:31:34.813Z</t>
+    <t>2026-08-31T06:16:44.753Z</t>
   </si>
   <si>
     <t>TC-0341</t>
@@ -6905,7 +6905,7 @@
     <t>Test Vector: CAPA_016, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:29:11.914Z</t>
+    <t>2026-08-31T05:57:51.387Z</t>
   </si>
   <si>
     <t>TC-0342</t>
@@ -6920,7 +6920,7 @@
     <t>Test Vector: CAPA_017, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:09:07.215Z</t>
+    <t>2026-08-31T06:22:33.803Z</t>
   </si>
   <si>
     <t>TC-0343</t>
@@ -6935,7 +6935,7 @@
     <t>Test Vector: CAPA_018, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:16:03.725Z</t>
+    <t>2026-08-31T05:51:24.933Z</t>
   </si>
   <si>
     <t>TC-0344</t>
@@ -6950,7 +6950,7 @@
     <t>Test Vector: CAPA_019, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:18:15.883Z</t>
+    <t>2026-08-31T05:43:23.452Z</t>
   </si>
   <si>
     <t>TC-0345</t>
@@ -6965,7 +6965,7 @@
     <t>Test Vector: CAPA_020, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:10:21.066Z</t>
+    <t>2026-08-31T05:44:21.670Z</t>
   </si>
   <si>
     <t>TC-0346</t>
@@ -6989,7 +6989,7 @@
     <t>Matched Expected: System satisfies all Offline Network Resilience &amp; Reconnection standards with zero regression.</t>
   </si>
   <si>
-    <t>2026-08-31T05:59:16.635Z</t>
+    <t>2026-08-31T05:28:40.591Z</t>
   </si>
   <si>
     <t>TC-0347</t>
@@ -7004,7 +7004,7 @@
     <t>Test Vector: OFFL_02, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:19:31.502Z</t>
+    <t>2026-08-31T06:10:37.221Z</t>
   </si>
   <si>
     <t>TC-0348</t>
@@ -7019,7 +7019,7 @@
     <t>Test Vector: OFFL_03, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:35:49.035Z</t>
+    <t>2026-08-31T06:23:45.435Z</t>
   </si>
   <si>
     <t>TC-0349</t>
@@ -7034,7 +7034,7 @@
     <t>Test Vector: OFFL_04, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:57:08.616Z</t>
+    <t>2026-08-31T05:50:03.943Z</t>
   </si>
   <si>
     <t>TC-0350</t>
@@ -7049,7 +7049,7 @@
     <t>Test Vector: OFFL_05, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:52:11.995Z</t>
+    <t>2026-08-31T05:41:51.521Z</t>
   </si>
   <si>
     <t>TC-0351</t>
@@ -7064,7 +7064,7 @@
     <t>Test Vector: OFFL_06, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:25:10.283Z</t>
+    <t>2026-08-31T05:29:40.348Z</t>
   </si>
   <si>
     <t>TC-0352</t>
@@ -7079,7 +7079,7 @@
     <t>Test Vector: OFFL_07, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:48:41.240Z</t>
+    <t>2026-08-31T05:42:20.990Z</t>
   </si>
   <si>
     <t>TC-0353</t>
@@ -7094,7 +7094,7 @@
     <t>Test Vector: OFFL_08, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:37:24.353Z</t>
+    <t>2026-08-31T06:21:55.068Z</t>
   </si>
   <si>
     <t>TC-0354</t>
@@ -7109,7 +7109,7 @@
     <t>Test Vector: OFFL_09, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:10:28.987Z</t>
+    <t>2026-08-31T05:54:41.760Z</t>
   </si>
   <si>
     <t>TC-0355</t>
@@ -7124,7 +7124,7 @@
     <t>Test Vector: OFFL_010, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:08:32.205Z</t>
+    <t>2026-08-31T05:26:37.204Z</t>
   </si>
   <si>
     <t>TC-0356</t>
@@ -7139,7 +7139,7 @@
     <t>Test Vector: OFFL_011, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:33:28.017Z</t>
+    <t>2026-08-31T06:07:16.623Z</t>
   </si>
   <si>
     <t>TC-0357</t>
@@ -7154,7 +7154,7 @@
     <t>Test Vector: OFFL_012, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:35:35.220Z</t>
+    <t>2026-08-31T06:13:04.604Z</t>
   </si>
   <si>
     <t>TC-0358</t>
@@ -7169,7 +7169,7 @@
     <t>Test Vector: OFFL_013, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:38:39.101Z</t>
+    <t>2026-08-31T05:28:13.699Z</t>
   </si>
   <si>
     <t>TC-0359</t>
@@ -7184,7 +7184,7 @@
     <t>Test Vector: OFFL_014, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:00:33.071Z</t>
+    <t>2026-08-31T06:18:03.948Z</t>
   </si>
   <si>
     <t>TC-0360</t>
@@ -7199,7 +7199,7 @@
     <t>Test Vector: OFFL_015, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:35:53.605Z</t>
+    <t>2026-08-31T06:03:35.939Z</t>
   </si>
   <si>
     <t>TC-0361</t>
@@ -7214,7 +7214,7 @@
     <t>Test Vector: OFFL_016, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:44:34.587Z</t>
+    <t>2026-08-31T05:56:22.945Z</t>
   </si>
   <si>
     <t>TC-0362</t>
@@ -7229,7 +7229,7 @@
     <t>Test Vector: OFFL_017, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:00:03.414Z</t>
+    <t>2026-08-31T05:42:50.289Z</t>
   </si>
   <si>
     <t>TC-0363</t>
@@ -7244,7 +7244,7 @@
     <t>Test Vector: OFFL_018, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:24:49.327Z</t>
+    <t>2026-08-31T05:53:06.055Z</t>
   </si>
   <si>
     <t>TC-0364</t>
@@ -7259,7 +7259,7 @@
     <t>Test Vector: OFFL_019, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:43:31.521Z</t>
+    <t>2026-08-31T05:26:27.577Z</t>
   </si>
   <si>
     <t>TC-0365</t>
@@ -7274,7 +7274,7 @@
     <t>Test Vector: OFFL_020, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:10:34.683Z</t>
+    <t>2026-08-31T06:10:53.800Z</t>
   </si>
 </sst>
 </file>
@@ -8055,7 +8055,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="13">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="K2" s="14" t="s">
         <v>42</v>
@@ -8093,7 +8093,7 @@
         <v>41</v>
       </c>
       <c r="J3" s="16">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K3" s="17" t="s">
         <v>42</v>
@@ -8131,7 +8131,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="13">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="K4" s="14" t="s">
         <v>42</v>
@@ -8169,7 +8169,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="16">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="K5" s="17" t="s">
         <v>42</v>
@@ -8245,7 +8245,7 @@
         <v>78</v>
       </c>
       <c r="J7" s="16">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="K7" s="17" t="s">
         <v>42</v>
@@ -8283,7 +8283,7 @@
         <v>78</v>
       </c>
       <c r="J8" s="13">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="K8" s="14" t="s">
         <v>42</v>
@@ -8321,7 +8321,7 @@
         <v>78</v>
       </c>
       <c r="J9" s="16">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="K9" s="17" t="s">
         <v>42</v>
@@ -8359,7 +8359,7 @@
         <v>78</v>
       </c>
       <c r="J10" s="13">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="K10" s="14" t="s">
         <v>42</v>
@@ -8397,7 +8397,7 @@
         <v>78</v>
       </c>
       <c r="J11" s="16">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K11" s="17" t="s">
         <v>42</v>
@@ -8435,7 +8435,7 @@
         <v>78</v>
       </c>
       <c r="J12" s="13">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K12" s="14" t="s">
         <v>42</v>
@@ -8473,7 +8473,7 @@
         <v>78</v>
       </c>
       <c r="J13" s="16">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="K13" s="17" t="s">
         <v>42</v>
@@ -8511,7 +8511,7 @@
         <v>128</v>
       </c>
       <c r="J14" s="13">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K14" s="14" t="s">
         <v>42</v>
@@ -8549,7 +8549,7 @@
         <v>128</v>
       </c>
       <c r="J15" s="16">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K15" s="17" t="s">
         <v>42</v>
@@ -8587,7 +8587,7 @@
         <v>128</v>
       </c>
       <c r="J16" s="13">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K16" s="14" t="s">
         <v>42</v>
@@ -8625,7 +8625,7 @@
         <v>128</v>
       </c>
       <c r="J17" s="16">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K17" s="17" t="s">
         <v>42</v>
@@ -8663,7 +8663,7 @@
         <v>128</v>
       </c>
       <c r="J18" s="13">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="K18" s="14" t="s">
         <v>42</v>
@@ -8701,7 +8701,7 @@
         <v>128</v>
       </c>
       <c r="J19" s="16">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="K19" s="17" t="s">
         <v>42</v>
@@ -8739,7 +8739,7 @@
         <v>171</v>
       </c>
       <c r="J20" s="13">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K20" s="14" t="s">
         <v>42</v>
@@ -8777,7 +8777,7 @@
         <v>171</v>
       </c>
       <c r="J21" s="16">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="K21" s="17" t="s">
         <v>42</v>
@@ -8815,7 +8815,7 @@
         <v>171</v>
       </c>
       <c r="J22" s="13">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="K22" s="14" t="s">
         <v>42</v>
@@ -8853,7 +8853,7 @@
         <v>171</v>
       </c>
       <c r="J23" s="16">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="K23" s="17" t="s">
         <v>42</v>
@@ -8891,7 +8891,7 @@
         <v>171</v>
       </c>
       <c r="J24" s="13">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="K24" s="14" t="s">
         <v>42</v>
@@ -8929,7 +8929,7 @@
         <v>171</v>
       </c>
       <c r="J25" s="16">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K25" s="17" t="s">
         <v>42</v>
@@ -8967,7 +8967,7 @@
         <v>171</v>
       </c>
       <c r="J26" s="13">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K26" s="14" t="s">
         <v>42</v>
@@ -9005,7 +9005,7 @@
         <v>41</v>
       </c>
       <c r="J27" s="16">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="K27" s="17" t="s">
         <v>42</v>
@@ -9043,7 +9043,7 @@
         <v>41</v>
       </c>
       <c r="J28" s="13">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="K28" s="14" t="s">
         <v>42</v>
@@ -9081,7 +9081,7 @@
         <v>41</v>
       </c>
       <c r="J29" s="16">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="K29" s="17" t="s">
         <v>42</v>
@@ -9119,7 +9119,7 @@
         <v>41</v>
       </c>
       <c r="J30" s="13">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K30" s="14" t="s">
         <v>42</v>
@@ -9157,7 +9157,7 @@
         <v>41</v>
       </c>
       <c r="J31" s="16">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="K31" s="17" t="s">
         <v>42</v>
@@ -9195,7 +9195,7 @@
         <v>78</v>
       </c>
       <c r="J32" s="13">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K32" s="14" t="s">
         <v>42</v>
@@ -9233,7 +9233,7 @@
         <v>78</v>
       </c>
       <c r="J33" s="16">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="K33" s="17" t="s">
         <v>42</v>
@@ -9271,7 +9271,7 @@
         <v>78</v>
       </c>
       <c r="J34" s="13">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="K34" s="14" t="s">
         <v>42</v>
@@ -9309,7 +9309,7 @@
         <v>78</v>
       </c>
       <c r="J35" s="16">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K35" s="17" t="s">
         <v>42</v>
@@ -9347,7 +9347,7 @@
         <v>78</v>
       </c>
       <c r="J36" s="13">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="K36" s="14" t="s">
         <v>42</v>
@@ -9385,7 +9385,7 @@
         <v>78</v>
       </c>
       <c r="J37" s="16">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K37" s="17" t="s">
         <v>42</v>
@@ -9423,7 +9423,7 @@
         <v>78</v>
       </c>
       <c r="J38" s="13">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K38" s="14" t="s">
         <v>42</v>
@@ -9461,7 +9461,7 @@
         <v>128</v>
       </c>
       <c r="J39" s="16">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="K39" s="17" t="s">
         <v>42</v>
@@ -9499,7 +9499,7 @@
         <v>128</v>
       </c>
       <c r="J40" s="13">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K40" s="14" t="s">
         <v>42</v>
@@ -9537,7 +9537,7 @@
         <v>128</v>
       </c>
       <c r="J41" s="16">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="K41" s="17" t="s">
         <v>42</v>
@@ -9575,7 +9575,7 @@
         <v>128</v>
       </c>
       <c r="J42" s="13">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K42" s="14" t="s">
         <v>42</v>
@@ -9613,7 +9613,7 @@
         <v>128</v>
       </c>
       <c r="J43" s="16">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="K43" s="17" t="s">
         <v>42</v>
@@ -9651,7 +9651,7 @@
         <v>128</v>
       </c>
       <c r="J44" s="13">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K44" s="14" t="s">
         <v>42</v>
@@ -9689,7 +9689,7 @@
         <v>171</v>
       </c>
       <c r="J45" s="16">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="K45" s="17" t="s">
         <v>42</v>
@@ -9727,7 +9727,7 @@
         <v>171</v>
       </c>
       <c r="J46" s="13">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="K46" s="14" t="s">
         <v>42</v>
@@ -9765,7 +9765,7 @@
         <v>171</v>
       </c>
       <c r="J47" s="16">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K47" s="17" t="s">
         <v>42</v>
@@ -9803,7 +9803,7 @@
         <v>171</v>
       </c>
       <c r="J48" s="13">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="K48" s="14" t="s">
         <v>42</v>
@@ -9841,7 +9841,7 @@
         <v>171</v>
       </c>
       <c r="J49" s="16">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="K49" s="17" t="s">
         <v>42</v>
@@ -9879,7 +9879,7 @@
         <v>171</v>
       </c>
       <c r="J50" s="13">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="K50" s="14" t="s">
         <v>42</v>
@@ -9917,7 +9917,7 @@
         <v>171</v>
       </c>
       <c r="J51" s="16">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="K51" s="17" t="s">
         <v>42</v>
@@ -9955,7 +9955,7 @@
         <v>41</v>
       </c>
       <c r="J52" s="13">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="K52" s="14" t="s">
         <v>42</v>
@@ -9993,7 +9993,7 @@
         <v>41</v>
       </c>
       <c r="J53" s="16">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K53" s="17" t="s">
         <v>42</v>
@@ -10031,7 +10031,7 @@
         <v>41</v>
       </c>
       <c r="J54" s="13">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K54" s="14" t="s">
         <v>42</v>
@@ -10069,7 +10069,7 @@
         <v>41</v>
       </c>
       <c r="J55" s="16">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K55" s="17" t="s">
         <v>42</v>
@@ -10107,7 +10107,7 @@
         <v>41</v>
       </c>
       <c r="J56" s="13">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="K56" s="14" t="s">
         <v>42</v>
@@ -10145,7 +10145,7 @@
         <v>78</v>
       </c>
       <c r="J57" s="16">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="K57" s="17" t="s">
         <v>42</v>
@@ -10183,7 +10183,7 @@
         <v>78</v>
       </c>
       <c r="J58" s="13">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="K58" s="14" t="s">
         <v>42</v>
@@ -10221,7 +10221,7 @@
         <v>78</v>
       </c>
       <c r="J59" s="16">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K59" s="17" t="s">
         <v>42</v>
@@ -10259,7 +10259,7 @@
         <v>78</v>
       </c>
       <c r="J60" s="13">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K60" s="14" t="s">
         <v>42</v>
@@ -10335,7 +10335,7 @@
         <v>78</v>
       </c>
       <c r="J62" s="13">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K62" s="14" t="s">
         <v>42</v>
@@ -10373,7 +10373,7 @@
         <v>78</v>
       </c>
       <c r="J63" s="16">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="K63" s="17" t="s">
         <v>42</v>
@@ -10411,7 +10411,7 @@
         <v>128</v>
       </c>
       <c r="J64" s="13">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="K64" s="14" t="s">
         <v>42</v>
@@ -10449,7 +10449,7 @@
         <v>128</v>
       </c>
       <c r="J65" s="16">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="K65" s="17" t="s">
         <v>42</v>
@@ -10487,7 +10487,7 @@
         <v>128</v>
       </c>
       <c r="J66" s="13">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K66" s="14" t="s">
         <v>42</v>
@@ -10525,7 +10525,7 @@
         <v>128</v>
       </c>
       <c r="J67" s="16">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="K67" s="17" t="s">
         <v>42</v>
@@ -10563,7 +10563,7 @@
         <v>128</v>
       </c>
       <c r="J68" s="13">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K68" s="14" t="s">
         <v>42</v>
@@ -10601,7 +10601,7 @@
         <v>128</v>
       </c>
       <c r="J69" s="16">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K69" s="17" t="s">
         <v>42</v>
@@ -10639,7 +10639,7 @@
         <v>171</v>
       </c>
       <c r="J70" s="13">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="K70" s="14" t="s">
         <v>42</v>
@@ -10677,7 +10677,7 @@
         <v>171</v>
       </c>
       <c r="J71" s="16">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="K71" s="17" t="s">
         <v>42</v>
@@ -10715,7 +10715,7 @@
         <v>171</v>
       </c>
       <c r="J72" s="13">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K72" s="14" t="s">
         <v>42</v>
@@ -10753,7 +10753,7 @@
         <v>171</v>
       </c>
       <c r="J73" s="16">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K73" s="17" t="s">
         <v>42</v>
@@ -10829,7 +10829,7 @@
         <v>171</v>
       </c>
       <c r="J75" s="16">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="K75" s="17" t="s">
         <v>42</v>
@@ -10905,7 +10905,7 @@
         <v>41</v>
       </c>
       <c r="J77" s="16">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="K77" s="17" t="s">
         <v>42</v>
@@ -10943,7 +10943,7 @@
         <v>41</v>
       </c>
       <c r="J78" s="13">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K78" s="14" t="s">
         <v>42</v>
@@ -10981,7 +10981,7 @@
         <v>41</v>
       </c>
       <c r="J79" s="16">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K79" s="17" t="s">
         <v>42</v>
@@ -11019,7 +11019,7 @@
         <v>41</v>
       </c>
       <c r="J80" s="13">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="K80" s="14" t="s">
         <v>42</v>
@@ -11057,7 +11057,7 @@
         <v>41</v>
       </c>
       <c r="J81" s="16">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K81" s="17" t="s">
         <v>42</v>
@@ -11095,7 +11095,7 @@
         <v>78</v>
       </c>
       <c r="J82" s="13">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="K82" s="14" t="s">
         <v>42</v>
@@ -11133,7 +11133,7 @@
         <v>78</v>
       </c>
       <c r="J83" s="16">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K83" s="17" t="s">
         <v>42</v>
@@ -11171,7 +11171,7 @@
         <v>78</v>
       </c>
       <c r="J84" s="13">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K84" s="14" t="s">
         <v>42</v>
@@ -11209,7 +11209,7 @@
         <v>78</v>
       </c>
       <c r="J85" s="16">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="K85" s="17" t="s">
         <v>42</v>
@@ -11247,7 +11247,7 @@
         <v>78</v>
       </c>
       <c r="J86" s="13">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K86" s="14" t="s">
         <v>42</v>
@@ -11285,7 +11285,7 @@
         <v>78</v>
       </c>
       <c r="J87" s="16">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="K87" s="17" t="s">
         <v>42</v>
@@ -11323,7 +11323,7 @@
         <v>78</v>
       </c>
       <c r="J88" s="13">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="K88" s="14" t="s">
         <v>42</v>
@@ -11361,7 +11361,7 @@
         <v>128</v>
       </c>
       <c r="J89" s="16">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="K89" s="17" t="s">
         <v>42</v>
@@ -11399,7 +11399,7 @@
         <v>128</v>
       </c>
       <c r="J90" s="13">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="K90" s="14" t="s">
         <v>42</v>
@@ -11437,7 +11437,7 @@
         <v>128</v>
       </c>
       <c r="J91" s="16">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="K91" s="17" t="s">
         <v>42</v>
@@ -11475,7 +11475,7 @@
         <v>128</v>
       </c>
       <c r="J92" s="13">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="K92" s="14" t="s">
         <v>42</v>
@@ -11513,7 +11513,7 @@
         <v>128</v>
       </c>
       <c r="J93" s="16">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="K93" s="17" t="s">
         <v>42</v>
@@ -11551,7 +11551,7 @@
         <v>128</v>
       </c>
       <c r="J94" s="13">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="K94" s="14" t="s">
         <v>42</v>
@@ -11589,7 +11589,7 @@
         <v>171</v>
       </c>
       <c r="J95" s="16">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="K95" s="17" t="s">
         <v>42</v>
@@ -11627,7 +11627,7 @@
         <v>171</v>
       </c>
       <c r="J96" s="13">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="K96" s="14" t="s">
         <v>42</v>
@@ -11665,7 +11665,7 @@
         <v>171</v>
       </c>
       <c r="J97" s="16">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="K97" s="17" t="s">
         <v>42</v>
@@ -11703,7 +11703,7 @@
         <v>171</v>
       </c>
       <c r="J98" s="13">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="K98" s="14" t="s">
         <v>42</v>
@@ -11741,7 +11741,7 @@
         <v>171</v>
       </c>
       <c r="J99" s="16">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K99" s="17" t="s">
         <v>42</v>
@@ -11779,7 +11779,7 @@
         <v>171</v>
       </c>
       <c r="J100" s="13">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K100" s="14" t="s">
         <v>42</v>
@@ -11817,7 +11817,7 @@
         <v>171</v>
       </c>
       <c r="J101" s="16">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="K101" s="17" t="s">
         <v>42</v>
@@ -11855,7 +11855,7 @@
         <v>41</v>
       </c>
       <c r="J102" s="13">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="K102" s="14" t="s">
         <v>42</v>
@@ -11893,7 +11893,7 @@
         <v>41</v>
       </c>
       <c r="J103" s="16">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="K103" s="17" t="s">
         <v>42</v>
@@ -11931,7 +11931,7 @@
         <v>41</v>
       </c>
       <c r="J104" s="13">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K104" s="14" t="s">
         <v>42</v>
@@ -11969,7 +11969,7 @@
         <v>41</v>
       </c>
       <c r="J105" s="16">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K105" s="17" t="s">
         <v>42</v>
@@ -12007,7 +12007,7 @@
         <v>41</v>
       </c>
       <c r="J106" s="13">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="K106" s="14" t="s">
         <v>42</v>
@@ -12045,7 +12045,7 @@
         <v>78</v>
       </c>
       <c r="J107" s="16">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K107" s="17" t="s">
         <v>42</v>
@@ -12083,7 +12083,7 @@
         <v>78</v>
       </c>
       <c r="J108" s="13">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="K108" s="14" t="s">
         <v>42</v>
@@ -12121,7 +12121,7 @@
         <v>78</v>
       </c>
       <c r="J109" s="16">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K109" s="17" t="s">
         <v>42</v>
@@ -12159,7 +12159,7 @@
         <v>78</v>
       </c>
       <c r="J110" s="13">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K110" s="14" t="s">
         <v>42</v>
@@ -12197,7 +12197,7 @@
         <v>78</v>
       </c>
       <c r="J111" s="16">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="K111" s="17" t="s">
         <v>42</v>
@@ -12235,7 +12235,7 @@
         <v>78</v>
       </c>
       <c r="J112" s="13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K112" s="14" t="s">
         <v>42</v>
@@ -12273,7 +12273,7 @@
         <v>78</v>
       </c>
       <c r="J113" s="16">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K113" s="17" t="s">
         <v>42</v>
@@ -12311,7 +12311,7 @@
         <v>128</v>
       </c>
       <c r="J114" s="13">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K114" s="14" t="s">
         <v>42</v>
@@ -12349,7 +12349,7 @@
         <v>128</v>
       </c>
       <c r="J115" s="16">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="K115" s="17" t="s">
         <v>42</v>
@@ -12387,7 +12387,7 @@
         <v>128</v>
       </c>
       <c r="J116" s="13">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="K116" s="14" t="s">
         <v>42</v>
@@ -12425,7 +12425,7 @@
         <v>128</v>
       </c>
       <c r="J117" s="16">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="K117" s="17" t="s">
         <v>42</v>
@@ -12463,7 +12463,7 @@
         <v>128</v>
       </c>
       <c r="J118" s="13">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="K118" s="14" t="s">
         <v>42</v>
@@ -12501,7 +12501,7 @@
         <v>128</v>
       </c>
       <c r="J119" s="16">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="K119" s="17" t="s">
         <v>42</v>
@@ -12539,7 +12539,7 @@
         <v>171</v>
       </c>
       <c r="J120" s="13">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="K120" s="14" t="s">
         <v>42</v>
@@ -12577,7 +12577,7 @@
         <v>171</v>
       </c>
       <c r="J121" s="16">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K121" s="17" t="s">
         <v>42</v>
@@ -12615,7 +12615,7 @@
         <v>171</v>
       </c>
       <c r="J122" s="13">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="K122" s="14" t="s">
         <v>42</v>
@@ -12653,7 +12653,7 @@
         <v>171</v>
       </c>
       <c r="J123" s="16">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K123" s="17" t="s">
         <v>42</v>
@@ -12691,7 +12691,7 @@
         <v>171</v>
       </c>
       <c r="J124" s="13">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="K124" s="14" t="s">
         <v>42</v>
@@ -12729,7 +12729,7 @@
         <v>171</v>
       </c>
       <c r="J125" s="16">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="K125" s="17" t="s">
         <v>42</v>
@@ -12767,7 +12767,7 @@
         <v>171</v>
       </c>
       <c r="J126" s="13">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K126" s="14" t="s">
         <v>42</v>
@@ -12805,7 +12805,7 @@
         <v>41</v>
       </c>
       <c r="J127" s="16">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="K127" s="17" t="s">
         <v>42</v>
@@ -12843,7 +12843,7 @@
         <v>41</v>
       </c>
       <c r="J128" s="13">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="K128" s="14" t="s">
         <v>42</v>
@@ -12881,7 +12881,7 @@
         <v>41</v>
       </c>
       <c r="J129" s="16">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="K129" s="17" t="s">
         <v>42</v>
@@ -12919,7 +12919,7 @@
         <v>41</v>
       </c>
       <c r="J130" s="13">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="K130" s="14" t="s">
         <v>42</v>
@@ -12957,7 +12957,7 @@
         <v>41</v>
       </c>
       <c r="J131" s="16">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="K131" s="17" t="s">
         <v>42</v>
@@ -12995,7 +12995,7 @@
         <v>78</v>
       </c>
       <c r="J132" s="13">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="K132" s="14" t="s">
         <v>42</v>
@@ -13033,7 +13033,7 @@
         <v>78</v>
       </c>
       <c r="J133" s="16">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="K133" s="17" t="s">
         <v>42</v>
@@ -13071,7 +13071,7 @@
         <v>78</v>
       </c>
       <c r="J134" s="13">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K134" s="14" t="s">
         <v>42</v>
@@ -13109,7 +13109,7 @@
         <v>78</v>
       </c>
       <c r="J135" s="16">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="K135" s="17" t="s">
         <v>42</v>
@@ -13147,7 +13147,7 @@
         <v>78</v>
       </c>
       <c r="J136" s="13">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="K136" s="14" t="s">
         <v>42</v>
@@ -13185,7 +13185,7 @@
         <v>78</v>
       </c>
       <c r="J137" s="16">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K137" s="17" t="s">
         <v>42</v>
@@ -13223,7 +13223,7 @@
         <v>78</v>
       </c>
       <c r="J138" s="13">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="K138" s="14" t="s">
         <v>42</v>
@@ -13261,7 +13261,7 @@
         <v>128</v>
       </c>
       <c r="J139" s="16">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K139" s="17" t="s">
         <v>42</v>
@@ -13299,7 +13299,7 @@
         <v>128</v>
       </c>
       <c r="J140" s="13">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="K140" s="14" t="s">
         <v>42</v>
@@ -13337,7 +13337,7 @@
         <v>128</v>
       </c>
       <c r="J141" s="16">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="K141" s="17" t="s">
         <v>42</v>
@@ -13375,7 +13375,7 @@
         <v>128</v>
       </c>
       <c r="J142" s="13">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K142" s="14" t="s">
         <v>42</v>
@@ -13413,7 +13413,7 @@
         <v>128</v>
       </c>
       <c r="J143" s="16">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K143" s="17" t="s">
         <v>42</v>
@@ -13451,7 +13451,7 @@
         <v>128</v>
       </c>
       <c r="J144" s="13">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K144" s="14" t="s">
         <v>42</v>
@@ -13489,7 +13489,7 @@
         <v>171</v>
       </c>
       <c r="J145" s="16">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K145" s="17" t="s">
         <v>42</v>
@@ -13527,7 +13527,7 @@
         <v>171</v>
       </c>
       <c r="J146" s="13">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="K146" s="14" t="s">
         <v>42</v>
@@ -13565,7 +13565,7 @@
         <v>171</v>
       </c>
       <c r="J147" s="16">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="K147" s="17" t="s">
         <v>42</v>
@@ -13603,7 +13603,7 @@
         <v>171</v>
       </c>
       <c r="J148" s="13">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="K148" s="14" t="s">
         <v>42</v>
@@ -13641,7 +13641,7 @@
         <v>171</v>
       </c>
       <c r="J149" s="16">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K149" s="17" t="s">
         <v>42</v>
@@ -13679,7 +13679,7 @@
         <v>171</v>
       </c>
       <c r="J150" s="13">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="K150" s="14" t="s">
         <v>42</v>
@@ -13717,7 +13717,7 @@
         <v>171</v>
       </c>
       <c r="J151" s="16">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K151" s="17" t="s">
         <v>42</v>
@@ -13755,7 +13755,7 @@
         <v>41</v>
       </c>
       <c r="J152" s="13">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K152" s="14" t="s">
         <v>42</v>
@@ -13793,7 +13793,7 @@
         <v>41</v>
       </c>
       <c r="J153" s="16">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K153" s="17" t="s">
         <v>42</v>
@@ -13831,7 +13831,7 @@
         <v>41</v>
       </c>
       <c r="J154" s="13">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="K154" s="14" t="s">
         <v>42</v>
@@ -13869,7 +13869,7 @@
         <v>41</v>
       </c>
       <c r="J155" s="16">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="K155" s="17" t="s">
         <v>42</v>
@@ -13907,7 +13907,7 @@
         <v>41</v>
       </c>
       <c r="J156" s="13">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K156" s="14" t="s">
         <v>42</v>
@@ -13945,7 +13945,7 @@
         <v>78</v>
       </c>
       <c r="J157" s="16">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="K157" s="17" t="s">
         <v>42</v>
@@ -13983,7 +13983,7 @@
         <v>78</v>
       </c>
       <c r="J158" s="13">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="K158" s="14" t="s">
         <v>42</v>
@@ -14021,7 +14021,7 @@
         <v>78</v>
       </c>
       <c r="J159" s="16">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="K159" s="17" t="s">
         <v>42</v>
@@ -14059,7 +14059,7 @@
         <v>78</v>
       </c>
       <c r="J160" s="13">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="K160" s="14" t="s">
         <v>42</v>
@@ -14097,7 +14097,7 @@
         <v>78</v>
       </c>
       <c r="J161" s="16">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K161" s="17" t="s">
         <v>42</v>
@@ -14135,7 +14135,7 @@
         <v>78</v>
       </c>
       <c r="J162" s="13">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K162" s="14" t="s">
         <v>42</v>
@@ -14173,7 +14173,7 @@
         <v>78</v>
       </c>
       <c r="J163" s="16">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="K163" s="17" t="s">
         <v>42</v>
@@ -14249,7 +14249,7 @@
         <v>128</v>
       </c>
       <c r="J165" s="16">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="K165" s="17" t="s">
         <v>42</v>
@@ -14287,7 +14287,7 @@
         <v>128</v>
       </c>
       <c r="J166" s="13">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="K166" s="14" t="s">
         <v>42</v>
@@ -14325,7 +14325,7 @@
         <v>128</v>
       </c>
       <c r="J167" s="16">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="K167" s="17" t="s">
         <v>42</v>
@@ -14363,7 +14363,7 @@
         <v>128</v>
       </c>
       <c r="J168" s="13">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="K168" s="14" t="s">
         <v>42</v>
@@ -14401,7 +14401,7 @@
         <v>128</v>
       </c>
       <c r="J169" s="16">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="K169" s="17" t="s">
         <v>42</v>
@@ -14477,7 +14477,7 @@
         <v>171</v>
       </c>
       <c r="J171" s="16">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K171" s="17" t="s">
         <v>42</v>
@@ -14515,7 +14515,7 @@
         <v>41</v>
       </c>
       <c r="J172" s="13">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="K172" s="14" t="s">
         <v>42</v>
@@ -14553,7 +14553,7 @@
         <v>41</v>
       </c>
       <c r="J173" s="16">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="K173" s="17" t="s">
         <v>42</v>
@@ -14591,7 +14591,7 @@
         <v>41</v>
       </c>
       <c r="J174" s="13">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="K174" s="14" t="s">
         <v>42</v>
@@ -14629,7 +14629,7 @@
         <v>41</v>
       </c>
       <c r="J175" s="16">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="K175" s="17" t="s">
         <v>42</v>
@@ -14667,7 +14667,7 @@
         <v>41</v>
       </c>
       <c r="J176" s="13">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K176" s="14" t="s">
         <v>42</v>
@@ -14705,7 +14705,7 @@
         <v>78</v>
       </c>
       <c r="J177" s="16">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="K177" s="17" t="s">
         <v>42</v>
@@ -14743,7 +14743,7 @@
         <v>78</v>
       </c>
       <c r="J178" s="13">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K178" s="14" t="s">
         <v>42</v>
@@ -14781,7 +14781,7 @@
         <v>78</v>
       </c>
       <c r="J179" s="16">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="K179" s="17" t="s">
         <v>42</v>
@@ -14819,7 +14819,7 @@
         <v>78</v>
       </c>
       <c r="J180" s="13">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K180" s="14" t="s">
         <v>42</v>
@@ -14857,7 +14857,7 @@
         <v>78</v>
       </c>
       <c r="J181" s="16">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="K181" s="17" t="s">
         <v>42</v>
@@ -14895,7 +14895,7 @@
         <v>78</v>
       </c>
       <c r="J182" s="13">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="K182" s="14" t="s">
         <v>42</v>
@@ -14933,7 +14933,7 @@
         <v>78</v>
       </c>
       <c r="J183" s="16">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="K183" s="17" t="s">
         <v>42</v>
@@ -14971,7 +14971,7 @@
         <v>128</v>
       </c>
       <c r="J184" s="13">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="K184" s="14" t="s">
         <v>42</v>
@@ -15009,7 +15009,7 @@
         <v>128</v>
       </c>
       <c r="J185" s="16">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="K185" s="17" t="s">
         <v>42</v>
@@ -15047,7 +15047,7 @@
         <v>128</v>
       </c>
       <c r="J186" s="13">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="K186" s="14" t="s">
         <v>42</v>
@@ -15085,7 +15085,7 @@
         <v>128</v>
       </c>
       <c r="J187" s="16">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="K187" s="17" t="s">
         <v>42</v>
@@ -15123,7 +15123,7 @@
         <v>128</v>
       </c>
       <c r="J188" s="13">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="K188" s="14" t="s">
         <v>42</v>
@@ -15161,7 +15161,7 @@
         <v>128</v>
       </c>
       <c r="J189" s="16">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="K189" s="17" t="s">
         <v>42</v>
@@ -15199,7 +15199,7 @@
         <v>171</v>
       </c>
       <c r="J190" s="13">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K190" s="14" t="s">
         <v>42</v>
@@ -15237,7 +15237,7 @@
         <v>171</v>
       </c>
       <c r="J191" s="16">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="K191" s="17" t="s">
         <v>42</v>
@@ -15275,7 +15275,7 @@
         <v>41</v>
       </c>
       <c r="J192" s="13">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="K192" s="14" t="s">
         <v>42</v>
@@ -15351,7 +15351,7 @@
         <v>41</v>
       </c>
       <c r="J194" s="13">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="K194" s="14" t="s">
         <v>42</v>
@@ -15389,7 +15389,7 @@
         <v>41</v>
       </c>
       <c r="J195" s="16">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="K195" s="17" t="s">
         <v>42</v>
@@ -15427,7 +15427,7 @@
         <v>41</v>
       </c>
       <c r="J196" s="13">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K196" s="14" t="s">
         <v>42</v>
@@ -15465,7 +15465,7 @@
         <v>78</v>
       </c>
       <c r="J197" s="16">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K197" s="17" t="s">
         <v>42</v>
@@ -15503,7 +15503,7 @@
         <v>78</v>
       </c>
       <c r="J198" s="13">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K198" s="14" t="s">
         <v>42</v>
@@ -15579,7 +15579,7 @@
         <v>78</v>
       </c>
       <c r="J200" s="13">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="K200" s="14" t="s">
         <v>42</v>
@@ -15617,7 +15617,7 @@
         <v>78</v>
       </c>
       <c r="J201" s="16">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="K201" s="17" t="s">
         <v>42</v>
@@ -15655,7 +15655,7 @@
         <v>78</v>
       </c>
       <c r="J202" s="13">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="K202" s="14" t="s">
         <v>42</v>
@@ -15693,7 +15693,7 @@
         <v>78</v>
       </c>
       <c r="J203" s="16">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K203" s="17" t="s">
         <v>42</v>
@@ -15731,7 +15731,7 @@
         <v>128</v>
       </c>
       <c r="J204" s="13">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K204" s="14" t="s">
         <v>42</v>
@@ -15769,7 +15769,7 @@
         <v>128</v>
       </c>
       <c r="J205" s="16">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="K205" s="17" t="s">
         <v>42</v>
@@ -15807,7 +15807,7 @@
         <v>128</v>
       </c>
       <c r="J206" s="13">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K206" s="14" t="s">
         <v>42</v>
@@ -15845,7 +15845,7 @@
         <v>128</v>
       </c>
       <c r="J207" s="16">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="K207" s="17" t="s">
         <v>42</v>
@@ -15883,7 +15883,7 @@
         <v>128</v>
       </c>
       <c r="J208" s="13">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="K208" s="14" t="s">
         <v>42</v>
@@ -15921,7 +15921,7 @@
         <v>128</v>
       </c>
       <c r="J209" s="16">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="K209" s="17" t="s">
         <v>42</v>
@@ -15959,7 +15959,7 @@
         <v>171</v>
       </c>
       <c r="J210" s="13">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="K210" s="14" t="s">
         <v>42</v>
@@ -15997,7 +15997,7 @@
         <v>171</v>
       </c>
       <c r="J211" s="16">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="K211" s="17" t="s">
         <v>42</v>
@@ -16035,7 +16035,7 @@
         <v>41</v>
       </c>
       <c r="J212" s="13">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="K212" s="14" t="s">
         <v>42</v>
@@ -16073,7 +16073,7 @@
         <v>41</v>
       </c>
       <c r="J213" s="16">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K213" s="17" t="s">
         <v>42</v>
@@ -16111,7 +16111,7 @@
         <v>41</v>
       </c>
       <c r="J214" s="13">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K214" s="14" t="s">
         <v>42</v>
@@ -16149,7 +16149,7 @@
         <v>41</v>
       </c>
       <c r="J215" s="16">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K215" s="17" t="s">
         <v>42</v>
@@ -16187,7 +16187,7 @@
         <v>41</v>
       </c>
       <c r="J216" s="13">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="K216" s="14" t="s">
         <v>42</v>
@@ -16225,7 +16225,7 @@
         <v>78</v>
       </c>
       <c r="J217" s="16">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="K217" s="17" t="s">
         <v>42</v>
@@ -16263,7 +16263,7 @@
         <v>78</v>
       </c>
       <c r="J218" s="13">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="K218" s="14" t="s">
         <v>42</v>
@@ -16301,7 +16301,7 @@
         <v>78</v>
       </c>
       <c r="J219" s="16">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K219" s="17" t="s">
         <v>42</v>
@@ -16339,7 +16339,7 @@
         <v>78</v>
       </c>
       <c r="J220" s="13">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K220" s="14" t="s">
         <v>42</v>
@@ -16377,7 +16377,7 @@
         <v>78</v>
       </c>
       <c r="J221" s="16">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K221" s="17" t="s">
         <v>42</v>
@@ -16415,7 +16415,7 @@
         <v>78</v>
       </c>
       <c r="J222" s="13">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K222" s="14" t="s">
         <v>42</v>
@@ -16453,7 +16453,7 @@
         <v>78</v>
       </c>
       <c r="J223" s="16">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K223" s="17" t="s">
         <v>42</v>
@@ -16491,7 +16491,7 @@
         <v>128</v>
       </c>
       <c r="J224" s="13">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="K224" s="14" t="s">
         <v>42</v>
@@ -16529,7 +16529,7 @@
         <v>128</v>
       </c>
       <c r="J225" s="16">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="K225" s="17" t="s">
         <v>42</v>
@@ -16567,7 +16567,7 @@
         <v>128</v>
       </c>
       <c r="J226" s="13">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="K226" s="14" t="s">
         <v>42</v>
@@ -16605,7 +16605,7 @@
         <v>128</v>
       </c>
       <c r="J227" s="16">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="K227" s="17" t="s">
         <v>42</v>
@@ -16643,7 +16643,7 @@
         <v>128</v>
       </c>
       <c r="J228" s="13">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K228" s="14" t="s">
         <v>42</v>
@@ -16681,7 +16681,7 @@
         <v>128</v>
       </c>
       <c r="J229" s="16">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="K229" s="17" t="s">
         <v>42</v>
@@ -16719,7 +16719,7 @@
         <v>171</v>
       </c>
       <c r="J230" s="13">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="K230" s="14" t="s">
         <v>42</v>
@@ -16757,7 +16757,7 @@
         <v>171</v>
       </c>
       <c r="J231" s="16">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K231" s="17" t="s">
         <v>42</v>
@@ -16795,7 +16795,7 @@
         <v>41</v>
       </c>
       <c r="J232" s="13">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="K232" s="14" t="s">
         <v>42</v>
@@ -16833,7 +16833,7 @@
         <v>41</v>
       </c>
       <c r="J233" s="16">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="K233" s="17" t="s">
         <v>42</v>
@@ -16871,7 +16871,7 @@
         <v>41</v>
       </c>
       <c r="J234" s="13">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="K234" s="14" t="s">
         <v>42</v>
@@ -16909,7 +16909,7 @@
         <v>41</v>
       </c>
       <c r="J235" s="16">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="K235" s="17" t="s">
         <v>42</v>
@@ -16947,7 +16947,7 @@
         <v>41</v>
       </c>
       <c r="J236" s="13">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="K236" s="14" t="s">
         <v>42</v>
@@ -16985,7 +16985,7 @@
         <v>78</v>
       </c>
       <c r="J237" s="16">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K237" s="17" t="s">
         <v>42</v>
@@ -17023,7 +17023,7 @@
         <v>78</v>
       </c>
       <c r="J238" s="13">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K238" s="14" t="s">
         <v>42</v>
@@ -17061,7 +17061,7 @@
         <v>78</v>
       </c>
       <c r="J239" s="16">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="K239" s="17" t="s">
         <v>42</v>
@@ -17099,7 +17099,7 @@
         <v>78</v>
       </c>
       <c r="J240" s="13">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K240" s="14" t="s">
         <v>42</v>
@@ -17137,7 +17137,7 @@
         <v>78</v>
       </c>
       <c r="J241" s="16">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="K241" s="17" t="s">
         <v>42</v>
@@ -17175,7 +17175,7 @@
         <v>78</v>
       </c>
       <c r="J242" s="13">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="K242" s="14" t="s">
         <v>42</v>
@@ -17213,7 +17213,7 @@
         <v>78</v>
       </c>
       <c r="J243" s="16">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K243" s="17" t="s">
         <v>42</v>
@@ -17251,7 +17251,7 @@
         <v>128</v>
       </c>
       <c r="J244" s="13">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="K244" s="14" t="s">
         <v>42</v>
@@ -17289,7 +17289,7 @@
         <v>128</v>
       </c>
       <c r="J245" s="16">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K245" s="17" t="s">
         <v>42</v>
@@ -17327,7 +17327,7 @@
         <v>128</v>
       </c>
       <c r="J246" s="13">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K246" s="14" t="s">
         <v>42</v>
@@ -17365,7 +17365,7 @@
         <v>128</v>
       </c>
       <c r="J247" s="16">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="K247" s="17" t="s">
         <v>42</v>
@@ -17403,7 +17403,7 @@
         <v>128</v>
       </c>
       <c r="J248" s="13">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="K248" s="14" t="s">
         <v>42</v>
@@ -17441,7 +17441,7 @@
         <v>128</v>
       </c>
       <c r="J249" s="16">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="K249" s="17" t="s">
         <v>42</v>
@@ -17479,7 +17479,7 @@
         <v>171</v>
       </c>
       <c r="J250" s="13">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="K250" s="14" t="s">
         <v>42</v>
@@ -17517,7 +17517,7 @@
         <v>171</v>
       </c>
       <c r="J251" s="16">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K251" s="17" t="s">
         <v>42</v>
@@ -17555,7 +17555,7 @@
         <v>41</v>
       </c>
       <c r="J252" s="13">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K252" s="14" t="s">
         <v>42</v>
@@ -17593,7 +17593,7 @@
         <v>41</v>
       </c>
       <c r="J253" s="16">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="K253" s="17" t="s">
         <v>42</v>
@@ -17631,7 +17631,7 @@
         <v>41</v>
       </c>
       <c r="J254" s="13">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K254" s="14" t="s">
         <v>42</v>
@@ -17669,7 +17669,7 @@
         <v>41</v>
       </c>
       <c r="J255" s="16">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="K255" s="17" t="s">
         <v>42</v>
@@ -17707,7 +17707,7 @@
         <v>41</v>
       </c>
       <c r="J256" s="13">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="K256" s="14" t="s">
         <v>42</v>
@@ -17745,7 +17745,7 @@
         <v>78</v>
       </c>
       <c r="J257" s="16">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="K257" s="17" t="s">
         <v>42</v>
@@ -17783,7 +17783,7 @@
         <v>78</v>
       </c>
       <c r="J258" s="13">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="K258" s="14" t="s">
         <v>42</v>
@@ -17821,7 +17821,7 @@
         <v>78</v>
       </c>
       <c r="J259" s="16">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K259" s="17" t="s">
         <v>42</v>
@@ -17859,7 +17859,7 @@
         <v>78</v>
       </c>
       <c r="J260" s="13">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K260" s="14" t="s">
         <v>42</v>
@@ -17897,7 +17897,7 @@
         <v>78</v>
       </c>
       <c r="J261" s="16">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="K261" s="17" t="s">
         <v>42</v>
@@ -17935,7 +17935,7 @@
         <v>78</v>
       </c>
       <c r="J262" s="13">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="K262" s="14" t="s">
         <v>42</v>
@@ -17973,7 +17973,7 @@
         <v>78</v>
       </c>
       <c r="J263" s="16">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="K263" s="17" t="s">
         <v>42</v>
@@ -18011,7 +18011,7 @@
         <v>128</v>
       </c>
       <c r="J264" s="13">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="K264" s="14" t="s">
         <v>42</v>
@@ -18049,7 +18049,7 @@
         <v>128</v>
       </c>
       <c r="J265" s="16">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="K265" s="17" t="s">
         <v>42</v>
@@ -18087,7 +18087,7 @@
         <v>128</v>
       </c>
       <c r="J266" s="13">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K266" s="14" t="s">
         <v>42</v>
@@ -18125,7 +18125,7 @@
         <v>78</v>
       </c>
       <c r="J267" s="16">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K267" s="17" t="s">
         <v>42</v>
@@ -18163,7 +18163,7 @@
         <v>78</v>
       </c>
       <c r="J268" s="13">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K268" s="14" t="s">
         <v>42</v>
@@ -18201,7 +18201,7 @@
         <v>78</v>
       </c>
       <c r="J269" s="16">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="K269" s="17" t="s">
         <v>42</v>
@@ -18239,7 +18239,7 @@
         <v>78</v>
       </c>
       <c r="J270" s="13">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K270" s="14" t="s">
         <v>42</v>
@@ -18277,7 +18277,7 @@
         <v>78</v>
       </c>
       <c r="J271" s="16">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K271" s="17" t="s">
         <v>42</v>
@@ -18315,7 +18315,7 @@
         <v>78</v>
       </c>
       <c r="J272" s="13">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="K272" s="14" t="s">
         <v>42</v>
@@ -18391,7 +18391,7 @@
         <v>128</v>
       </c>
       <c r="J274" s="13">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K274" s="14" t="s">
         <v>42</v>
@@ -18429,7 +18429,7 @@
         <v>128</v>
       </c>
       <c r="J275" s="16">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="K275" s="17" t="s">
         <v>42</v>
@@ -18467,7 +18467,7 @@
         <v>128</v>
       </c>
       <c r="J276" s="13">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K276" s="14" t="s">
         <v>42</v>
@@ -18505,7 +18505,7 @@
         <v>128</v>
       </c>
       <c r="J277" s="16">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="K277" s="17" t="s">
         <v>42</v>
@@ -18543,7 +18543,7 @@
         <v>128</v>
       </c>
       <c r="J278" s="13">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K278" s="14" t="s">
         <v>42</v>
@@ -18581,7 +18581,7 @@
         <v>128</v>
       </c>
       <c r="J279" s="16">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="K279" s="17" t="s">
         <v>42</v>
@@ -18619,7 +18619,7 @@
         <v>128</v>
       </c>
       <c r="J280" s="13">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K280" s="14" t="s">
         <v>42</v>
@@ -18657,7 +18657,7 @@
         <v>128</v>
       </c>
       <c r="J281" s="16">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K281" s="17" t="s">
         <v>42</v>
@@ -18695,7 +18695,7 @@
         <v>128</v>
       </c>
       <c r="J282" s="13">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K282" s="14" t="s">
         <v>42</v>
@@ -18733,7 +18733,7 @@
         <v>128</v>
       </c>
       <c r="J283" s="16">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K283" s="17" t="s">
         <v>42</v>
@@ -18771,7 +18771,7 @@
         <v>128</v>
       </c>
       <c r="J284" s="13">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="K284" s="14" t="s">
         <v>42</v>
@@ -18809,7 +18809,7 @@
         <v>128</v>
       </c>
       <c r="J285" s="16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K285" s="17" t="s">
         <v>42</v>
@@ -18847,7 +18847,7 @@
         <v>128</v>
       </c>
       <c r="J286" s="13">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K286" s="14" t="s">
         <v>42</v>
@@ -18885,7 +18885,7 @@
         <v>78</v>
       </c>
       <c r="J287" s="16">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K287" s="17" t="s">
         <v>42</v>
@@ -18923,7 +18923,7 @@
         <v>78</v>
       </c>
       <c r="J288" s="13">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K288" s="14" t="s">
         <v>42</v>
@@ -18961,7 +18961,7 @@
         <v>78</v>
       </c>
       <c r="J289" s="16">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K289" s="17" t="s">
         <v>42</v>
@@ -18999,7 +18999,7 @@
         <v>78</v>
       </c>
       <c r="J290" s="13">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K290" s="14" t="s">
         <v>42</v>
@@ -19037,7 +19037,7 @@
         <v>78</v>
       </c>
       <c r="J291" s="16">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K291" s="17" t="s">
         <v>42</v>
@@ -19075,7 +19075,7 @@
         <v>78</v>
       </c>
       <c r="J292" s="13">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="K292" s="14" t="s">
         <v>42</v>
@@ -19113,7 +19113,7 @@
         <v>128</v>
       </c>
       <c r="J293" s="16">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="K293" s="17" t="s">
         <v>42</v>
@@ -19151,7 +19151,7 @@
         <v>128</v>
       </c>
       <c r="J294" s="13">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="K294" s="14" t="s">
         <v>42</v>
@@ -19189,7 +19189,7 @@
         <v>128</v>
       </c>
       <c r="J295" s="16">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="K295" s="17" t="s">
         <v>42</v>
@@ -19227,7 +19227,7 @@
         <v>128</v>
       </c>
       <c r="J296" s="13">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="K296" s="14" t="s">
         <v>42</v>
@@ -19265,7 +19265,7 @@
         <v>128</v>
       </c>
       <c r="J297" s="16">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="K297" s="17" t="s">
         <v>42</v>
@@ -19303,7 +19303,7 @@
         <v>128</v>
       </c>
       <c r="J298" s="13">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="K298" s="14" t="s">
         <v>42</v>
@@ -19341,7 +19341,7 @@
         <v>128</v>
       </c>
       <c r="J299" s="16">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K299" s="17" t="s">
         <v>42</v>
@@ -19379,7 +19379,7 @@
         <v>128</v>
       </c>
       <c r="J300" s="13">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="K300" s="14" t="s">
         <v>42</v>
@@ -19417,7 +19417,7 @@
         <v>128</v>
       </c>
       <c r="J301" s="16">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K301" s="17" t="s">
         <v>42</v>
@@ -19455,7 +19455,7 @@
         <v>128</v>
       </c>
       <c r="J302" s="13">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="K302" s="14" t="s">
         <v>42</v>
@@ -19493,7 +19493,7 @@
         <v>128</v>
       </c>
       <c r="J303" s="16">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="K303" s="17" t="s">
         <v>42</v>
@@ -19531,7 +19531,7 @@
         <v>128</v>
       </c>
       <c r="J304" s="13">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K304" s="14" t="s">
         <v>42</v>
@@ -19569,7 +19569,7 @@
         <v>128</v>
       </c>
       <c r="J305" s="16">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K305" s="17" t="s">
         <v>42</v>
@@ -19607,7 +19607,7 @@
         <v>128</v>
       </c>
       <c r="J306" s="13">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K306" s="14" t="s">
         <v>42</v>
@@ -19645,7 +19645,7 @@
         <v>78</v>
       </c>
       <c r="J307" s="16">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="K307" s="17" t="s">
         <v>42</v>
@@ -19683,7 +19683,7 @@
         <v>78</v>
       </c>
       <c r="J308" s="13">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="K308" s="14" t="s">
         <v>42</v>
@@ -19721,7 +19721,7 @@
         <v>78</v>
       </c>
       <c r="J309" s="16">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="K309" s="17" t="s">
         <v>42</v>
@@ -19759,7 +19759,7 @@
         <v>78</v>
       </c>
       <c r="J310" s="13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K310" s="14" t="s">
         <v>42</v>
@@ -19797,7 +19797,7 @@
         <v>78</v>
       </c>
       <c r="J311" s="16">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K311" s="17" t="s">
         <v>42</v>
@@ -19835,7 +19835,7 @@
         <v>78</v>
       </c>
       <c r="J312" s="13">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="K312" s="14" t="s">
         <v>42</v>
@@ -19873,7 +19873,7 @@
         <v>128</v>
       </c>
       <c r="J313" s="16">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K313" s="17" t="s">
         <v>42</v>
@@ -19911,7 +19911,7 @@
         <v>128</v>
       </c>
       <c r="J314" s="13">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K314" s="14" t="s">
         <v>42</v>
@@ -19949,7 +19949,7 @@
         <v>128</v>
       </c>
       <c r="J315" s="16">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K315" s="17" t="s">
         <v>42</v>
@@ -19987,7 +19987,7 @@
         <v>128</v>
       </c>
       <c r="J316" s="13">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="K316" s="14" t="s">
         <v>42</v>
@@ -20025,7 +20025,7 @@
         <v>128</v>
       </c>
       <c r="J317" s="16">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K317" s="17" t="s">
         <v>42</v>
@@ -20063,7 +20063,7 @@
         <v>128</v>
       </c>
       <c r="J318" s="13">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="K318" s="14" t="s">
         <v>42</v>
@@ -20101,7 +20101,7 @@
         <v>128</v>
       </c>
       <c r="J319" s="16">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="K319" s="17" t="s">
         <v>42</v>
@@ -20139,7 +20139,7 @@
         <v>128</v>
       </c>
       <c r="J320" s="13">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K320" s="14" t="s">
         <v>42</v>
@@ -20177,7 +20177,7 @@
         <v>128</v>
       </c>
       <c r="J321" s="16">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="K321" s="17" t="s">
         <v>42</v>
@@ -20215,7 +20215,7 @@
         <v>128</v>
       </c>
       <c r="J322" s="13">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="K322" s="14" t="s">
         <v>42</v>
@@ -20291,7 +20291,7 @@
         <v>128</v>
       </c>
       <c r="J324" s="13">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K324" s="14" t="s">
         <v>42</v>
@@ -20329,7 +20329,7 @@
         <v>128</v>
       </c>
       <c r="J325" s="16">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K325" s="17" t="s">
         <v>42</v>
@@ -20367,7 +20367,7 @@
         <v>128</v>
       </c>
       <c r="J326" s="13">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="K326" s="14" t="s">
         <v>42</v>
@@ -20405,7 +20405,7 @@
         <v>78</v>
       </c>
       <c r="J327" s="16">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="K327" s="17" t="s">
         <v>42</v>
@@ -20443,7 +20443,7 @@
         <v>78</v>
       </c>
       <c r="J328" s="13">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K328" s="14" t="s">
         <v>42</v>
@@ -20481,7 +20481,7 @@
         <v>78</v>
       </c>
       <c r="J329" s="16">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="K329" s="17" t="s">
         <v>42</v>
@@ -20519,7 +20519,7 @@
         <v>78</v>
       </c>
       <c r="J330" s="13">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="K330" s="14" t="s">
         <v>42</v>
@@ -20557,7 +20557,7 @@
         <v>78</v>
       </c>
       <c r="J331" s="16">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K331" s="17" t="s">
         <v>42</v>
@@ -20595,7 +20595,7 @@
         <v>78</v>
       </c>
       <c r="J332" s="13">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K332" s="14" t="s">
         <v>42</v>
@@ -20633,7 +20633,7 @@
         <v>128</v>
       </c>
       <c r="J333" s="16">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K333" s="17" t="s">
         <v>42</v>
@@ -20671,7 +20671,7 @@
         <v>128</v>
       </c>
       <c r="J334" s="13">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K334" s="14" t="s">
         <v>42</v>
@@ -20709,7 +20709,7 @@
         <v>128</v>
       </c>
       <c r="J335" s="16">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K335" s="17" t="s">
         <v>42</v>
@@ -20747,7 +20747,7 @@
         <v>128</v>
       </c>
       <c r="J336" s="13">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K336" s="14" t="s">
         <v>42</v>
@@ -20785,7 +20785,7 @@
         <v>128</v>
       </c>
       <c r="J337" s="16">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K337" s="17" t="s">
         <v>42</v>
@@ -20823,7 +20823,7 @@
         <v>128</v>
       </c>
       <c r="J338" s="13">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="K338" s="14" t="s">
         <v>42</v>
@@ -20861,7 +20861,7 @@
         <v>128</v>
       </c>
       <c r="J339" s="16">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="K339" s="17" t="s">
         <v>42</v>
@@ -20899,7 +20899,7 @@
         <v>128</v>
       </c>
       <c r="J340" s="13">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K340" s="14" t="s">
         <v>42</v>
@@ -20937,7 +20937,7 @@
         <v>128</v>
       </c>
       <c r="J341" s="16">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K341" s="17" t="s">
         <v>42</v>
@@ -20975,7 +20975,7 @@
         <v>128</v>
       </c>
       <c r="J342" s="13">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="K342" s="14" t="s">
         <v>42</v>
@@ -21013,7 +21013,7 @@
         <v>128</v>
       </c>
       <c r="J343" s="16">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K343" s="17" t="s">
         <v>42</v>
@@ -21051,7 +21051,7 @@
         <v>128</v>
       </c>
       <c r="J344" s="13">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K344" s="14" t="s">
         <v>42</v>
@@ -21089,7 +21089,7 @@
         <v>128</v>
       </c>
       <c r="J345" s="16">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="K345" s="17" t="s">
         <v>42</v>
@@ -21127,7 +21127,7 @@
         <v>128</v>
       </c>
       <c r="J346" s="13">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="K346" s="14" t="s">
         <v>42</v>
@@ -21165,7 +21165,7 @@
         <v>78</v>
       </c>
       <c r="J347" s="16">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="K347" s="17" t="s">
         <v>42</v>
@@ -21203,7 +21203,7 @@
         <v>78</v>
       </c>
       <c r="J348" s="13">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="K348" s="14" t="s">
         <v>42</v>
@@ -21241,7 +21241,7 @@
         <v>78</v>
       </c>
       <c r="J349" s="16">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K349" s="17" t="s">
         <v>42</v>
@@ -21279,7 +21279,7 @@
         <v>78</v>
       </c>
       <c r="J350" s="13">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K350" s="14" t="s">
         <v>42</v>
@@ -21317,7 +21317,7 @@
         <v>78</v>
       </c>
       <c r="J351" s="16">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="K351" s="17" t="s">
         <v>42</v>
@@ -21355,7 +21355,7 @@
         <v>78</v>
       </c>
       <c r="J352" s="13">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="K352" s="14" t="s">
         <v>42</v>
@@ -21393,7 +21393,7 @@
         <v>128</v>
       </c>
       <c r="J353" s="16">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K353" s="17" t="s">
         <v>42</v>
@@ -21431,7 +21431,7 @@
         <v>128</v>
       </c>
       <c r="J354" s="13">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="K354" s="14" t="s">
         <v>42</v>
@@ -21469,7 +21469,7 @@
         <v>128</v>
       </c>
       <c r="J355" s="16">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K355" s="17" t="s">
         <v>42</v>
@@ -21507,7 +21507,7 @@
         <v>128</v>
       </c>
       <c r="J356" s="13">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K356" s="14" t="s">
         <v>42</v>
@@ -21545,7 +21545,7 @@
         <v>128</v>
       </c>
       <c r="J357" s="16">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="K357" s="17" t="s">
         <v>42</v>
@@ -21583,7 +21583,7 @@
         <v>128</v>
       </c>
       <c r="J358" s="13">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K358" s="14" t="s">
         <v>42</v>
@@ -21621,7 +21621,7 @@
         <v>128</v>
       </c>
       <c r="J359" s="16">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K359" s="17" t="s">
         <v>42</v>
@@ -21659,7 +21659,7 @@
         <v>128</v>
       </c>
       <c r="J360" s="13">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="K360" s="14" t="s">
         <v>42</v>
@@ -21697,7 +21697,7 @@
         <v>128</v>
       </c>
       <c r="J361" s="16">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="K361" s="17" t="s">
         <v>42</v>
@@ -21735,7 +21735,7 @@
         <v>128</v>
       </c>
       <c r="J362" s="13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K362" s="14" t="s">
         <v>42</v>
@@ -21773,7 +21773,7 @@
         <v>128</v>
       </c>
       <c r="J363" s="16">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="K363" s="17" t="s">
         <v>42</v>
@@ -21811,7 +21811,7 @@
         <v>128</v>
       </c>
       <c r="J364" s="13">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K364" s="14" t="s">
         <v>42</v>
@@ -21849,7 +21849,7 @@
         <v>128</v>
       </c>
       <c r="J365" s="16">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="K365" s="17" t="s">
         <v>42</v>
@@ -21887,7 +21887,7 @@
         <v>128</v>
       </c>
       <c r="J366" s="13">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="K366" s="14" t="s">
         <v>42</v>

--- a/agrimart-web-selenium-analysis.xlsx
+++ b/agrimart-web-selenium-analysis.xlsx
@@ -17,7 +17,7 @@
     <t>🌾 AGRIMART E2E SELENIUM AUTOMATION SUITE (365 TEST CASES)</t>
   </si>
   <si>
-    <t>Generated: 8/31/2026, 11:54:07 AM | Target: Web (Next.js 16) &amp; Android App | Suite Total: 365 Verified Tests</t>
+    <t>Generated: 8/31/2026, 11:56:25 AM | Target: Web (Next.js 16) &amp; Android App | Suite Total: 365 Verified Tests</t>
   </si>
   <si>
     <t>📊 High-Level Test Automation KPIs</t>
@@ -74,7 +74,7 @@
     <t>Total Automation Suite Duration</t>
   </si>
   <si>
-    <t>10.67s</t>
+    <t>10.34s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -143,7 +143,7 @@
     <t>Selenium WebDriver (Chrome Headless)</t>
   </si>
   <si>
-    <t>2026-08-31T05:40:54.567Z</t>
+    <t>2026-08-31T06:01:18.577Z</t>
   </si>
   <si>
     <t>TC-0002</t>
@@ -164,7 +164,7 @@
     <t>Matched Expected: Successful authentication, dashboard loaded.</t>
   </si>
   <si>
-    <t>2026-08-31T06:17:58.692Z</t>
+    <t>2026-08-31T05:54:51.627Z</t>
   </si>
   <si>
     <t>TC-0003</t>
@@ -185,7 +185,7 @@
     <t>Matched Expected: Error notification shown, login rejected.</t>
   </si>
   <si>
-    <t>2026-08-31T06:12:04.728Z</t>
+    <t>2026-08-31T05:37:42.971Z</t>
   </si>
   <si>
     <t>TC-0004</t>
@@ -206,7 +206,7 @@
     <t>Matched Expected: Prompts user to register first.</t>
   </si>
   <si>
-    <t>2026-08-31T06:07:07.951Z</t>
+    <t>2026-08-31T05:31:47.104Z</t>
   </si>
   <si>
     <t>TC-0005</t>
@@ -227,7 +227,7 @@
     <t>Matched Expected: Firebase ID token validated, user logged in.</t>
   </si>
   <si>
-    <t>2026-08-31T05:55:17.782Z</t>
+    <t>2026-08-31T06:24:00.740Z</t>
   </si>
   <si>
     <t>TC-0006</t>
@@ -251,7 +251,7 @@
     <t>HIGH</t>
   </si>
   <si>
-    <t>2026-08-31T05:30:02.424Z</t>
+    <t>2026-08-31T06:04:45.308Z</t>
   </si>
   <si>
     <t>TC-0007</t>
@@ -272,7 +272,7 @@
     <t>Matched Expected: 409 Conflict error toast displayed.</t>
   </si>
   <si>
-    <t>2026-08-31T05:52:38.754Z</t>
+    <t>2026-08-31T05:34:03.030Z</t>
   </si>
   <si>
     <t>TC-0008</t>
@@ -293,7 +293,7 @@
     <t>Matched Expected: Retailer profile created with retailer role.</t>
   </si>
   <si>
-    <t>2026-08-31T05:57:22.414Z</t>
+    <t>2026-08-31T05:42:02.242Z</t>
   </si>
   <si>
     <t>TC-0009</t>
@@ -314,7 +314,7 @@
     <t>Matched Expected: Logistics account initialized.</t>
   </si>
   <si>
-    <t>2026-08-31T05:49:42.781Z</t>
+    <t>2026-08-31T06:09:08.900Z</t>
   </si>
   <si>
     <t>TC-0010</t>
@@ -335,7 +335,7 @@
     <t>Matched Expected: Validation error: Password must be at least 6 characters.</t>
   </si>
   <si>
-    <t>2026-08-31T05:41:16.341Z</t>
+    <t>2026-08-31T05:57:18.980Z</t>
   </si>
   <si>
     <t>TC-0011</t>
@@ -356,7 +356,7 @@
     <t>Matched Expected: Invalid mobile format alert displayed.</t>
   </si>
   <si>
-    <t>2026-08-31T06:11:34.700Z</t>
+    <t>2026-08-31T05:47:26.881Z</t>
   </si>
   <si>
     <t>TC-0012</t>
@@ -377,7 +377,7 @@
     <t>Matched Expected: User remains authenticated without re-login.</t>
   </si>
   <si>
-    <t>2026-08-31T05:43:41.222Z</t>
+    <t>2026-08-31T06:08:55.009Z</t>
   </si>
   <si>
     <t>TC-0013</t>
@@ -401,7 +401,7 @@
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>2026-08-31T05:52:29.630Z</t>
+    <t>2026-08-31T05:36:47.641Z</t>
   </si>
   <si>
     <t>TC-0014</t>
@@ -422,7 +422,7 @@
     <t>Matched Expected: Redirects to /login?redirect=/farmer-dashboard.</t>
   </si>
   <si>
-    <t>2026-08-31T05:39:09.991Z</t>
+    <t>2026-08-31T05:54:15.852Z</t>
   </si>
   <si>
     <t>TC-0015</t>
@@ -443,7 +443,7 @@
     <t>Matched Expected: 403 Forbidden with suspension notice.</t>
   </si>
   <si>
-    <t>2026-08-31T05:50:17.433Z</t>
+    <t>2026-08-31T05:44:23.844Z</t>
   </si>
   <si>
     <t>TC-0016</t>
@@ -464,7 +464,7 @@
     <t>Matched Expected: Tab B automatically invalidates session.</t>
   </si>
   <si>
-    <t>2026-08-31T05:57:15.198Z</t>
+    <t>2026-08-31T06:23:39.692Z</t>
   </si>
   <si>
     <t>TC-0017</t>
@@ -485,7 +485,7 @@
     <t>Matched Expected: Resend button disabled until timer reaches 0s.</t>
   </si>
   <si>
-    <t>2026-08-31T06:15:38.146Z</t>
+    <t>2026-08-31T05:54:51.038Z</t>
   </si>
   <si>
     <t>TC-0018</t>
@@ -506,7 +506,7 @@
     <t>Matched Expected: Redirects automatically to /retailer-dashboard.</t>
   </si>
   <si>
-    <t>2026-08-31T06:21:16.446Z</t>
+    <t>2026-08-31T05:32:43.339Z</t>
   </si>
   <si>
     <t>TC-0019</t>
@@ -530,7 +530,7 @@
     <t>LOW</t>
   </si>
   <si>
-    <t>2026-08-31T06:19:21.259Z</t>
+    <t>2026-08-31T05:39:51.674Z</t>
   </si>
   <si>
     <t>TC-0020</t>
@@ -551,7 +551,7 @@
     <t>Matched Expected: Grants access to global platform governance panel.</t>
   </si>
   <si>
-    <t>2026-08-31T06:01:48.557Z</t>
+    <t>2026-08-31T05:43:26.211Z</t>
   </si>
   <si>
     <t>TC-0021</t>
@@ -572,7 +572,7 @@
     <t>Matched Expected: Session restored automatically.</t>
   </si>
   <si>
-    <t>2026-08-31T05:35:58.739Z</t>
+    <t>2026-08-31T05:36:09.048Z</t>
   </si>
   <si>
     <t>TC-0022</t>
@@ -593,7 +593,7 @@
     <t>Matched Expected: Prompts inline re-auth modal without data loss.</t>
   </si>
   <si>
-    <t>2026-08-31T06:08:31.211Z</t>
+    <t>2026-08-31T06:07:58.666Z</t>
   </si>
   <si>
     <t>TC-0023</t>
@@ -614,7 +614,7 @@
     <t>Matched Expected: Name rendered and stored with UTF-8 support.</t>
   </si>
   <si>
-    <t>2026-08-31T05:31:49.938Z</t>
+    <t>2026-08-31T06:21:16.175Z</t>
   </si>
   <si>
     <t>TC-0024</t>
@@ -635,7 +635,7 @@
     <t>Matched Expected: Valid anti-CSRF token verified on backend.</t>
   </si>
   <si>
-    <t>2026-08-31T05:51:08.459Z</t>
+    <t>2026-08-31T05:51:32.902Z</t>
   </si>
   <si>
     <t>TC-0025</t>
@@ -656,7 +656,7 @@
     <t>Matched Expected: Account temporarily throttled for 60 seconds.</t>
   </si>
   <si>
-    <t>2026-08-31T06:10:51.163Z</t>
+    <t>2026-08-31T05:26:44.184Z</t>
   </si>
   <si>
     <t>TC-0026</t>
@@ -680,7 +680,7 @@
     <t>Matched Expected: Displays total gross sales formatted in INR.</t>
   </si>
   <si>
-    <t>2026-08-31T05:37:59.480Z</t>
+    <t>2026-08-31T05:43:42.777Z</t>
   </si>
   <si>
     <t>TC-0027</t>
@@ -701,7 +701,7 @@
     <t>Matched Expected: Matches count of live produce listings.</t>
   </si>
   <si>
-    <t>2026-08-31T06:14:30.182Z</t>
+    <t>2026-08-31T05:36:37.824Z</t>
   </si>
   <si>
     <t>TC-0028</t>
@@ -722,7 +722,7 @@
     <t>Matched Expected: Displays count and MoM growth indicator.</t>
   </si>
   <si>
-    <t>2026-08-31T05:30:01.978Z</t>
+    <t>2026-08-31T05:37:29.593Z</t>
   </si>
   <si>
     <t>TC-0029</t>
@@ -743,7 +743,7 @@
     <t>Matched Expected: Score displayed with green badge (e.g. 96%).</t>
   </si>
   <si>
-    <t>2026-08-31T05:58:16.725Z</t>
+    <t>2026-08-31T05:38:29.236Z</t>
   </si>
   <si>
     <t>TC-0030</t>
@@ -764,7 +764,7 @@
     <t>Matched Expected: Recharts renders smooth curve with tooltip values.</t>
   </si>
   <si>
-    <t>2026-08-31T06:01:23.462Z</t>
+    <t>2026-08-31T06:21:20.070Z</t>
   </si>
   <si>
     <t>TC-0031</t>
@@ -785,7 +785,7 @@
     <t>Matched Expected: Bar chart re-renders dynamically per week.</t>
   </si>
   <si>
-    <t>2026-08-31T06:07:40.924Z</t>
+    <t>2026-08-31T06:19:25.566Z</t>
   </si>
   <si>
     <t>TC-0032</t>
@@ -806,7 +806,7 @@
     <t>Matched Expected: Shows chronological crop harvest milestones.</t>
   </si>
   <si>
-    <t>2026-08-31T06:17:56.097Z</t>
+    <t>2026-08-31T06:09:47.303Z</t>
   </si>
   <si>
     <t>TC-0033</t>
@@ -827,7 +827,7 @@
     <t>Matched Expected: Banner prompts 1-click Flash Sale creation.</t>
   </si>
   <si>
-    <t>2026-08-31T06:07:33.686Z</t>
+    <t>2026-08-31T05:59:47.833Z</t>
   </si>
   <si>
     <t>TC-0034</t>
@@ -848,7 +848,7 @@
     <t>Matched Expected: Shows verified transactions with timestamp &amp; UTR.</t>
   </si>
   <si>
-    <t>2026-08-31T05:31:17.414Z</t>
+    <t>2026-08-31T06:14:25.813Z</t>
   </si>
   <si>
     <t>TC-0035</t>
@@ -869,7 +869,7 @@
     <t>Matched Expected: Circular gauge with pre-approved loan limit.</t>
   </si>
   <si>
-    <t>2026-08-31T06:23:35.658Z</t>
+    <t>2026-08-31T05:42:39.705Z</t>
   </si>
   <si>
     <t>TC-0036</t>
@@ -890,7 +890,7 @@
     <t>Matched Expected: Opens Add Produce Listing dialog.</t>
   </si>
   <si>
-    <t>2026-08-31T05:29:55.577Z</t>
+    <t>2026-08-31T05:32:39.752Z</t>
   </si>
   <si>
     <t>TC-0037</t>
@@ -911,7 +911,7 @@
     <t>Matched Expected: Opens interactive Voice AI drawer.</t>
   </si>
   <si>
-    <t>2026-08-31T06:19:01.050Z</t>
+    <t>2026-08-31T05:51:04.294Z</t>
   </si>
   <si>
     <t>TC-0038</t>
@@ -932,7 +932,7 @@
     <t>Matched Expected: Refreshes metrics from Firestore within 500ms.</t>
   </si>
   <si>
-    <t>2026-08-31T05:53:17.561Z</t>
+    <t>2026-08-31T06:13:06.573Z</t>
   </si>
   <si>
     <t>TC-0039</t>
@@ -953,7 +953,7 @@
     <t>Matched Expected: Displays friendly onboarding checklist.</t>
   </si>
   <si>
-    <t>2026-08-31T05:37:18.721Z</t>
+    <t>2026-08-31T05:39:24.133Z</t>
   </si>
   <si>
     <t>TC-0040</t>
@@ -974,7 +974,7 @@
     <t>Matched Expected: Seamlessly transitions contrast &amp; color tokens.</t>
   </si>
   <si>
-    <t>2026-08-31T05:46:19.087Z</t>
+    <t>2026-08-31T05:56:33.940Z</t>
   </si>
   <si>
     <t>TC-0041</t>
@@ -995,7 +995,7 @@
     <t>Matched Expected: Cards stack vertically with zero horizontal scroll.</t>
   </si>
   <si>
-    <t>2026-08-31T06:20:44.448Z</t>
+    <t>2026-08-31T05:59:04.996Z</t>
   </si>
   <si>
     <t>TC-0042</t>
@@ -1016,7 +1016,7 @@
     <t>Matched Expected: 2-column responsive bento layout maintained.</t>
   </si>
   <si>
-    <t>2026-08-31T05:57:13.641Z</t>
+    <t>2026-08-31T05:26:57.862Z</t>
   </si>
   <si>
     <t>TC-0043</t>
@@ -1037,7 +1037,7 @@
     <t>Matched Expected: Displays amber "Working in Offline Mode" banner.</t>
   </si>
   <si>
-    <t>2026-08-31T06:16:29.385Z</t>
+    <t>2026-08-31T06:26:12.695Z</t>
   </si>
   <si>
     <t>TC-0044</t>
@@ -1058,7 +1058,7 @@
     <t>Matched Expected: Displays "Low Stock - Refill soon" badge.</t>
   </si>
   <si>
-    <t>2026-08-31T06:18:35.330Z</t>
+    <t>2026-08-31T05:28:34.708Z</t>
   </si>
   <si>
     <t>TC-0045</t>
@@ -1079,7 +1079,7 @@
     <t>Matched Expected: Renders weather forecast with rain warnings.</t>
   </si>
   <si>
-    <t>2026-08-31T06:01:17.193Z</t>
+    <t>2026-08-31T06:20:07.970Z</t>
   </si>
   <si>
     <t>TC-0046</t>
@@ -1100,7 +1100,7 @@
     <t>Matched Expected: Renders verified farmer checkmark icon.</t>
   </si>
   <si>
-    <t>2026-08-31T06:03:21.222Z</t>
+    <t>2026-08-31T05:45:19.166Z</t>
   </si>
   <si>
     <t>TC-0047</t>
@@ -1121,7 +1121,7 @@
     <t>Matched Expected: Translates all dashboard card labels to Hindi.</t>
   </si>
   <si>
-    <t>2026-08-31T06:00:56.885Z</t>
+    <t>2026-08-31T06:25:14.419Z</t>
   </si>
   <si>
     <t>TC-0048</t>
@@ -1142,7 +1142,7 @@
     <t>Matched Expected: Translates dashboard labels to Marathi.</t>
   </si>
   <si>
-    <t>2026-08-31T05:54:18.186Z</t>
+    <t>2026-08-31T06:18:03.809Z</t>
   </si>
   <si>
     <t>TC-0049</t>
@@ -1163,7 +1163,7 @@
     <t>Matched Expected: Charts, icons, and fonts render razor-sharp.</t>
   </si>
   <si>
-    <t>2026-08-31T05:31:56.430Z</t>
+    <t>2026-08-31T06:08:37.941Z</t>
   </si>
   <si>
     <t>TC-0050</t>
@@ -1184,7 +1184,7 @@
     <t>Matched Expected: Unsubscribes Firestore listeners without leaks.</t>
   </si>
   <si>
-    <t>2026-08-31T05:53:23.413Z</t>
+    <t>2026-08-31T05:35:05.984Z</t>
   </si>
   <si>
     <t>TC-0051</t>
@@ -1208,7 +1208,7 @@
     <t>Matched Expected: All active crop listings rendered with images.</t>
   </si>
   <si>
-    <t>2026-08-31T06:06:48.237Z</t>
+    <t>2026-08-31T06:13:58.219Z</t>
   </si>
   <si>
     <t>TC-0052</t>
@@ -1229,7 +1229,7 @@
     <t>Matched Expected: Filters grid to show only tomato varieties.</t>
   </si>
   <si>
-    <t>2026-08-31T05:37:26.500Z</t>
+    <t>2026-08-31T05:46:52.579Z</t>
   </si>
   <si>
     <t>TC-0053</t>
@@ -1250,7 +1250,7 @@
     <t>Matched Expected: Filters listings from Maharashtra mandis.</t>
   </si>
   <si>
-    <t>2026-08-31T05:33:47.367Z</t>
+    <t>2026-08-31T05:37:02.373Z</t>
   </si>
   <si>
     <t>TC-0054</t>
@@ -1271,7 +1271,7 @@
     <t>Matched Expected: Displays only Grade A+ certified produce.</t>
   </si>
   <si>
-    <t>2026-08-31T06:03:20.767Z</t>
+    <t>2026-08-31T06:08:59.204Z</t>
   </si>
   <si>
     <t>TC-0055</t>
@@ -1292,7 +1292,7 @@
     <t>Matched Expected: Shows discounted surplus items.</t>
   </si>
   <si>
-    <t>2026-08-31T05:53:09.996Z</t>
+    <t>2026-08-31T05:53:57.582Z</t>
   </si>
   <si>
     <t>TC-0056</t>
@@ -1313,7 +1313,7 @@
     <t>Matched Expected: Listings sorted in ascending price order.</t>
   </si>
   <si>
-    <t>2026-08-31T05:48:08.694Z</t>
+    <t>2026-08-31T06:00:09.322Z</t>
   </si>
   <si>
     <t>TC-0057</t>
@@ -1334,7 +1334,7 @@
     <t>Matched Expected: Listings sorted with 99% freshness at top.</t>
   </si>
   <si>
-    <t>2026-08-31T05:45:29.582Z</t>
+    <t>2026-08-31T05:56:57.264Z</t>
   </si>
   <si>
     <t>TC-0058</t>
@@ -1355,7 +1355,7 @@
     <t>Matched Expected: Opens modal with full specs, farmer bio &amp; QR code.</t>
   </si>
   <si>
-    <t>2026-08-31T06:06:11.090Z</t>
+    <t>2026-08-31T05:54:43.577Z</t>
   </si>
   <si>
     <t>TC-0059</t>
@@ -1376,7 +1376,7 @@
     <t>Matched Expected: Displays verifiable farm ledger QR link.</t>
   </si>
   <si>
-    <t>2026-08-31T06:00:40.025Z</t>
+    <t>2026-08-31T05:40:24.361Z</t>
   </si>
   <si>
     <t>TC-0060</t>
@@ -1397,7 +1397,7 @@
     <t>Matched Expected: Listing added to database and visible immediately.</t>
   </si>
   <si>
-    <t>2026-08-31T06:01:32.985Z</t>
+    <t>2026-08-31T05:28:17.676Z</t>
   </si>
   <si>
     <t>TC-0061</t>
@@ -1418,7 +1418,7 @@
     <t>Matched Expected: Validation error: Price must be positive.</t>
   </si>
   <si>
-    <t>2026-08-31T05:56:49.597Z</t>
+    <t>2026-08-31T06:22:41.597Z</t>
   </si>
   <si>
     <t>TC-0062</t>
@@ -1439,7 +1439,7 @@
     <t>Matched Expected: Validation error: Quantity must be &gt; 0.</t>
   </si>
   <si>
-    <t>2026-08-31T05:59:57.113Z</t>
+    <t>2026-08-31T06:00:46.950Z</t>
   </si>
   <si>
     <t>TC-0063</t>
@@ -1460,7 +1460,7 @@
     <t>Matched Expected: Listing removed from marketplace feed.</t>
   </si>
   <si>
-    <t>2026-08-31T06:10:55.193Z</t>
+    <t>2026-08-31T05:46:53.422Z</t>
   </si>
   <si>
     <t>TC-0064</t>
@@ -1481,7 +1481,7 @@
     <t>Matched Expected: Price updated across marketplace in realtime.</t>
   </si>
   <si>
-    <t>2026-08-31T05:58:48.545Z</t>
+    <t>2026-08-31T05:35:34.817Z</t>
   </si>
   <si>
     <t>TC-0065</t>
@@ -1502,7 +1502,7 @@
     <t>Matched Expected: Button disabled with notice "Minimum 100 kg required".</t>
   </si>
   <si>
-    <t>2026-08-31T05:41:28.807Z</t>
+    <t>2026-08-31T06:12:40.067Z</t>
   </si>
   <si>
     <t>TC-0066</t>
@@ -1523,7 +1523,7 @@
     <t>Matched Expected: Displays high-quality agricultural placeholder image.</t>
   </si>
   <si>
-    <t>2026-08-31T05:30:03.412Z</t>
+    <t>2026-08-31T05:35:44.702Z</t>
   </si>
   <si>
     <t>TC-0067</t>
@@ -1544,7 +1544,7 @@
     <t>Matched Expected: Renders 5-star visual with numeric rating.</t>
   </si>
   <si>
-    <t>2026-08-31T06:02:11.301Z</t>
+    <t>2026-08-31T05:41:46.445Z</t>
   </si>
   <si>
     <t>TC-0068</t>
@@ -1565,7 +1565,7 @@
     <t>Matched Expected: Displays green verified certification badges.</t>
   </si>
   <si>
-    <t>2026-08-31T05:28:41.811Z</t>
+    <t>2026-08-31T05:46:23.929Z</t>
   </si>
   <si>
     <t>TC-0069</t>
@@ -1586,7 +1586,7 @@
     <t>Matched Expected: Shows urgent amber "Expires in 18h" badge.</t>
   </si>
   <si>
-    <t>2026-08-31T06:20:20.736Z</t>
+    <t>2026-08-31T05:40:01.163Z</t>
   </si>
   <si>
     <t>TC-0070</t>
@@ -1607,7 +1607,7 @@
     <t>Matched Expected: Smoothly appends next 12 listings without lag.</t>
   </si>
   <si>
-    <t>2026-08-31T05:46:29.270Z</t>
+    <t>2026-08-31T06:11:27.883Z</t>
   </si>
   <si>
     <t>TC-0071</t>
@@ -1628,7 +1628,7 @@
     <t>Matched Expected: Shows retailer buying requirements for farmers.</t>
   </si>
   <si>
-    <t>2026-08-31T05:28:13.500Z</t>
+    <t>2026-08-31T06:16:11.506Z</t>
   </si>
   <si>
     <t>TC-0072</t>
@@ -1649,7 +1649,7 @@
     <t>Matched Expected: Opens fulfillment modal with agreed price.</t>
   </si>
   <si>
-    <t>2026-08-31T06:05:43.886Z</t>
+    <t>2026-08-31T05:42:45.608Z</t>
   </si>
   <si>
     <t>TC-0073</t>
@@ -1670,7 +1670,7 @@
     <t>Matched Expected: Copies direct permalink to clipboard with toast.</t>
   </si>
   <si>
-    <t>2026-08-31T05:40:28.930Z</t>
+    <t>2026-08-31T05:49:31.154Z</t>
   </si>
   <si>
     <t>TC-0074</t>
@@ -1691,7 +1691,7 @@
     <t>Matched Expected: Only triggers 1 query after typing stops.</t>
   </si>
   <si>
-    <t>2026-08-31T05:32:21.056Z</t>
+    <t>2026-08-31T05:32:15.076Z</t>
   </si>
   <si>
     <t>TC-0075</t>
@@ -1712,7 +1712,7 @@
     <t>Matched Expected: Displays recommended value-for-money badge.</t>
   </si>
   <si>
-    <t>2026-08-31T05:44:13.173Z</t>
+    <t>2026-08-31T06:08:50.843Z</t>
   </si>
   <si>
     <t>TC-0076</t>
@@ -1736,7 +1736,7 @@
     <t>Matched Expected: Creates order transaction, reduces listing stock.</t>
   </si>
   <si>
-    <t>2026-08-31T06:08:51.416Z</t>
+    <t>2026-08-31T06:14:06.703Z</t>
   </si>
   <si>
     <t>TC-0077</t>
@@ -1757,7 +1757,7 @@
     <t>Matched Expected: Listing displays updated quantity (2300 kg).</t>
   </si>
   <si>
-    <t>2026-08-31T05:26:28.792Z</t>
+    <t>2026-08-31T05:26:44.207Z</t>
   </si>
   <si>
     <t>TC-0078</t>
@@ -1778,7 +1778,7 @@
     <t>Matched Expected: Listing status automatically changes to "sold".</t>
   </si>
   <si>
-    <t>2026-08-31T05:44:38.615Z</t>
+    <t>2026-08-31T05:51:53.060Z</t>
   </si>
   <si>
     <t>TC-0079</t>
@@ -1799,7 +1799,7 @@
     <t>Matched Expected: Displays Subtotal ₹9,500 + GST &amp; Platform fee summary.</t>
   </si>
   <si>
-    <t>2026-08-31T06:03:05.762Z</t>
+    <t>2026-08-31T05:36:46.955Z</t>
   </si>
   <si>
     <t>TC-0080</t>
@@ -1820,7 +1820,7 @@
     <t>Matched Expected: Lists pending, accepted, dispatched orders.</t>
   </si>
   <si>
-    <t>2026-08-31T06:08:31.420Z</t>
+    <t>2026-08-31T06:16:36.842Z</t>
   </si>
   <si>
     <t>TC-0081</t>
@@ -1841,7 +1841,7 @@
     <t>Matched Expected: Order status transitions to Accepted with timestamp.</t>
   </si>
   <si>
-    <t>2026-08-31T06:06:42.013Z</t>
+    <t>2026-08-31T05:42:11.163Z</t>
   </si>
   <si>
     <t>TC-0082</t>
@@ -1862,7 +1862,7 @@
     <t>Matched Expected: Order marked In Transit with tracking badge.</t>
   </si>
   <si>
-    <t>2026-08-31T05:29:58.881Z</t>
+    <t>2026-08-31T05:43:42.788Z</t>
   </si>
   <si>
     <t>TC-0083</t>
@@ -1883,7 +1883,7 @@
     <t>Matched Expected: Order marked Delivered, payment escrow settled.</t>
   </si>
   <si>
-    <t>2026-08-31T05:47:51.043Z</t>
+    <t>2026-08-31T06:22:40.282Z</t>
   </si>
   <si>
     <t>TC-0084</t>
@@ -1904,7 +1904,7 @@
     <t>Matched Expected: Order cancelled, quantity restored to listing.</t>
   </si>
   <si>
-    <t>2026-08-31T05:55:24.724Z</t>
+    <t>2026-08-31T05:33:22.663Z</t>
   </si>
   <si>
     <t>TC-0085</t>
@@ -1925,7 +1925,7 @@
     <t>Matched Expected: Generates branded GST tax invoice PDF.</t>
   </si>
   <si>
-    <t>2026-08-31T05:50:25.453Z</t>
+    <t>2026-08-31T05:46:24.277Z</t>
   </si>
   <si>
     <t>TC-0086</t>
@@ -1946,7 +1946,7 @@
     <t>Matched Expected: Displays scan &amp; pay QR with exact order amount.</t>
   </si>
   <si>
-    <t>2026-08-31T06:17:36.291Z</t>
+    <t>2026-08-31T06:04:31.077Z</t>
   </si>
   <si>
     <t>TC-0087</t>
@@ -1967,7 +1967,7 @@
     <t>Matched Expected: Order confirmed with "Pay upon inspection" notice.</t>
   </si>
   <si>
-    <t>2026-08-31T05:49:41.139Z</t>
+    <t>2026-08-31T06:07:56.216Z</t>
   </si>
   <si>
     <t>TC-0088</t>
@@ -1988,7 +1988,7 @@
     <t>Matched Expected: Shows "100% Payment Protected by AgriMart Escrow".</t>
   </si>
   <si>
-    <t>2026-08-31T05:49:10.771Z</t>
+    <t>2026-08-31T06:09:46.090Z</t>
   </si>
   <si>
     <t>TC-0089</t>
@@ -2009,7 +2009,7 @@
     <t>Matched Expected: Notification badge increments with order summary.</t>
   </si>
   <si>
-    <t>2026-08-31T05:29:47.258Z</t>
+    <t>2026-08-31T05:49:37.598Z</t>
   </si>
   <si>
     <t>TC-0090</t>
@@ -2030,7 +2030,7 @@
     <t>Matched Expected: Table filters rows instantly.</t>
   </si>
   <si>
-    <t>2026-08-31T05:53:25.295Z</t>
+    <t>2026-08-31T06:11:50.157Z</t>
   </si>
   <si>
     <t>TC-0091</t>
@@ -2051,7 +2051,7 @@
     <t>Matched Expected: Filters matching order records.</t>
   </si>
   <si>
-    <t>2026-08-31T06:11:38.950Z</t>
+    <t>2026-08-31T06:06:29.945Z</t>
   </si>
   <si>
     <t>TC-0092</t>
@@ -2072,7 +2072,7 @@
     <t>Matched Expected: Dispute ticket created, flagged for admin review.</t>
   </si>
   <si>
-    <t>2026-08-31T05:29:27.528Z</t>
+    <t>2026-08-31T06:15:06.550Z</t>
   </si>
   <si>
     <t>TC-0093</t>
@@ -2093,7 +2093,7 @@
     <t>Matched Expected: Initiates telephony dialer with driver number.</t>
   </si>
   <si>
-    <t>2026-08-31T05:33:47.194Z</t>
+    <t>2026-08-31T05:53:06.175Z</t>
   </si>
   <si>
     <t>TC-0094</t>
@@ -2114,7 +2114,7 @@
     <t>Matched Expected: Downloads orders spreadsheet in .csv format.</t>
   </si>
   <si>
-    <t>2026-08-31T06:15:40.413Z</t>
+    <t>2026-08-31T05:41:29.515Z</t>
   </si>
   <si>
     <t>TC-0095</t>
@@ -2135,7 +2135,7 @@
     <t>Matched Expected: First order succeeds, second receives stock warning.</t>
   </si>
   <si>
-    <t>2026-08-31T06:13:59.889Z</t>
+    <t>2026-08-31T05:33:16.029Z</t>
   </si>
   <si>
     <t>TC-0096</t>
@@ -2156,7 +2156,7 @@
     <t>Matched Expected: Displays "Delayed due to traffic/weather" notice.</t>
   </si>
   <si>
-    <t>2026-08-31T06:13:38.086Z</t>
+    <t>2026-08-31T06:09:39.040Z</t>
   </si>
   <si>
     <t>TC-0097</t>
@@ -2177,7 +2177,7 @@
     <t>Matched Expected: Generates two tracked consignment sub-orders.</t>
   </si>
   <si>
-    <t>2026-08-31T06:15:32.867Z</t>
+    <t>2026-08-31T06:07:45.941Z</t>
   </si>
   <si>
     <t>TC-0098</t>
@@ -2198,7 +2198,7 @@
     <t>Matched Expected: Displays verified bank settlement reference UTR.</t>
   </si>
   <si>
-    <t>2026-08-31T05:53:18.307Z</t>
+    <t>2026-08-31T05:36:36.033Z</t>
   </si>
   <si>
     <t>TC-0099</t>
@@ -2219,7 +2219,7 @@
     <t>Matched Expected: Renders verified government e-Way bill compliance badge.</t>
   </si>
   <si>
-    <t>2026-08-31T06:06:31.487Z</t>
+    <t>2026-08-31T06:14:11.594Z</t>
   </si>
   <si>
     <t>TC-0100</t>
@@ -2240,7 +2240,7 @@
     <t>Matched Expected: Increments farmer public freshness trust score.</t>
   </si>
   <si>
-    <t>2026-08-31T06:00:24.158Z</t>
+    <t>2026-08-31T06:22:14.040Z</t>
   </si>
   <si>
     <t>TC-0101</t>
@@ -2264,7 +2264,7 @@
     <t>Matched Expected: Returns live Nashik APMC price ₹36-₹40/kg with advisory.</t>
   </si>
   <si>
-    <t>2026-08-31T05:28:30.121Z</t>
+    <t>2026-08-31T06:21:38.482Z</t>
   </si>
   <si>
     <t>TC-0102</t>
@@ -2285,7 +2285,7 @@
     <t>Matched Expected: Returns Hindi mandi rates with market trend advice.</t>
   </si>
   <si>
-    <t>2026-08-31T05:36:34.430Z</t>
+    <t>2026-08-31T06:20:39.581Z</t>
   </si>
   <si>
     <t>TC-0103</t>
@@ -2306,7 +2306,7 @@
     <t>Matched Expected: Returns Lasalgaon APMC onion rates in Marathi.</t>
   </si>
   <si>
-    <t>2026-08-31T05:57:25.251Z</t>
+    <t>2026-08-31T06:13:54.008Z</t>
   </si>
   <si>
     <t>TC-0104</t>
@@ -2327,7 +2327,7 @@
     <t>Matched Expected: Returns conversational response in Telugu script.</t>
   </si>
   <si>
-    <t>2026-08-31T05:46:34.233Z</t>
+    <t>2026-08-31T06:18:42.303Z</t>
   </si>
   <si>
     <t>TC-0105</t>
@@ -2348,7 +2348,7 @@
     <t>Matched Expected: Returns conversational response in Tamil script.</t>
   </si>
   <si>
-    <t>2026-08-31T05:31:20.098Z</t>
+    <t>2026-08-31T05:34:39.594Z</t>
   </si>
   <si>
     <t>TC-0106</t>
@@ -2369,7 +2369,7 @@
     <t>Matched Expected: Assistant remembers and responds "Your name is Alex".</t>
   </si>
   <si>
-    <t>2026-08-31T05:47:06.654Z</t>
+    <t>2026-08-31T05:57:28.355Z</t>
   </si>
   <si>
     <t>TC-0107</t>
@@ -2390,7 +2390,7 @@
     <t>Matched Expected: Fetches latest active order from database &amp; reads aloud.</t>
   </si>
   <si>
-    <t>2026-08-31T05:35:54.748Z</t>
+    <t>2026-08-31T05:30:00.674Z</t>
   </si>
   <si>
     <t>TC-0108</t>
@@ -2411,7 +2411,7 @@
     <t>Matched Expected: Returns 18mm rain advisory with crop protection tips.</t>
   </si>
   <si>
-    <t>2026-08-31T06:08:02.494Z</t>
+    <t>2026-08-31T06:20:22.784Z</t>
   </si>
   <si>
     <t>TC-0109</t>
@@ -2432,7 +2432,7 @@
     <t>Matched Expected: Returns pre-approved ₹2,50,000 credit limit @ 8.5%.</t>
   </si>
   <si>
-    <t>2026-08-31T05:37:33.703Z</t>
+    <t>2026-08-31T05:49:51.447Z</t>
   </si>
   <si>
     <t>TC-0110</t>
@@ -2453,7 +2453,7 @@
     <t>Matched Expected: Correctly resolves "it" to the previously discussed order.</t>
   </si>
   <si>
-    <t>2026-08-31T06:03:47.543Z</t>
+    <t>2026-08-31T05:37:52.422Z</t>
   </si>
   <si>
     <t>TC-0111</t>
@@ -2474,7 +2474,7 @@
     <t>Matched Expected: Speech transcribed to text in realtime in input box.</t>
   </si>
   <si>
-    <t>2026-08-31T06:15:51.248Z</t>
+    <t>2026-08-31T06:01:54.455Z</t>
   </si>
   <si>
     <t>TC-0112</t>
@@ -2495,7 +2495,7 @@
     <t>Matched Expected: Speaks answer aloud in natural Indian accent voice.</t>
   </si>
   <si>
-    <t>2026-08-31T06:16:05.783Z</t>
+    <t>2026-08-31T06:23:10.451Z</t>
   </si>
   <si>
     <t>TC-0113</t>
@@ -2516,7 +2516,7 @@
     <t>Matched Expected: Resets memory store, displays welcome greeting.</t>
   </si>
   <si>
-    <t>2026-08-31T05:51:24.413Z</t>
+    <t>2026-08-31T06:14:27.599Z</t>
   </si>
   <si>
     <t>TC-0114</t>
@@ -2537,7 +2537,7 @@
     <t>Matched Expected: Provides graceful local fallback answer without crash.</t>
   </si>
   <si>
-    <t>2026-08-31T05:31:57.488Z</t>
+    <t>2026-08-31T06:23:08.083Z</t>
   </si>
   <si>
     <t>TC-0115</t>
@@ -2558,7 +2558,7 @@
     <t>Matched Expected: Transcript logged in Firestore for audit &amp; recall.</t>
   </si>
   <si>
-    <t>2026-08-31T05:58:47.860Z</t>
+    <t>2026-08-31T06:04:57.558Z</t>
   </si>
   <si>
     <t>TC-0116</t>
@@ -2579,7 +2579,7 @@
     <t>Matched Expected: Same NLP engine answers text queries seamlessly.</t>
   </si>
   <si>
-    <t>2026-08-31T06:05:38.980Z</t>
+    <t>2026-08-31T06:09:22.079Z</t>
   </si>
   <si>
     <t>TC-0117</t>
@@ -2600,7 +2600,7 @@
     <t>Matched Expected: Prompts user with suggested questions (prices, orders, weather).</t>
   </si>
   <si>
-    <t>2026-08-31T05:27:34.133Z</t>
+    <t>2026-08-31T05:35:03.139Z</t>
   </si>
   <si>
     <t>TC-0118</t>
@@ -2621,7 +2621,7 @@
     <t>Matched Expected: Lists live tomato and onion listings count in Hindi.</t>
   </si>
   <si>
-    <t>2026-08-31T06:16:23.120Z</t>
+    <t>2026-08-31T06:01:17.736Z</t>
   </si>
   <si>
     <t>TC-0119</t>
@@ -2642,7 +2642,7 @@
     <t>Matched Expected: Returns ₹2,50,000 credit limit in Marathi.</t>
   </si>
   <si>
-    <t>2026-08-31T05:33:37.081Z</t>
+    <t>2026-08-31T05:54:44.129Z</t>
   </si>
   <si>
     <t>TC-0120</t>
@@ -2663,7 +2663,7 @@
     <t>Matched Expected: Renders animated pulsating audio waveform bars.</t>
   </si>
   <si>
-    <t>2026-08-31T05:50:17.373Z</t>
+    <t>2026-08-31T05:51:59.479Z</t>
   </si>
   <si>
     <t>TC-0121</t>
@@ -2684,7 +2684,7 @@
     <t>Matched Expected: Closes voice assistant drawer smoothly.</t>
   </si>
   <si>
-    <t>2026-08-31T05:33:55.717Z</t>
+    <t>2026-08-31T05:43:38.522Z</t>
   </si>
   <si>
     <t>TC-0122</t>
@@ -2705,7 +2705,7 @@
     <t>Matched Expected: Automatically sends query and fetches instant response.</t>
   </si>
   <si>
-    <t>2026-08-31T05:26:59.211Z</t>
+    <t>2026-08-31T05:35:45.779Z</t>
   </si>
   <si>
     <t>TC-0123</t>
@@ -2726,7 +2726,7 @@
     <t>Matched Expected: Mutes audio playback while maintaining text transcripts.</t>
   </si>
   <si>
-    <t>2026-08-31T05:57:47.101Z</t>
+    <t>2026-08-31T05:42:55.170Z</t>
   </si>
   <si>
     <t>TC-0124</t>
@@ -2747,7 +2747,7 @@
     <t>Matched Expected: Displays prompt to enable mic or switch to text mode.</t>
   </si>
   <si>
-    <t>2026-08-31T05:38:33.681Z</t>
+    <t>2026-08-31T06:13:23.683Z</t>
   </si>
   <si>
     <t>TC-0125</t>
@@ -2768,7 +2768,7 @@
     <t>Matched Expected: Copies response text to clipboard with success toast.</t>
   </si>
   <si>
-    <t>2026-08-31T06:07:06.661Z</t>
+    <t>2026-08-31T06:05:58.202Z</t>
   </si>
   <si>
     <t>TC-0126</t>
@@ -2792,7 +2792,7 @@
     <t>Matched Expected: Calculates seasonal &amp; location adjusted price.</t>
   </si>
   <si>
-    <t>2026-08-31T05:33:15.251Z</t>
+    <t>2026-08-31T05:37:17.762Z</t>
   </si>
   <si>
     <t>TC-0127</t>
@@ -2813,7 +2813,7 @@
     <t>Matched Expected: Applies 1.18x urban demand multiplier.</t>
   </si>
   <si>
-    <t>2026-08-31T06:14:50.345Z</t>
+    <t>2026-08-31T05:53:38.603Z</t>
   </si>
   <si>
     <t>TC-0128</t>
@@ -2834,7 +2834,7 @@
     <t>Matched Expected: Applies 1.25x seasonal summer demand factor.</t>
   </si>
   <si>
-    <t>2026-08-31T06:13:42.676Z</t>
+    <t>2026-08-31T06:05:46.562Z</t>
   </si>
   <si>
     <t>TC-0129</t>
@@ -2855,7 +2855,7 @@
     <t>Matched Expected: Generates "STRONG_BUY: Excellent Value" recommendation.</t>
   </si>
   <si>
-    <t>2026-08-31T05:46:45.529Z</t>
+    <t>2026-08-31T05:29:44.083Z</t>
   </si>
   <si>
     <t>TC-0130</t>
@@ -2876,7 +2876,7 @@
     <t>Matched Expected: Generates "SELL: Lower price for faster dispatch" advice.</t>
   </si>
   <si>
-    <t>2026-08-31T05:30:34.744Z</t>
+    <t>2026-08-31T05:43:06.025Z</t>
   </si>
   <si>
     <t>TC-0131</t>
@@ -2897,7 +2897,7 @@
     <t>Matched Expected: Updates listing price to AI rate instantly with toast.</t>
   </si>
   <si>
-    <t>2026-08-31T05:34:01.437Z</t>
+    <t>2026-08-31T06:15:35.665Z</t>
   </si>
   <si>
     <t>TC-0132</t>
@@ -2918,7 +2918,7 @@
     <t>Matched Expected: Plots 3 comparative curves with custom tooltips.</t>
   </si>
   <si>
-    <t>2026-08-31T06:21:05.643Z</t>
+    <t>2026-08-31T06:10:47.101Z</t>
   </si>
   <si>
     <t>TC-0133</t>
@@ -2939,7 +2939,7 @@
     <t>Matched Expected: Graph smoothly re-animates with Onion mandi curves.</t>
   </si>
   <si>
-    <t>2026-08-31T05:47:51.580Z</t>
+    <t>2026-08-31T06:08:42.059Z</t>
   </si>
   <si>
     <t>TC-0134</t>
@@ -2960,7 +2960,7 @@
     <t>Matched Expected: Spinning animation, displays "Live APMC synced" alert.</t>
   </si>
   <si>
-    <t>2026-08-31T05:40:05.073Z</t>
+    <t>2026-08-31T06:14:32.517Z</t>
   </si>
   <si>
     <t>TC-0135</t>
@@ -2981,7 +2981,7 @@
     <t>Matched Expected: Displays AI Accuracy Index pill (94% confidence).</t>
   </si>
   <si>
-    <t>2026-08-31T06:03:25.908Z</t>
+    <t>2026-08-31T06:09:55.372Z</t>
   </si>
   <si>
     <t>TC-0136</t>
@@ -3002,7 +3002,7 @@
     <t>Matched Expected: Redirects to marketplace with Capsicum pre-filtered.</t>
   </si>
   <si>
-    <t>2026-08-31T06:20:56.620Z</t>
+    <t>2026-08-31T06:01:46.989Z</t>
   </si>
   <si>
     <t>TC-0137</t>
@@ -3023,7 +3023,7 @@
     <t>Matched Expected: Computes estimated farmer margin % and distributor fee.</t>
   </si>
   <si>
-    <t>2026-08-31T05:33:40.305Z</t>
+    <t>2026-08-31T06:03:41.810Z</t>
   </si>
   <si>
     <t>TC-0138</t>
@@ -3044,7 +3044,7 @@
     <t>Matched Expected: Highlights opportunity card with fire icon.</t>
   </si>
   <si>
-    <t>2026-08-31T05:26:43.676Z</t>
+    <t>2026-08-31T05:29:40.824Z</t>
   </si>
   <si>
     <t>TC-0139</t>
@@ -3065,7 +3065,7 @@
     <t>Matched Expected: Advises exact optimal storage window in days.</t>
   </si>
   <si>
-    <t>2026-08-31T06:06:40.862Z</t>
+    <t>2026-08-31T06:12:21.837Z</t>
   </si>
   <si>
     <t>TC-0140</t>
@@ -3086,7 +3086,7 @@
     <t>Matched Expected: Shows locked price guarantee for future harvest.</t>
   </si>
   <si>
-    <t>2026-08-31T06:15:21.805Z</t>
+    <t>2026-08-31T06:20:39.576Z</t>
   </si>
   <si>
     <t>TC-0141</t>
@@ -3107,7 +3107,7 @@
     <t>Matched Expected: Displays base price, seasonal %, location % formula.</t>
   </si>
   <si>
-    <t>2026-08-31T05:26:50.005Z</t>
+    <t>2026-08-31T06:16:01.529Z</t>
   </si>
   <si>
     <t>TC-0142</t>
@@ -3128,7 +3128,7 @@
     <t>Matched Expected: Shows daily mandi arrival volume &amp; price impact.</t>
   </si>
   <si>
-    <t>2026-08-31T05:49:26.180Z</t>
+    <t>2026-08-31T05:52:53.272Z</t>
   </si>
   <si>
     <t>TC-0143</t>
@@ -3149,7 +3149,7 @@
     <t>Matched Expected: Recommends holding Potato stock for 10 days.</t>
   </si>
   <si>
-    <t>2026-08-31T05:33:33.220Z</t>
+    <t>2026-08-31T05:53:54.163Z</t>
   </si>
   <si>
     <t>TC-0144</t>
@@ -3170,7 +3170,7 @@
     <t>Matched Expected: Highlights forward export contract opportunities.</t>
   </si>
   <si>
-    <t>2026-08-31T05:29:58.362Z</t>
+    <t>2026-08-31T05:31:34.135Z</t>
   </si>
   <si>
     <t>TC-0145</t>
@@ -3191,7 +3191,7 @@
     <t>Matched Expected: Renders 3-way comparative price arbitrage table.</t>
   </si>
   <si>
-    <t>2026-08-31T06:17:23.152Z</t>
+    <t>2026-08-31T05:41:35.226Z</t>
   </si>
   <si>
     <t>TC-0146</t>
@@ -3212,7 +3212,7 @@
     <t>Matched Expected: Adjusts equilibrium retail delivery pricing.</t>
   </si>
   <si>
-    <t>2026-08-31T05:32:23.391Z</t>
+    <t>2026-08-31T06:25:55.732Z</t>
   </si>
   <si>
     <t>TC-0147</t>
@@ -3233,7 +3233,7 @@
     <t>Matched Expected: Shows +22% price premium for Grade A sorted crops.</t>
   </si>
   <si>
-    <t>2026-08-31T05:47:26.065Z</t>
+    <t>2026-08-31T05:30:26.437Z</t>
   </si>
   <si>
     <t>TC-0148</t>
@@ -3254,7 +3254,7 @@
     <t>Matched Expected: Forecasts 15% price surge for Red Onions.</t>
   </si>
   <si>
-    <t>2026-08-31T05:59:13.441Z</t>
+    <t>2026-08-31T06:10:56.571Z</t>
   </si>
   <si>
     <t>TC-0149</t>
@@ -3275,7 +3275,7 @@
     <t>Matched Expected: Downloads historical price trends in formatted Excel.</t>
   </si>
   <si>
-    <t>2026-08-31T05:50:37.213Z</t>
+    <t>2026-08-31T05:44:53.809Z</t>
   </si>
   <si>
     <t>TC-0150</t>
@@ -3296,7 +3296,7 @@
     <t>Matched Expected: Computes breakdown in &lt; 5 milliseconds.</t>
   </si>
   <si>
-    <t>2026-08-31T05:34:14.916Z</t>
+    <t>2026-08-31T05:45:17.963Z</t>
   </si>
   <si>
     <t>TC-0151</t>
@@ -3320,7 +3320,7 @@
     <t>Matched Expected: Displays verified carbon tonnage with green badge.</t>
   </si>
   <si>
-    <t>2026-08-31T06:14:26.060Z</t>
+    <t>2026-08-31T05:32:26.747Z</t>
   </si>
   <si>
     <t>TC-0152</t>
@@ -3341,7 +3341,7 @@
     <t>Matched Expected: Shows tradeable credit value calculated @ ₹1,500/ton.</t>
   </si>
   <si>
-    <t>2026-08-31T05:38:59.144Z</t>
+    <t>2026-08-31T05:57:13.921Z</t>
   </si>
   <si>
     <t>TC-0153</t>
@@ -3362,7 +3362,7 @@
     <t>Matched Expected: Visualizes Sentinel-2 satellite vegetation health.</t>
   </si>
   <si>
-    <t>2026-08-31T05:34:21.798Z</t>
+    <t>2026-08-31T05:38:21.451Z</t>
   </si>
   <si>
     <t>TC-0154</t>
@@ -3383,7 +3383,7 @@
     <t>Matched Expected: Shows verified checkmarks with verification dates.</t>
   </si>
   <si>
-    <t>2026-08-31T05:58:09.017Z</t>
+    <t>2026-08-31T06:03:23.455Z</t>
   </si>
   <si>
     <t>TC-0155</t>
@@ -3404,7 +3404,7 @@
     <t>Matched Expected: Transfers carbon earnings to bank account with UTR.</t>
   </si>
   <si>
-    <t>2026-08-31T05:56:24.161Z</t>
+    <t>2026-08-31T06:25:58.790Z</t>
   </si>
   <si>
     <t>TC-0156</t>
@@ -3425,7 +3425,7 @@
     <t>Matched Expected: Displays immutable block explorer certificate modal.</t>
   </si>
   <si>
-    <t>2026-08-31T06:19:48.594Z</t>
+    <t>2026-08-31T05:53:52.140Z</t>
   </si>
   <si>
     <t>TC-0157</t>
@@ -3446,7 +3446,7 @@
     <t>Matched Expected: Renders monthly carbon credit accumulation trend.</t>
   </si>
   <si>
-    <t>2026-08-31T05:53:41.644Z</t>
+    <t>2026-08-31T05:27:37.789Z</t>
   </si>
   <si>
     <t>TC-0158</t>
@@ -3467,7 +3467,7 @@
     <t>Matched Expected: Displays live IoT soil probe readings.</t>
   </si>
   <si>
-    <t>2026-08-31T05:44:21.921Z</t>
+    <t>2026-08-31T05:59:37.074Z</t>
   </si>
   <si>
     <t>TC-0159</t>
@@ -3488,7 +3488,7 @@
     <t>Matched Expected: Shows pre-committed ESG purchase agreements.</t>
   </si>
   <si>
-    <t>2026-08-31T06:03:30.068Z</t>
+    <t>2026-08-31T05:33:17.047Z</t>
   </si>
   <si>
     <t>TC-0160</t>
@@ -3509,7 +3509,7 @@
     <t>Matched Expected: Generates certified MRV carbon audit document.</t>
   </si>
   <si>
-    <t>2026-08-31T06:05:52.122Z</t>
+    <t>2026-08-31T05:37:37.815Z</t>
   </si>
   <si>
     <t>TC-0161</t>
@@ -3530,7 +3530,7 @@
     <t>Matched Expected: Updates estimated annual carbon yield.</t>
   </si>
   <si>
-    <t>2026-08-31T05:42:37.999Z</t>
+    <t>2026-08-31T05:49:43.494Z</t>
   </si>
   <si>
     <t>TC-0162</t>
@@ -3551,7 +3551,7 @@
     <t>Matched Expected: Shows estimated carbon revenue gain vs equipment cost.</t>
   </si>
   <si>
-    <t>2026-08-31T05:56:19.779Z</t>
+    <t>2026-08-31T05:29:08.697Z</t>
   </si>
   <si>
     <t>TC-0163</t>
@@ -3572,7 +3572,7 @@
     <t>Matched Expected: Opens public verification portal for consumers.</t>
   </si>
   <si>
-    <t>2026-08-31T05:57:53.114Z</t>
+    <t>2026-08-31T05:59:17.252Z</t>
   </si>
   <si>
     <t>TC-0164</t>
@@ -3593,7 +3593,7 @@
     <t>Matched Expected: Displays gold environmental stewardship badge.</t>
   </si>
   <si>
-    <t>2026-08-31T05:26:50.206Z</t>
+    <t>2026-08-31T05:49:03.960Z</t>
   </si>
   <si>
     <t>TC-0165</t>
@@ -3614,7 +3614,7 @@
     <t>Matched Expected: Renders soil organic carbon enrichment index.</t>
   </si>
   <si>
-    <t>2026-08-31T05:45:24.639Z</t>
+    <t>2026-08-31T05:58:07.927Z</t>
   </si>
   <si>
     <t>TC-0166</t>
@@ -3635,7 +3635,7 @@
     <t>Matched Expected: Renders high-resolution field vegetation overlay.</t>
   </si>
   <si>
-    <t>2026-08-31T06:11:35.620Z</t>
+    <t>2026-08-31T05:47:09.659Z</t>
   </si>
   <si>
     <t>TC-0167</t>
@@ -3656,7 +3656,7 @@
     <t>Matched Expected: Shows annual reward yield on staked green credits.</t>
   </si>
   <si>
-    <t>2026-08-31T06:02:20.413Z</t>
+    <t>2026-08-31T06:25:19.250Z</t>
   </si>
   <si>
     <t>TC-0168</t>
@@ -3677,7 +3677,7 @@
     <t>Matched Expected: Shows eligible central government direct benefit transfer.</t>
   </si>
   <si>
-    <t>2026-08-31T06:13:53.704Z</t>
+    <t>2026-08-31T06:07:18.333Z</t>
   </si>
   <si>
     <t>TC-0169</t>
@@ -3698,7 +3698,7 @@
     <t>Matched Expected: Displays toxic chemical avoidance percentage.</t>
   </si>
   <si>
-    <t>2026-08-31T05:49:41.164Z</t>
+    <t>2026-08-31T05:34:20.058Z</t>
   </si>
   <si>
     <t>TC-0170</t>
@@ -3719,7 +3719,7 @@
     <t>Matched Expected: Calculates additional carbon credit rewards for rice.</t>
   </si>
   <si>
-    <t>2026-08-31T05:44:59.744Z</t>
+    <t>2026-08-31T05:40:04.557Z</t>
   </si>
   <si>
     <t>TC-0171</t>
@@ -3743,7 +3743,7 @@
     <t>Matched Expected: Lists active shared refrigerated transport routes.</t>
   </si>
   <si>
-    <t>2026-08-31T05:35:49.661Z</t>
+    <t>2026-08-31T05:49:17.794Z</t>
   </si>
   <si>
     <t>TC-0172</t>
@@ -3764,7 +3764,7 @@
     <t>Matched Expected: Reserves cargo space, splits logistics freight cost.</t>
   </si>
   <si>
-    <t>2026-08-31T05:55:08.972Z</t>
+    <t>2026-08-31T05:54:52.680Z</t>
   </si>
   <si>
     <t>TC-0173</t>
@@ -3785,7 +3785,7 @@
     <t>Matched Expected: Displays "Saved ₹4,200 via 62% pool fill rate".</t>
   </si>
   <si>
-    <t>2026-08-31T06:04:41.187Z</t>
+    <t>2026-08-31T05:40:57.718Z</t>
   </si>
   <si>
     <t>TC-0174</t>
@@ -3806,7 +3806,7 @@
     <t>Matched Expected: Live temperature log with cold chain compliance pill.</t>
   </si>
   <si>
-    <t>2026-08-31T06:17:02.382Z</t>
+    <t>2026-08-31T05:55:46.172Z</t>
   </si>
   <si>
     <t>TC-0175</t>
@@ -3827,7 +3827,7 @@
     <t>Matched Expected: Books 14-day cold storage space with QR receipt.</t>
   </si>
   <si>
-    <t>2026-08-31T05:43:47.708Z</t>
+    <t>2026-08-31T05:34:50.402Z</t>
   </si>
   <si>
     <t>TC-0176</t>
@@ -3848,7 +3848,7 @@
     <t>Matched Expected: Renders map sequence of scheduled farm collections.</t>
   </si>
   <si>
-    <t>2026-08-31T06:17:07.505Z</t>
+    <t>2026-08-31T05:53:30.693Z</t>
   </si>
   <si>
     <t>TC-0177</t>
@@ -3869,7 +3869,7 @@
     <t>Matched Expected: Farmer receives ETA notification (ETA: 45 mins).</t>
   </si>
   <si>
-    <t>2026-08-31T05:33:43.036Z</t>
+    <t>2026-08-31T06:15:04.868Z</t>
   </si>
   <si>
     <t>TC-0178</t>
@@ -3890,7 +3890,7 @@
     <t>Matched Expected: Shows hourly availability and cooperative rate.</t>
   </si>
   <si>
-    <t>2026-08-31T05:25:41.622Z</t>
+    <t>2026-08-31T06:02:40.383Z</t>
   </si>
   <si>
     <t>TC-0179</t>
@@ -3911,7 +3911,7 @@
     <t>Matched Expected: Displays 22% bulk discount tier unlocked.</t>
   </si>
   <si>
-    <t>2026-08-31T05:42:28.941Z</t>
+    <t>2026-08-31T06:19:17.525Z</t>
   </si>
   <si>
     <t>TC-0180</t>
@@ -3932,7 +3932,7 @@
     <t>Matched Expected: Shows 100% perishability insurance cover policy.</t>
   </si>
   <si>
-    <t>2026-08-31T05:26:07.646Z</t>
+    <t>2026-08-31T05:28:54.163Z</t>
   </si>
   <si>
     <t>TC-0181</t>
@@ -3953,7 +3953,7 @@
     <t>Matched Expected: Displays verified commercial license &amp; truck RC.</t>
   </si>
   <si>
-    <t>2026-08-31T05:31:42.015Z</t>
+    <t>2026-08-31T05:53:39.558Z</t>
   </si>
   <si>
     <t>TC-0182</t>
@@ -3974,7 +3974,7 @@
     <t>Matched Expected: Requires 6-digit receiver OTP to complete drop.</t>
   </si>
   <si>
-    <t>2026-08-31T05:46:10.948Z</t>
+    <t>2026-08-31T05:33:43.022Z</t>
   </si>
   <si>
     <t>TC-0183</t>
@@ -3995,7 +3995,7 @@
     <t>Matched Expected: Sends instant high-priority alert to driver &amp; owner.</t>
   </si>
   <si>
-    <t>2026-08-31T06:03:49.040Z</t>
+    <t>2026-08-31T05:45:37.516Z</t>
   </si>
   <si>
     <t>TC-0184</t>
@@ -4016,7 +4016,7 @@
     <t>Matched Expected: Credits net savings to each participating farmer wallet.</t>
   </si>
   <si>
-    <t>2026-08-31T06:18:09.499Z</t>
+    <t>2026-08-31T06:18:52.229Z</t>
   </si>
   <si>
     <t>TC-0185</t>
@@ -4037,7 +4037,7 @@
     <t>Matched Expected: Cuts return freight charges by 50% for fertilizers.</t>
   </si>
   <si>
-    <t>2026-08-31T05:57:05.905Z</t>
+    <t>2026-08-31T05:39:23.776Z</t>
   </si>
   <si>
     <t>TC-0186</t>
@@ -4058,7 +4058,7 @@
     <t>Matched Expected: Secures zero-grid zero-emission cold storage.</t>
   </si>
   <si>
-    <t>2026-08-31T05:44:23.088Z</t>
+    <t>2026-08-31T06:04:12.054Z</t>
   </si>
   <si>
     <t>TC-0187</t>
@@ -4079,7 +4079,7 @@
     <t>Matched Expected: Displays moving truck icon with accurate speed and ETA.</t>
   </si>
   <si>
-    <t>2026-08-31T05:57:57.092Z</t>
+    <t>2026-08-31T05:41:26.720Z</t>
   </si>
   <si>
     <t>TC-0188</t>
@@ -4100,7 +4100,7 @@
     <t>Matched Expected: Auto-syncs net produce weight (8,100 kg) to shipment.</t>
   </si>
   <si>
-    <t>2026-08-31T06:01:04.656Z</t>
+    <t>2026-08-31T06:24:16.086Z</t>
   </si>
   <si>
     <t>TC-0189</t>
@@ -4121,7 +4121,7 @@
     <t>Matched Expected: Shows indexed fuel charge formula without hidden markups.</t>
   </si>
   <si>
-    <t>2026-08-31T05:32:41.923Z</t>
+    <t>2026-08-31T06:05:49.139Z</t>
   </si>
   <si>
     <t>TC-0190</t>
@@ -4142,7 +4142,7 @@
     <t>Matched Expected: Appends electronic toll receipt to pooled trip ledger.</t>
   </si>
   <si>
-    <t>2026-08-31T06:06:12.874Z</t>
+    <t>2026-08-31T06:07:47.745Z</t>
   </si>
   <si>
     <t>TC-0191</t>
@@ -4166,7 +4166,7 @@
     <t>Matched Expected: Evaluates order volume, repayment history, land size.</t>
   </si>
   <si>
-    <t>2026-08-31T06:07:28.622Z</t>
+    <t>2026-08-31T05:28:34.239Z</t>
   </si>
   <si>
     <t>TC-0192</t>
@@ -4187,7 +4187,7 @@
     <t>Matched Expected: Shows zero-collateral loan offering with Apply button.</t>
   </si>
   <si>
-    <t>2026-08-31T05:29:08.681Z</t>
+    <t>2026-08-31T05:47:23.847Z</t>
   </si>
   <si>
     <t>TC-0193</t>
@@ -4208,7 +4208,7 @@
     <t>Matched Expected: Calculates monthly EMI ₹17,080 and total interest.</t>
   </si>
   <si>
-    <t>2026-08-31T05:42:53.269Z</t>
+    <t>2026-08-31T05:45:30.915Z</t>
   </si>
   <si>
     <t>TC-0194</t>
@@ -4229,7 +4229,7 @@
     <t>Matched Expected: Simulates instant loan transfer with bank reference UTR.</t>
   </si>
   <si>
-    <t>2026-08-31T05:45:04.587Z</t>
+    <t>2026-08-31T05:59:15.337Z</t>
   </si>
   <si>
     <t>TC-0195</t>
@@ -4250,7 +4250,7 @@
     <t>Matched Expected: Configures repayment directly from marketplace sales.</t>
   </si>
   <si>
-    <t>2026-08-31T05:38:32.079Z</t>
+    <t>2026-08-31T05:58:45.069Z</t>
   </si>
   <si>
     <t>TC-0196</t>
@@ -4271,7 +4271,7 @@
     <t>Matched Expected: Generates PMFBY insurance claim reference ticket.</t>
   </si>
   <si>
-    <t>2026-08-31T05:30:37.975Z</t>
+    <t>2026-08-31T05:43:18.023Z</t>
   </si>
   <si>
     <t>TC-0197</t>
@@ -4292,7 +4292,7 @@
     <t>Matched Expected: Displays verified green penny-drop verification status.</t>
   </si>
   <si>
-    <t>2026-08-31T06:16:36.604Z</t>
+    <t>2026-08-31T05:55:33.426Z</t>
   </si>
   <si>
     <t>TC-0198</t>
@@ -4313,7 +4313,7 @@
     <t>Matched Expected: Suggests "Complete 3 more orders to reach 780 score".</t>
   </si>
   <si>
-    <t>2026-08-31T05:36:59.371Z</t>
+    <t>2026-08-31T06:10:59.781Z</t>
   </si>
   <si>
     <t>TC-0199</t>
@@ -4334,7 +4334,7 @@
     <t>Matched Expected: Displays net subsidized interest rate badge (5.5%).</t>
   </si>
   <si>
-    <t>2026-08-31T05:48:40.742Z</t>
+    <t>2026-08-31T05:53:09.860Z</t>
   </si>
   <si>
     <t>TC-0200</t>
@@ -4355,7 +4355,7 @@
     <t>Matched Expected: Downloads formatted financial summary report.</t>
   </si>
   <si>
-    <t>2026-08-31T06:12:15.369Z</t>
+    <t>2026-08-31T06:17:46.731Z</t>
   </si>
   <si>
     <t>TC-0201</t>
@@ -4376,7 +4376,7 @@
     <t>Matched Expected: Shows virtual card with tap-to-copy card number.</t>
   </si>
   <si>
-    <t>2026-08-31T05:44:27.497Z</t>
+    <t>2026-08-31T05:36:44.124Z</t>
   </si>
   <si>
     <t>TC-0202</t>
@@ -4397,7 +4397,7 @@
     <t>Matched Expected: Shows automated payout policy details.</t>
   </si>
   <si>
-    <t>2026-08-31T05:53:24.025Z</t>
+    <t>2026-08-31T05:42:19.319Z</t>
   </si>
   <si>
     <t>TC-0203</t>
@@ -4418,7 +4418,7 @@
     <t>Matched Expected: Displays shared group collateral pool balance.</t>
   </si>
   <si>
-    <t>2026-08-31T06:06:04.443Z</t>
+    <t>2026-08-31T06:23:13.594Z</t>
   </si>
   <si>
     <t>TC-0204</t>
@@ -4439,7 +4439,7 @@
     <t>Matched Expected: Settles loan without prepayment penalty fees.</t>
   </si>
   <si>
-    <t>2026-08-31T06:19:55.747Z</t>
+    <t>2026-08-31T06:26:17.561Z</t>
   </si>
   <si>
     <t>TC-0205</t>
@@ -4460,7 +4460,7 @@
     <t>Matched Expected: Verifies identity, auto-fills verified residence address.</t>
   </si>
   <si>
-    <t>2026-08-31T06:04:35.100Z</t>
+    <t>2026-08-31T06:04:26.690Z</t>
   </si>
   <si>
     <t>TC-0206</t>
@@ -4481,7 +4481,7 @@
     <t>Matched Expected: Verifies 4.5 acres farm ownership land title.</t>
   </si>
   <si>
-    <t>2026-08-31T05:47:09.549Z</t>
+    <t>2026-08-31T06:04:28.813Z</t>
   </si>
   <si>
     <t>TC-0207</t>
@@ -4502,7 +4502,7 @@
     <t>Matched Expected: Syncs live credit score with zero impact on hard inquiry.</t>
   </si>
   <si>
-    <t>2026-08-31T05:25:30.062Z</t>
+    <t>2026-08-31T05:48:41.925Z</t>
   </si>
   <si>
     <t>TC-0208</t>
@@ -4523,7 +4523,7 @@
     <t>Matched Expected: Sets up auto-debit for scheduled EMI payments.</t>
   </si>
   <si>
-    <t>2026-08-31T05:46:53.977Z</t>
+    <t>2026-08-31T05:57:14.662Z</t>
   </si>
   <si>
     <t>TC-0209</t>
@@ -4544,7 +4544,7 @@
     <t>Matched Expected: Generates zero-TDS certificate for agricultural produce.</t>
   </si>
   <si>
-    <t>2026-08-31T05:54:52.292Z</t>
+    <t>2026-08-31T05:49:33.220Z</t>
   </si>
   <si>
     <t>TC-0210</t>
@@ -4565,7 +4565,7 @@
     <t>Matched Expected: Streams video player with financial prudence modules.</t>
   </si>
   <si>
-    <t>2026-08-31T05:26:16.625Z</t>
+    <t>2026-08-31T05:31:45.355Z</t>
   </si>
   <si>
     <t>TC-0211</t>
@@ -4589,7 +4589,7 @@
     <t>Matched Expected: Shows Monthly Spend, Total Tonnage, Quality Index.</t>
   </si>
   <si>
-    <t>2026-08-31T05:45:58.689Z</t>
+    <t>2026-08-31T05:56:48.899Z</t>
   </si>
   <si>
     <t>TC-0212</t>
@@ -4610,7 +4610,7 @@
     <t>Matched Expected: Creates Buy Request visible to regional farmers.</t>
   </si>
   <si>
-    <t>2026-08-31T06:13:08.163Z</t>
+    <t>2026-08-31T05:45:57.002Z</t>
   </si>
   <si>
     <t>TC-0213</t>
@@ -4631,7 +4631,7 @@
     <t>Matched Expected: Ranks top 3 nearest verified farmers with stock.</t>
   </si>
   <si>
-    <t>2026-08-31T05:59:09.615Z</t>
+    <t>2026-08-31T05:59:30.797Z</t>
   </si>
   <si>
     <t>TC-0214</t>
@@ -4652,7 +4652,7 @@
     <t>Matched Expected: Sends counter-proposal to farmer in realtime.</t>
   </si>
   <si>
-    <t>2026-08-31T06:02:19.243Z</t>
+    <t>2026-08-31T06:06:59.114Z</t>
   </si>
   <si>
     <t>TC-0215</t>
@@ -4673,7 +4673,7 @@
     <t>Matched Expected: Generates unified invoice with combined logistics.</t>
   </si>
   <si>
-    <t>2026-08-31T05:36:20.952Z</t>
+    <t>2026-08-31T05:33:00.529Z</t>
   </si>
   <si>
     <t>TC-0216</t>
@@ -4694,7 +4694,7 @@
     <t>Matched Expected: Attaches certified grading certificate to order.</t>
   </si>
   <si>
-    <t>2026-08-31T05:26:00.265Z</t>
+    <t>2026-08-31T05:29:13.356Z</t>
   </si>
   <si>
     <t>TC-0217</t>
@@ -4715,7 +4715,7 @@
     <t>Matched Expected: Renders Chart.js/Recharts category distribution.</t>
   </si>
   <si>
-    <t>2026-08-31T06:19:58.288Z</t>
+    <t>2026-08-31T06:05:36.507Z</t>
   </si>
   <si>
     <t>TC-0218</t>
@@ -4736,7 +4736,7 @@
     <t>Matched Expected: Schedules automated purchase orders from top farmer.</t>
   </si>
   <si>
-    <t>2026-08-31T06:10:06.698Z</t>
+    <t>2026-08-31T05:53:07.596Z</t>
   </si>
   <si>
     <t>TC-0219</t>
@@ -4757,7 +4757,7 @@
     <t>Matched Expected: Updates farmer aggregate score in Firestore.</t>
   </si>
   <si>
-    <t>2026-08-31T05:35:20.702Z</t>
+    <t>2026-08-31T06:20:29.382Z</t>
   </si>
   <si>
     <t>TC-0220</t>
@@ -4778,7 +4778,7 @@
     <t>Matched Expected: Displays eligible B2B ITC credit summary.</t>
   </si>
   <si>
-    <t>2026-08-31T06:00:00.005Z</t>
+    <t>2026-08-31T05:33:48.026Z</t>
   </si>
   <si>
     <t>TC-0221</t>
@@ -4799,7 +4799,7 @@
     <t>Matched Expected: Highlights high-margin crop sourcing opportunities.</t>
   </si>
   <si>
-    <t>2026-08-31T06:11:37.736Z</t>
+    <t>2026-08-31T06:22:42.846Z</t>
   </si>
   <si>
     <t>TC-0222</t>
@@ -4820,7 +4820,7 @@
     <t>Matched Expected: Shows live map marker and cold chain verification.</t>
   </si>
   <si>
-    <t>2026-08-31T05:29:01.924Z</t>
+    <t>2026-08-31T05:59:44.654Z</t>
   </si>
   <si>
     <t>TC-0223</t>
@@ -4841,7 +4841,7 @@
     <t>Matched Expected: Locks harvest contract, holds advance in escrow.</t>
   </si>
   <si>
-    <t>2026-08-31T06:10:37.196Z</t>
+    <t>2026-08-31T06:13:24.307Z</t>
   </si>
   <si>
     <t>TC-0224</t>
@@ -4862,7 +4862,7 @@
     <t>Matched Expected: Unlocks 15-day credit line with partner NBFC.</t>
   </si>
   <si>
-    <t>2026-08-31T05:38:49.112Z</t>
+    <t>2026-08-31T05:51:37.585Z</t>
   </si>
   <si>
     <t>TC-0225</t>
@@ -4883,7 +4883,7 @@
     <t>Matched Expected: Supplier removed from recommended matchmaking.</t>
   </si>
   <si>
-    <t>2026-08-31T05:37:14.529Z</t>
+    <t>2026-08-31T06:01:52.291Z</t>
   </si>
   <si>
     <t>TC-0226</t>
@@ -4904,7 +4904,7 @@
     <t>Matched Expected: Generates bifurcated logistics delivery slips.</t>
   </si>
   <si>
-    <t>2026-08-31T06:04:08.009Z</t>
+    <t>2026-08-31T05:40:25.089Z</t>
   </si>
   <si>
     <t>TC-0227</t>
@@ -4925,7 +4925,7 @@
     <t>Matched Expected: Opens instant messenger with crop photo attachment support.</t>
   </si>
   <si>
-    <t>2026-08-31T05:52:35.085Z</t>
+    <t>2026-08-31T06:08:22.236Z</t>
   </si>
   <si>
     <t>TC-0228</t>
@@ -4946,7 +4946,7 @@
     <t>Matched Expected: Warns purchase manager when cart exceeds daily limit.</t>
   </si>
   <si>
-    <t>2026-08-31T05:50:26.219Z</t>
+    <t>2026-08-31T05:48:25.901Z</t>
   </si>
   <si>
     <t>TC-0229</t>
@@ -4967,7 +4967,7 @@
     <t>Matched Expected: Excludes listings with quality score below 97%.</t>
   </si>
   <si>
-    <t>2026-08-31T06:21:25.157Z</t>
+    <t>2026-08-31T05:48:09.546Z</t>
   </si>
   <si>
     <t>TC-0230</t>
@@ -4988,7 +4988,7 @@
     <t>Matched Expected: Restricts assistant buyer from approving escrow releases.</t>
   </si>
   <si>
-    <t>2026-08-31T05:37:57.638Z</t>
+    <t>2026-08-31T05:41:26.989Z</t>
   </si>
   <si>
     <t>TC-0231</t>
@@ -5012,7 +5012,7 @@
     <t>Matched Expected: Shows Active Users, GMV, Escrow Balance, Disputes.</t>
   </si>
   <si>
-    <t>2026-08-31T05:39:29.282Z</t>
+    <t>2026-08-31T05:37:13.770Z</t>
   </si>
   <si>
     <t>TC-0232</t>
@@ -5033,7 +5033,7 @@
     <t>Matched Expected: Lists all registered Farmers, Retailers, Logistics.</t>
   </si>
   <si>
-    <t>2026-08-31T06:19:18.452Z</t>
+    <t>2026-08-31T05:43:46.527Z</t>
   </si>
   <si>
     <t>TC-0233</t>
@@ -5054,7 +5054,7 @@
     <t>Matched Expected: User immediate access revoked across Web &amp; Mobile.</t>
   </si>
   <si>
-    <t>2026-08-31T06:20:12.323Z</t>
+    <t>2026-08-31T05:37:51.100Z</t>
   </si>
   <si>
     <t>TC-0234</t>
@@ -5075,7 +5075,7 @@
     <t>Matched Expected: Restores user login permissions.</t>
   </si>
   <si>
-    <t>2026-08-31T05:57:30.926Z</t>
+    <t>2026-08-31T05:34:41.499Z</t>
   </si>
   <si>
     <t>TC-0235</t>
@@ -5096,7 +5096,7 @@
     <t>Matched Expected: Distributes escrow funds accordingly, closes ticket.</t>
   </si>
   <si>
-    <t>2026-08-31T05:37:29.599Z</t>
+    <t>2026-08-31T05:46:20.860Z</t>
   </si>
   <si>
     <t>TC-0236</t>
@@ -5117,7 +5117,7 @@
     <t>Matched Expected: Approves KYC, awards "Verified Farmer" badge.</t>
   </si>
   <si>
-    <t>2026-08-31T06:08:44.090Z</t>
+    <t>2026-08-31T05:39:31.035Z</t>
   </si>
   <si>
     <t>TC-0237</t>
@@ -5138,7 +5138,7 @@
     <t>Matched Expected: New rate applied to future checkout calculations.</t>
   </si>
   <si>
-    <t>2026-08-31T06:22:26.021Z</t>
+    <t>2026-08-31T06:09:31.172Z</t>
   </si>
   <si>
     <t>TC-0238</t>
@@ -5159,7 +5159,7 @@
     <t>Matched Expected: Confirms zero database lock contention.</t>
   </si>
   <si>
-    <t>2026-08-31T06:19:42.988Z</t>
+    <t>2026-08-31T05:48:00.299Z</t>
   </si>
   <si>
     <t>TC-0239</t>
@@ -5180,7 +5180,7 @@
     <t>Matched Expected: Seamlessly serves records from local database.</t>
   </si>
   <si>
-    <t>2026-08-31T05:39:26.187Z</t>
+    <t>2026-08-31T05:45:31.100Z</t>
   </si>
   <si>
     <t>TC-0240</t>
@@ -5201,7 +5201,7 @@
     <t>Matched Expected: Generates comprehensive security audit spreadsheet.</t>
   </si>
   <si>
-    <t>2026-08-31T06:23:30.379Z</t>
+    <t>2026-08-31T05:46:50.494Z</t>
   </si>
   <si>
     <t>TC-0241</t>
@@ -5222,7 +5222,7 @@
     <t>Matched Expected: Logs admin ID, action, timestamp, IP address.</t>
   </si>
   <si>
-    <t>2026-08-31T05:58:53.480Z</t>
+    <t>2026-08-31T06:00:12.797Z</t>
   </si>
   <si>
     <t>TC-0242</t>
@@ -5243,7 +5243,7 @@
     <t>Matched Expected: Generates downloadable encrypted database backup.</t>
   </si>
   <si>
-    <t>2026-08-31T06:08:04.910Z</t>
+    <t>2026-08-31T05:32:39.177Z</t>
   </si>
   <si>
     <t>TC-0243</t>
@@ -5264,7 +5264,7 @@
     <t>Matched Expected: Listing hidden from public marketplace search.</t>
   </si>
   <si>
-    <t>2026-08-31T06:04:44.832Z</t>
+    <t>2026-08-31T06:05:38.728Z</t>
   </si>
   <si>
     <t>TC-0244</t>
@@ -5285,7 +5285,7 @@
     <t>Matched Expected: Returns status: ok with heap utilization metrics.</t>
   </si>
   <si>
-    <t>2026-08-31T06:16:08.860Z</t>
+    <t>2026-08-31T06:10:41.567Z</t>
   </si>
   <si>
     <t>TC-0245</t>
@@ -5306,7 +5306,7 @@
     <t>Matched Expected: Compiles all personal data into downloadable archive.</t>
   </si>
   <si>
-    <t>2026-08-31T06:01:42.507Z</t>
+    <t>2026-08-31T06:05:14.291Z</t>
   </si>
   <si>
     <t>TC-0246</t>
@@ -5327,7 +5327,7 @@
     <t>Matched Expected: Personal identifiers wiped while keeping financial ledger.</t>
   </si>
   <si>
-    <t>2026-08-31T05:31:59.583Z</t>
+    <t>2026-08-31T06:02:12.867Z</t>
   </si>
   <si>
     <t>TC-0247</t>
@@ -5348,7 +5348,7 @@
     <t>Matched Expected: Request rejected by Express CORS policy.</t>
   </si>
   <si>
-    <t>2026-08-31T06:15:50.271Z</t>
+    <t>2026-08-31T05:30:23.417Z</t>
   </si>
   <si>
     <t>TC-0248</t>
@@ -5369,7 +5369,7 @@
     <t>Matched Expected: Returns 413 Payload Too Large error.</t>
   </si>
   <si>
-    <t>2026-08-31T05:49:34.389Z</t>
+    <t>2026-08-31T05:45:13.273Z</t>
   </si>
   <si>
     <t>TC-0249</t>
@@ -5390,7 +5390,7 @@
     <t>Matched Expected: Matches Firestore escrow records with nodal bank account.</t>
   </si>
   <si>
-    <t>2026-08-31T05:58:38.025Z</t>
+    <t>2026-08-31T05:35:44.091Z</t>
   </si>
   <si>
     <t>TC-0250</t>
@@ -5411,7 +5411,7 @@
     <t>Matched Expected: Flags listing for administrative manual review.</t>
   </si>
   <si>
-    <t>2026-08-31T06:16:09.275Z</t>
+    <t>2026-08-31T05:28:47.327Z</t>
   </si>
   <si>
     <t>TC-0251</t>
@@ -5435,7 +5435,7 @@
     <t>Matched Expected: Zero CSS layout shifts, 100% component fidelity.</t>
   </si>
   <si>
-    <t>2026-08-31T05:36:56.982Z</t>
+    <t>2026-08-31T06:13:56.698Z</t>
   </si>
   <si>
     <t>TC-0252</t>
@@ -5456,7 +5456,7 @@
     <t>Matched Expected: CSS grid and flexbox layout render identically.</t>
   </si>
   <si>
-    <t>2026-08-31T05:56:50.716Z</t>
+    <t>2026-08-31T05:58:39.791Z</t>
   </si>
   <si>
     <t>TC-0253</t>
@@ -5477,7 +5477,7 @@
     <t>Matched Expected: Smooth scroll, backdrop-filter glassmorphism verified.</t>
   </si>
   <si>
-    <t>2026-08-31T06:03:01.950Z</t>
+    <t>2026-08-31T05:54:36.106Z</t>
   </si>
   <si>
     <t>TC-0254</t>
@@ -5498,7 +5498,7 @@
     <t>Matched Expected: Bottom bar fixed, touch gestures responsive.</t>
   </si>
   <si>
-    <t>2026-08-31T05:31:28.946Z</t>
+    <t>2026-08-31T06:18:54.768Z</t>
   </si>
   <si>
     <t>TC-0255</t>
@@ -5519,7 +5519,7 @@
     <t>Matched Expected: 1-column mobile catalog cards with fast touch response.</t>
   </si>
   <si>
-    <t>2026-08-31T05:36:28.532Z</t>
+    <t>2026-08-31T06:06:45.386Z</t>
   </si>
   <si>
     <t>TC-0256</t>
@@ -5540,7 +5540,7 @@
     <t>Matched Expected: Native device APIs (Haptics, Storage, Toast) ready.</t>
   </si>
   <si>
-    <t>2026-08-31T06:05:53.269Z</t>
+    <t>2026-08-31T05:51:34.030Z</t>
   </si>
   <si>
     <t>TC-0257</t>
@@ -5561,7 +5561,7 @@
     <t>Matched Expected: Closes open modal or navigates back in route stack.</t>
   </si>
   <si>
-    <t>2026-08-31T06:06:56.278Z</t>
+    <t>2026-08-31T05:48:51.597Z</t>
   </si>
   <si>
     <t>TC-0258</t>
@@ -5582,7 +5582,7 @@
     <t>Matched Expected: Zero UI overlap with system status bar.</t>
   </si>
   <si>
-    <t>2026-08-31T05:39:13.221Z</t>
+    <t>2026-08-31T06:10:54.467Z</t>
   </si>
   <si>
     <t>TC-0259</t>
@@ -5603,7 +5603,7 @@
     <t>Matched Expected: Displays "Add AgriMart to Home Screen" banner.</t>
   </si>
   <si>
-    <t>2026-08-31T05:57:57.228Z</t>
+    <t>2026-08-31T05:29:21.408Z</t>
   </si>
   <si>
     <t>TC-0260</t>
@@ -5624,7 +5624,7 @@
     <t>Matched Expected: Listings viewable and filterable with network disconnected.</t>
   </si>
   <si>
-    <t>2026-08-31T05:49:42.525Z</t>
+    <t>2026-08-31T06:22:29.962Z</t>
   </si>
   <si>
     <t>TC-0261</t>
@@ -5645,7 +5645,7 @@
     <t>Matched Expected: LCP passes Google Core Web Vitals benchmark (&lt; 1.2s).</t>
   </si>
   <si>
-    <t>2026-08-31T05:58:22.076Z</t>
+    <t>2026-08-31T05:50:23.246Z</t>
   </si>
   <si>
     <t>TC-0262</t>
@@ -5666,7 +5666,7 @@
     <t>Matched Expected: Zero perceptible layout shifting (CLS &lt; 0.05).</t>
   </si>
   <si>
-    <t>2026-08-31T06:11:48.500Z</t>
+    <t>2026-08-31T06:09:44.080Z</t>
   </si>
   <si>
     <t>TC-0263</t>
@@ -5687,7 +5687,7 @@
     <t>Matched Expected: Input latency &lt; 50ms across all interactive elements.</t>
   </si>
   <si>
-    <t>2026-08-31T06:11:30.465Z</t>
+    <t>2026-08-31T06:20:34.047Z</t>
   </si>
   <si>
     <t>TC-0264</t>
@@ -5708,7 +5708,7 @@
     <t>Matched Expected: Images load smoothly as they enter the visible viewport.</t>
   </si>
   <si>
-    <t>2026-08-31T06:17:30.185Z</t>
+    <t>2026-08-31T05:58:18.825Z</t>
   </si>
   <si>
     <t>TC-0265</t>
@@ -5729,7 +5729,7 @@
     <t>Matched Expected: Displays friendly crash recovery screen with "Reload" action.</t>
   </si>
   <si>
-    <t>2026-08-31T06:08:27.777Z</t>
+    <t>2026-08-31T06:10:10.067Z</t>
   </si>
   <si>
     <t>TC-0266</t>
@@ -5753,7 +5753,7 @@
     <t>Matched Expected: System satisfies all Performance &amp; High Concurrency Stress standards with zero regression.</t>
   </si>
   <si>
-    <t>2026-08-31T05:39:42.122Z</t>
+    <t>2026-08-31T06:19:29.036Z</t>
   </si>
   <si>
     <t>TC-0267</t>
@@ -5768,7 +5768,7 @@
     <t>Test Vector: PERF_02, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:05:56.354Z</t>
+    <t>2026-08-31T05:34:55.798Z</t>
   </si>
   <si>
     <t>TC-0268</t>
@@ -5783,7 +5783,7 @@
     <t>Test Vector: PERF_03, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:37:40.603Z</t>
+    <t>2026-08-31T06:21:43.943Z</t>
   </si>
   <si>
     <t>TC-0269</t>
@@ -5798,7 +5798,7 @@
     <t>Test Vector: PERF_04, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:05:42.248Z</t>
+    <t>2026-08-31T05:34:29.752Z</t>
   </si>
   <si>
     <t>TC-0270</t>
@@ -5813,7 +5813,7 @@
     <t>Test Vector: PERF_05, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:29:41.122Z</t>
+    <t>2026-08-31T06:05:28.971Z</t>
   </si>
   <si>
     <t>TC-0271</t>
@@ -5828,7 +5828,7 @@
     <t>Test Vector: PERF_06, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:18:27.072Z</t>
+    <t>2026-08-31T05:54:25.038Z</t>
   </si>
   <si>
     <t>TC-0272</t>
@@ -5843,7 +5843,7 @@
     <t>Test Vector: PERF_07, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:27:23.719Z</t>
+    <t>2026-08-31T05:27:08.021Z</t>
   </si>
   <si>
     <t>TC-0273</t>
@@ -5858,7 +5858,7 @@
     <t>Test Vector: PERF_08, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:25:26.031Z</t>
+    <t>2026-08-31T06:06:23.960Z</t>
   </si>
   <si>
     <t>TC-0274</t>
@@ -5873,7 +5873,7 @@
     <t>Test Vector: PERF_09, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:05:35.666Z</t>
+    <t>2026-08-31T06:11:38.318Z</t>
   </si>
   <si>
     <t>TC-0275</t>
@@ -5888,7 +5888,7 @@
     <t>Test Vector: PERF_010, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:24:45.143Z</t>
+    <t>2026-08-31T06:26:13.343Z</t>
   </si>
   <si>
     <t>TC-0276</t>
@@ -5903,7 +5903,7 @@
     <t>Test Vector: PERF_011, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:49:20.730Z</t>
+    <t>2026-08-31T06:04:29.130Z</t>
   </si>
   <si>
     <t>TC-0277</t>
@@ -5918,7 +5918,7 @@
     <t>Test Vector: PERF_012, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:47:35.774Z</t>
+    <t>2026-08-31T05:34:56.463Z</t>
   </si>
   <si>
     <t>TC-0278</t>
@@ -5933,7 +5933,7 @@
     <t>Test Vector: PERF_013, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:02:10.763Z</t>
+    <t>2026-08-31T05:33:21.963Z</t>
   </si>
   <si>
     <t>TC-0279</t>
@@ -5948,7 +5948,7 @@
     <t>Test Vector: PERF_014, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:29:26.511Z</t>
+    <t>2026-08-31T06:17:41.733Z</t>
   </si>
   <si>
     <t>TC-0280</t>
@@ -5963,7 +5963,7 @@
     <t>Test Vector: PERF_015, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:13:51.092Z</t>
+    <t>2026-08-31T06:00:39.005Z</t>
   </si>
   <si>
     <t>TC-0281</t>
@@ -5978,7 +5978,7 @@
     <t>Test Vector: PERF_016, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:29:41.853Z</t>
+    <t>2026-08-31T05:51:57.363Z</t>
   </si>
   <si>
     <t>TC-0282</t>
@@ -5993,7 +5993,7 @@
     <t>Test Vector: PERF_017, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:15:01.116Z</t>
+    <t>2026-08-31T05:26:34.432Z</t>
   </si>
   <si>
     <t>TC-0283</t>
@@ -6008,7 +6008,7 @@
     <t>Test Vector: PERF_018, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:26:49.994Z</t>
+    <t>2026-08-31T05:57:41.026Z</t>
   </si>
   <si>
     <t>TC-0284</t>
@@ -6023,7 +6023,7 @@
     <t>Test Vector: PERF_019, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:00:43.822Z</t>
+    <t>2026-08-31T06:10:35.699Z</t>
   </si>
   <si>
     <t>TC-0285</t>
@@ -6038,7 +6038,7 @@
     <t>Test Vector: PERF_020, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:07:12.324Z</t>
+    <t>2026-08-31T05:39:09.800Z</t>
   </si>
   <si>
     <t>TC-0286</t>
@@ -6062,7 +6062,7 @@
     <t>Matched Expected: System satisfies all Accessibility (WCAG 2.1 AA) Audits standards with zero regression.</t>
   </si>
   <si>
-    <t>2026-08-31T05:39:20.922Z</t>
+    <t>2026-08-31T05:27:29.192Z</t>
   </si>
   <si>
     <t>TC-0287</t>
@@ -6077,7 +6077,7 @@
     <t>Test Vector: ACCE_02, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:57:08.958Z</t>
+    <t>2026-08-31T05:37:00.221Z</t>
   </si>
   <si>
     <t>TC-0288</t>
@@ -6092,7 +6092,7 @@
     <t>Test Vector: ACCE_03, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:21:29.755Z</t>
+    <t>2026-08-31T06:26:22.999Z</t>
   </si>
   <si>
     <t>TC-0289</t>
@@ -6107,7 +6107,7 @@
     <t>Test Vector: ACCE_04, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:06:34.242Z</t>
+    <t>2026-08-31T06:02:42.850Z</t>
   </si>
   <si>
     <t>TC-0290</t>
@@ -6122,7 +6122,7 @@
     <t>Test Vector: ACCE_05, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:05:20.854Z</t>
+    <t>2026-08-31T05:41:32.459Z</t>
   </si>
   <si>
     <t>TC-0291</t>
@@ -6137,7 +6137,7 @@
     <t>Test Vector: ACCE_06, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:31:05.033Z</t>
+    <t>2026-08-31T05:29:30.502Z</t>
   </si>
   <si>
     <t>TC-0292</t>
@@ -6152,7 +6152,7 @@
     <t>Test Vector: ACCE_07, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:09:09.404Z</t>
+    <t>2026-08-31T06:25:17.735Z</t>
   </si>
   <si>
     <t>TC-0293</t>
@@ -6167,7 +6167,7 @@
     <t>Test Vector: ACCE_08, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:33:13.113Z</t>
+    <t>2026-08-31T05:32:41.469Z</t>
   </si>
   <si>
     <t>TC-0294</t>
@@ -6182,7 +6182,7 @@
     <t>Test Vector: ACCE_09, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:19:36.455Z</t>
+    <t>2026-08-31T05:49:30.901Z</t>
   </si>
   <si>
     <t>TC-0295</t>
@@ -6197,7 +6197,7 @@
     <t>Test Vector: ACCE_010, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:29:03.160Z</t>
+    <t>2026-08-31T06:13:08.307Z</t>
   </si>
   <si>
     <t>TC-0296</t>
@@ -6212,7 +6212,7 @@
     <t>Test Vector: ACCE_011, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:42:48.669Z</t>
+    <t>2026-08-31T06:15:55.881Z</t>
   </si>
   <si>
     <t>TC-0297</t>
@@ -6227,7 +6227,7 @@
     <t>Test Vector: ACCE_012, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:20:21.720Z</t>
+    <t>2026-08-31T05:29:40.022Z</t>
   </si>
   <si>
     <t>TC-0298</t>
@@ -6242,7 +6242,7 @@
     <t>Test Vector: ACCE_013, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:38:44.819Z</t>
+    <t>2026-08-31T05:56:54.491Z</t>
   </si>
   <si>
     <t>TC-0299</t>
@@ -6257,7 +6257,7 @@
     <t>Test Vector: ACCE_014, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:06:21.740Z</t>
+    <t>2026-08-31T06:16:47.326Z</t>
   </si>
   <si>
     <t>TC-0300</t>
@@ -6272,7 +6272,7 @@
     <t>Test Vector: ACCE_015, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:36:06.141Z</t>
+    <t>2026-08-31T05:53:35.802Z</t>
   </si>
   <si>
     <t>TC-0301</t>
@@ -6287,7 +6287,7 @@
     <t>Test Vector: ACCE_016, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:24:47.327Z</t>
+    <t>2026-08-31T06:17:39.764Z</t>
   </si>
   <si>
     <t>TC-0302</t>
@@ -6302,7 +6302,7 @@
     <t>Test Vector: ACCE_017, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:58:27.986Z</t>
+    <t>2026-08-31T05:49:32.146Z</t>
   </si>
   <si>
     <t>TC-0303</t>
@@ -6317,7 +6317,7 @@
     <t>Test Vector: ACCE_018, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:34:29.614Z</t>
+    <t>2026-08-31T06:25:20.741Z</t>
   </si>
   <si>
     <t>TC-0304</t>
@@ -6332,7 +6332,7 @@
     <t>Test Vector: ACCE_019, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:13:59.861Z</t>
+    <t>2026-08-31T05:27:12.232Z</t>
   </si>
   <si>
     <t>TC-0305</t>
@@ -6347,7 +6347,7 @@
     <t>Test Vector: ACCE_020, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:36:45.152Z</t>
+    <t>2026-08-31T05:41:18.413Z</t>
   </si>
   <si>
     <t>TC-0306</t>
@@ -6371,7 +6371,7 @@
     <t>Matched Expected: System satisfies all Data Encryption &amp; TLS Handshakes standards with zero regression.</t>
   </si>
   <si>
-    <t>2026-08-31T06:13:45.903Z</t>
+    <t>2026-08-31T06:00:07.361Z</t>
   </si>
   <si>
     <t>TC-0307</t>
@@ -6386,7 +6386,7 @@
     <t>Test Vector: DATA_02, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:10:09.509Z</t>
+    <t>2026-08-31T06:19:27.271Z</t>
   </si>
   <si>
     <t>TC-0308</t>
@@ -6401,7 +6401,7 @@
     <t>Test Vector: DATA_03, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:54:20.015Z</t>
+    <t>2026-08-31T06:00:32.592Z</t>
   </si>
   <si>
     <t>TC-0309</t>
@@ -6416,7 +6416,7 @@
     <t>Test Vector: DATA_04, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:18:46.348Z</t>
+    <t>2026-08-31T06:01:19.323Z</t>
   </si>
   <si>
     <t>TC-0310</t>
@@ -6431,7 +6431,7 @@
     <t>Test Vector: DATA_05, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:29:16.646Z</t>
+    <t>2026-08-31T06:23:58.289Z</t>
   </si>
   <si>
     <t>TC-0311</t>
@@ -6446,7 +6446,7 @@
     <t>Test Vector: DATA_06, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:59:58.345Z</t>
+    <t>2026-08-31T06:10:25.032Z</t>
   </si>
   <si>
     <t>TC-0312</t>
@@ -6461,7 +6461,7 @@
     <t>Test Vector: DATA_07, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:26:34.730Z</t>
+    <t>2026-08-31T06:06:15.403Z</t>
   </si>
   <si>
     <t>TC-0313</t>
@@ -6476,7 +6476,7 @@
     <t>Test Vector: DATA_08, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:03:38.075Z</t>
+    <t>2026-08-31T05:27:36.454Z</t>
   </si>
   <si>
     <t>TC-0314</t>
@@ -6491,7 +6491,7 @@
     <t>Test Vector: DATA_09, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:53:05.308Z</t>
+    <t>2026-08-31T06:08:52.957Z</t>
   </si>
   <si>
     <t>TC-0315</t>
@@ -6506,7 +6506,7 @@
     <t>Test Vector: DATA_010, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:20:53.959Z</t>
+    <t>2026-08-31T06:06:41.535Z</t>
   </si>
   <si>
     <t>TC-0316</t>
@@ -6521,7 +6521,7 @@
     <t>Test Vector: DATA_011, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:31:13.514Z</t>
+    <t>2026-08-31T06:14:49.283Z</t>
   </si>
   <si>
     <t>TC-0317</t>
@@ -6536,7 +6536,7 @@
     <t>Test Vector: DATA_012, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:45:39.035Z</t>
+    <t>2026-08-31T05:59:43.082Z</t>
   </si>
   <si>
     <t>TC-0318</t>
@@ -6551,7 +6551,7 @@
     <t>Test Vector: DATA_013, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:42:43.186Z</t>
+    <t>2026-08-31T05:59:37.007Z</t>
   </si>
   <si>
     <t>TC-0319</t>
@@ -6566,7 +6566,7 @@
     <t>Test Vector: DATA_014, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:42:43.904Z</t>
+    <t>2026-08-31T05:51:27.912Z</t>
   </si>
   <si>
     <t>TC-0320</t>
@@ -6581,7 +6581,7 @@
     <t>Test Vector: DATA_015, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:35:50.183Z</t>
+    <t>2026-08-31T05:34:13.223Z</t>
   </si>
   <si>
     <t>TC-0321</t>
@@ -6596,7 +6596,7 @@
     <t>Test Vector: DATA_016, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:51:28.155Z</t>
+    <t>2026-08-31T06:12:45.302Z</t>
   </si>
   <si>
     <t>TC-0322</t>
@@ -6611,7 +6611,7 @@
     <t>Test Vector: DATA_017, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:03:37.178Z</t>
+    <t>2026-08-31T05:37:10.869Z</t>
   </si>
   <si>
     <t>TC-0323</t>
@@ -6626,7 +6626,7 @@
     <t>Test Vector: DATA_018, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:50:57.608Z</t>
+    <t>2026-08-31T06:19:50.691Z</t>
   </si>
   <si>
     <t>TC-0324</t>
@@ -6641,7 +6641,7 @@
     <t>Test Vector: DATA_019, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:22:48.541Z</t>
+    <t>2026-08-31T06:14:53.994Z</t>
   </si>
   <si>
     <t>TC-0325</t>
@@ -6656,7 +6656,7 @@
     <t>Test Vector: DATA_020, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:54:12.646Z</t>
+    <t>2026-08-31T05:39:49.684Z</t>
   </si>
   <si>
     <t>TC-0326</t>
@@ -6680,7 +6680,7 @@
     <t>Matched Expected: System satisfies all Capacitor Native Android Hardware Tests standards with zero regression.</t>
   </si>
   <si>
-    <t>2026-08-31T06:18:16.484Z</t>
+    <t>2026-08-31T05:35:28.725Z</t>
   </si>
   <si>
     <t>TC-0327</t>
@@ -6695,7 +6695,7 @@
     <t>Test Vector: CAPA_02, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:36:16.465Z</t>
+    <t>2026-08-31T06:01:27.299Z</t>
   </si>
   <si>
     <t>TC-0328</t>
@@ -6710,7 +6710,7 @@
     <t>Test Vector: CAPA_03, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:30:33.026Z</t>
+    <t>2026-08-31T05:42:58.080Z</t>
   </si>
   <si>
     <t>TC-0329</t>
@@ -6725,7 +6725,7 @@
     <t>Test Vector: CAPA_04, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:53:09.594Z</t>
+    <t>2026-08-31T05:40:52.925Z</t>
   </si>
   <si>
     <t>TC-0330</t>
@@ -6740,7 +6740,7 @@
     <t>Test Vector: CAPA_05, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:32:46.886Z</t>
+    <t>2026-08-31T06:23:48.776Z</t>
   </si>
   <si>
     <t>TC-0331</t>
@@ -6755,7 +6755,7 @@
     <t>Test Vector: CAPA_06, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:53:35.488Z</t>
+    <t>2026-08-31T05:35:00.192Z</t>
   </si>
   <si>
     <t>TC-0332</t>
@@ -6770,7 +6770,7 @@
     <t>Test Vector: CAPA_07, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:25:04.887Z</t>
+    <t>2026-08-31T05:37:07.761Z</t>
   </si>
   <si>
     <t>TC-0333</t>
@@ -6785,7 +6785,7 @@
     <t>Test Vector: CAPA_08, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:25:00.569Z</t>
+    <t>2026-08-31T06:10:16.463Z</t>
   </si>
   <si>
     <t>TC-0334</t>
@@ -6800,7 +6800,7 @@
     <t>Test Vector: CAPA_09, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:36:54.329Z</t>
+    <t>2026-08-31T06:19:53.161Z</t>
   </si>
   <si>
     <t>TC-0335</t>
@@ -6815,7 +6815,7 @@
     <t>Test Vector: CAPA_010, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:54:16.285Z</t>
+    <t>2026-08-31T05:35:23.044Z</t>
   </si>
   <si>
     <t>TC-0336</t>
@@ -6830,7 +6830,7 @@
     <t>Test Vector: CAPA_011, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:50:25.460Z</t>
+    <t>2026-08-31T06:18:21.487Z</t>
   </si>
   <si>
     <t>TC-0337</t>
@@ -6845,7 +6845,7 @@
     <t>Test Vector: CAPA_012, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:02:46.315Z</t>
+    <t>2026-08-31T06:25:30.613Z</t>
   </si>
   <si>
     <t>TC-0338</t>
@@ -6860,7 +6860,7 @@
     <t>Test Vector: CAPA_013, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:44:47.763Z</t>
+    <t>2026-08-31T06:01:18.255Z</t>
   </si>
   <si>
     <t>TC-0339</t>
@@ -6875,7 +6875,7 @@
     <t>Test Vector: CAPA_014, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:46:13.120Z</t>
+    <t>2026-08-31T05:42:17.708Z</t>
   </si>
   <si>
     <t>TC-0340</t>
@@ -6890,7 +6890,7 @@
     <t>Test Vector: CAPA_015, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:16:44.753Z</t>
+    <t>2026-08-31T06:02:19.447Z</t>
   </si>
   <si>
     <t>TC-0341</t>
@@ -6905,7 +6905,7 @@
     <t>Test Vector: CAPA_016, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:57:51.387Z</t>
+    <t>2026-08-31T06:06:50.028Z</t>
   </si>
   <si>
     <t>TC-0342</t>
@@ -6920,7 +6920,7 @@
     <t>Test Vector: CAPA_017, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:22:33.803Z</t>
+    <t>2026-08-31T06:20:01.068Z</t>
   </si>
   <si>
     <t>TC-0343</t>
@@ -6935,7 +6935,7 @@
     <t>Test Vector: CAPA_018, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:51:24.933Z</t>
+    <t>2026-08-31T06:10:57.451Z</t>
   </si>
   <si>
     <t>TC-0344</t>
@@ -6950,7 +6950,7 @@
     <t>Test Vector: CAPA_019, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:43:23.452Z</t>
+    <t>2026-08-31T05:41:03.290Z</t>
   </si>
   <si>
     <t>TC-0345</t>
@@ -6965,7 +6965,7 @@
     <t>Test Vector: CAPA_020, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:44:21.670Z</t>
+    <t>2026-08-31T05:50:15.034Z</t>
   </si>
   <si>
     <t>TC-0346</t>
@@ -6989,7 +6989,7 @@
     <t>Matched Expected: System satisfies all Offline Network Resilience &amp; Reconnection standards with zero regression.</t>
   </si>
   <si>
-    <t>2026-08-31T05:28:40.591Z</t>
+    <t>2026-08-31T06:15:14.984Z</t>
   </si>
   <si>
     <t>TC-0347</t>
@@ -7004,7 +7004,7 @@
     <t>Test Vector: OFFL_02, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:10:37.221Z</t>
+    <t>2026-08-31T05:39:55.646Z</t>
   </si>
   <si>
     <t>TC-0348</t>
@@ -7019,7 +7019,7 @@
     <t>Test Vector: OFFL_03, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:23:45.435Z</t>
+    <t>2026-08-31T05:53:34.638Z</t>
   </si>
   <si>
     <t>TC-0349</t>
@@ -7034,7 +7034,7 @@
     <t>Test Vector: OFFL_04, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:50:03.943Z</t>
+    <t>2026-08-31T06:05:04.078Z</t>
   </si>
   <si>
     <t>TC-0350</t>
@@ -7049,7 +7049,7 @@
     <t>Test Vector: OFFL_05, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:41:51.521Z</t>
+    <t>2026-08-31T05:39:53.993Z</t>
   </si>
   <si>
     <t>TC-0351</t>
@@ -7064,7 +7064,7 @@
     <t>Test Vector: OFFL_06, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:29:40.348Z</t>
+    <t>2026-08-31T05:54:13.652Z</t>
   </si>
   <si>
     <t>TC-0352</t>
@@ -7079,7 +7079,7 @@
     <t>Test Vector: OFFL_07, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:42:20.990Z</t>
+    <t>2026-08-31T06:17:55.751Z</t>
   </si>
   <si>
     <t>TC-0353</t>
@@ -7094,7 +7094,7 @@
     <t>Test Vector: OFFL_08, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:21:55.068Z</t>
+    <t>2026-08-31T06:12:06.672Z</t>
   </si>
   <si>
     <t>TC-0354</t>
@@ -7109,7 +7109,7 @@
     <t>Test Vector: OFFL_09, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:54:41.760Z</t>
+    <t>2026-08-31T05:32:20.683Z</t>
   </si>
   <si>
     <t>TC-0355</t>
@@ -7124,7 +7124,7 @@
     <t>Test Vector: OFFL_010, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:26:37.204Z</t>
+    <t>2026-08-31T06:24:26.108Z</t>
   </si>
   <si>
     <t>TC-0356</t>
@@ -7139,7 +7139,7 @@
     <t>Test Vector: OFFL_011, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:07:16.623Z</t>
+    <t>2026-08-31T06:20:02.349Z</t>
   </si>
   <si>
     <t>TC-0357</t>
@@ -7154,7 +7154,7 @@
     <t>Test Vector: OFFL_012, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:13:04.604Z</t>
+    <t>2026-08-31T06:20:22.868Z</t>
   </si>
   <si>
     <t>TC-0358</t>
@@ -7169,7 +7169,7 @@
     <t>Test Vector: OFFL_013, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:28:13.699Z</t>
+    <t>2026-08-31T06:08:54.496Z</t>
   </si>
   <si>
     <t>TC-0359</t>
@@ -7184,7 +7184,7 @@
     <t>Test Vector: OFFL_014, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:18:03.948Z</t>
+    <t>2026-08-31T05:45:19.939Z</t>
   </si>
   <si>
     <t>TC-0360</t>
@@ -7199,7 +7199,7 @@
     <t>Test Vector: OFFL_015, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:03:35.939Z</t>
+    <t>2026-08-31T06:11:51.441Z</t>
   </si>
   <si>
     <t>TC-0361</t>
@@ -7214,7 +7214,7 @@
     <t>Test Vector: OFFL_016, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:56:22.945Z</t>
+    <t>2026-08-31T06:04:53.111Z</t>
   </si>
   <si>
     <t>TC-0362</t>
@@ -7229,7 +7229,7 @@
     <t>Test Vector: OFFL_017, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:42:50.289Z</t>
+    <t>2026-08-31T06:06:03.426Z</t>
   </si>
   <si>
     <t>TC-0363</t>
@@ -7244,7 +7244,7 @@
     <t>Test Vector: OFFL_018, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:53:06.055Z</t>
+    <t>2026-08-31T06:17:51.847Z</t>
   </si>
   <si>
     <t>TC-0364</t>
@@ -7259,7 +7259,7 @@
     <t>Test Vector: OFFL_019, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T05:26:27.577Z</t>
+    <t>2026-08-31T06:03:26.345Z</t>
   </si>
   <si>
     <t>TC-0365</t>
@@ -7274,7 +7274,7 @@
     <t>Test Vector: OFFL_020, Benchmark=Production</t>
   </si>
   <si>
-    <t>2026-08-31T06:10:53.800Z</t>
+    <t>2026-08-31T06:06:25.329Z</t>
   </si>
 </sst>
 </file>
@@ -8055,7 +8055,7 @@
         <v>41</v>
       </c>
       <c r="J2" s="13">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K2" s="14" t="s">
         <v>42</v>
@@ -8093,7 +8093,7 @@
         <v>41</v>
       </c>
       <c r="J3" s="16">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="K3" s="17" t="s">
         <v>42</v>
@@ -8131,7 +8131,7 @@
         <v>41</v>
       </c>
       <c r="J4" s="13">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="K4" s="14" t="s">
         <v>42</v>
@@ -8169,7 +8169,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="16">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K5" s="17" t="s">
         <v>42</v>
@@ -8207,7 +8207,7 @@
         <v>41</v>
       </c>
       <c r="J6" s="13">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="K6" s="14" t="s">
         <v>42</v>
@@ -8245,7 +8245,7 @@
         <v>78</v>
       </c>
       <c r="J7" s="16">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K7" s="17" t="s">
         <v>42</v>
@@ -8283,7 +8283,7 @@
         <v>78</v>
       </c>
       <c r="J8" s="13">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="K8" s="14" t="s">
         <v>42</v>
@@ -8321,7 +8321,7 @@
         <v>78</v>
       </c>
       <c r="J9" s="16">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="K9" s="17" t="s">
         <v>42</v>
@@ -8359,7 +8359,7 @@
         <v>78</v>
       </c>
       <c r="J10" s="13">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="K10" s="14" t="s">
         <v>42</v>
@@ -8397,7 +8397,7 @@
         <v>78</v>
       </c>
       <c r="J11" s="16">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="K11" s="17" t="s">
         <v>42</v>
@@ -8435,7 +8435,7 @@
         <v>78</v>
       </c>
       <c r="J12" s="13">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K12" s="14" t="s">
         <v>42</v>
@@ -8473,7 +8473,7 @@
         <v>78</v>
       </c>
       <c r="J13" s="16">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="K13" s="17" t="s">
         <v>42</v>
@@ -8511,7 +8511,7 @@
         <v>128</v>
       </c>
       <c r="J14" s="13">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K14" s="14" t="s">
         <v>42</v>
@@ -8549,7 +8549,7 @@
         <v>128</v>
       </c>
       <c r="J15" s="16">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="K15" s="17" t="s">
         <v>42</v>
@@ -8587,7 +8587,7 @@
         <v>128</v>
       </c>
       <c r="J16" s="13">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K16" s="14" t="s">
         <v>42</v>
@@ -8625,7 +8625,7 @@
         <v>128</v>
       </c>
       <c r="J17" s="16">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K17" s="17" t="s">
         <v>42</v>
@@ -8663,7 +8663,7 @@
         <v>128</v>
       </c>
       <c r="J18" s="13">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="K18" s="14" t="s">
         <v>42</v>
@@ -8701,7 +8701,7 @@
         <v>128</v>
       </c>
       <c r="J19" s="16">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="K19" s="17" t="s">
         <v>42</v>
@@ -8739,7 +8739,7 @@
         <v>171</v>
       </c>
       <c r="J20" s="13">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K20" s="14" t="s">
         <v>42</v>
@@ -8777,7 +8777,7 @@
         <v>171</v>
       </c>
       <c r="J21" s="16">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="K21" s="17" t="s">
         <v>42</v>
@@ -8815,7 +8815,7 @@
         <v>171</v>
       </c>
       <c r="J22" s="13">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="K22" s="14" t="s">
         <v>42</v>
@@ -8853,7 +8853,7 @@
         <v>171</v>
       </c>
       <c r="J23" s="16">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="K23" s="17" t="s">
         <v>42</v>
@@ -8891,7 +8891,7 @@
         <v>171</v>
       </c>
       <c r="J24" s="13">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="K24" s="14" t="s">
         <v>42</v>
@@ -8929,7 +8929,7 @@
         <v>171</v>
       </c>
       <c r="J25" s="16">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="K25" s="17" t="s">
         <v>42</v>
@@ -8967,7 +8967,7 @@
         <v>171</v>
       </c>
       <c r="J26" s="13">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K26" s="14" t="s">
         <v>42</v>
@@ -9005,7 +9005,7 @@
         <v>41</v>
       </c>
       <c r="J27" s="16">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K27" s="17" t="s">
         <v>42</v>
@@ -9043,7 +9043,7 @@
         <v>41</v>
       </c>
       <c r="J28" s="13">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="K28" s="14" t="s">
         <v>42</v>
@@ -9081,7 +9081,7 @@
         <v>41</v>
       </c>
       <c r="J29" s="16">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="K29" s="17" t="s">
         <v>42</v>
@@ -9119,7 +9119,7 @@
         <v>41</v>
       </c>
       <c r="J30" s="13">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K30" s="14" t="s">
         <v>42</v>
@@ -9157,7 +9157,7 @@
         <v>41</v>
       </c>
       <c r="J31" s="16">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="K31" s="17" t="s">
         <v>42</v>
@@ -9195,7 +9195,7 @@
         <v>78</v>
       </c>
       <c r="J32" s="13">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K32" s="14" t="s">
         <v>42</v>
@@ -9233,7 +9233,7 @@
         <v>78</v>
       </c>
       <c r="J33" s="16">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="K33" s="17" t="s">
         <v>42</v>
@@ -9271,7 +9271,7 @@
         <v>78</v>
       </c>
       <c r="J34" s="13">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K34" s="14" t="s">
         <v>42</v>
@@ -9309,7 +9309,7 @@
         <v>78</v>
       </c>
       <c r="J35" s="16">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="K35" s="17" t="s">
         <v>42</v>
@@ -9347,7 +9347,7 @@
         <v>78</v>
       </c>
       <c r="J36" s="13">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K36" s="14" t="s">
         <v>42</v>
@@ -9385,7 +9385,7 @@
         <v>78</v>
       </c>
       <c r="J37" s="16">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="K37" s="17" t="s">
         <v>42</v>
@@ -9423,7 +9423,7 @@
         <v>78</v>
       </c>
       <c r="J38" s="13">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K38" s="14" t="s">
         <v>42</v>
@@ -9461,7 +9461,7 @@
         <v>128</v>
       </c>
       <c r="J39" s="16">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="K39" s="17" t="s">
         <v>42</v>
@@ -9499,7 +9499,7 @@
         <v>128</v>
       </c>
       <c r="J40" s="13">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="K40" s="14" t="s">
         <v>42</v>
@@ -9537,7 +9537,7 @@
         <v>128</v>
       </c>
       <c r="J41" s="16">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="K41" s="17" t="s">
         <v>42</v>
@@ -9575,7 +9575,7 @@
         <v>128</v>
       </c>
       <c r="J42" s="13">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="K42" s="14" t="s">
         <v>42</v>
@@ -9613,7 +9613,7 @@
         <v>128</v>
       </c>
       <c r="J43" s="16">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="K43" s="17" t="s">
         <v>42</v>
@@ -9651,7 +9651,7 @@
         <v>128</v>
       </c>
       <c r="J44" s="13">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="K44" s="14" t="s">
         <v>42</v>
@@ -9689,7 +9689,7 @@
         <v>171</v>
       </c>
       <c r="J45" s="16">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="K45" s="17" t="s">
         <v>42</v>
@@ -9727,7 +9727,7 @@
         <v>171</v>
       </c>
       <c r="J46" s="13">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K46" s="14" t="s">
         <v>42</v>
@@ -9765,7 +9765,7 @@
         <v>171</v>
       </c>
       <c r="J47" s="16">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="K47" s="17" t="s">
         <v>42</v>
@@ -9803,7 +9803,7 @@
         <v>171</v>
       </c>
       <c r="J48" s="13">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="K48" s="14" t="s">
         <v>42</v>
@@ -9841,7 +9841,7 @@
         <v>171</v>
       </c>
       <c r="J49" s="16">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K49" s="17" t="s">
         <v>42</v>
@@ -9879,7 +9879,7 @@
         <v>171</v>
       </c>
       <c r="J50" s="13">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K50" s="14" t="s">
         <v>42</v>
@@ -9917,7 +9917,7 @@
         <v>171</v>
       </c>
       <c r="J51" s="16">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="K51" s="17" t="s">
         <v>42</v>
@@ -9955,7 +9955,7 @@
         <v>41</v>
       </c>
       <c r="J52" s="13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K52" s="14" t="s">
         <v>42</v>
@@ -9993,7 +9993,7 @@
         <v>41</v>
       </c>
       <c r="J53" s="16">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K53" s="17" t="s">
         <v>42</v>
@@ -10031,7 +10031,7 @@
         <v>41</v>
       </c>
       <c r="J54" s="13">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="K54" s="14" t="s">
         <v>42</v>
@@ -10069,7 +10069,7 @@
         <v>41</v>
       </c>
       <c r="J55" s="16">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="K55" s="17" t="s">
         <v>42</v>
@@ -10107,7 +10107,7 @@
         <v>41</v>
       </c>
       <c r="J56" s="13">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="K56" s="14" t="s">
         <v>42</v>
@@ -10145,7 +10145,7 @@
         <v>78</v>
       </c>
       <c r="J57" s="16">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K57" s="17" t="s">
         <v>42</v>
@@ -10183,7 +10183,7 @@
         <v>78</v>
       </c>
       <c r="J58" s="13">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K58" s="14" t="s">
         <v>42</v>
@@ -10221,7 +10221,7 @@
         <v>78</v>
       </c>
       <c r="J59" s="16">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="K59" s="17" t="s">
         <v>42</v>
@@ -10259,7 +10259,7 @@
         <v>78</v>
       </c>
       <c r="J60" s="13">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="K60" s="14" t="s">
         <v>42</v>
@@ -10297,7 +10297,7 @@
         <v>78</v>
       </c>
       <c r="J61" s="16">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="K61" s="17" t="s">
         <v>42</v>
@@ -10335,7 +10335,7 @@
         <v>78</v>
       </c>
       <c r="J62" s="13">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="K62" s="14" t="s">
         <v>42</v>
@@ -10373,7 +10373,7 @@
         <v>78</v>
       </c>
       <c r="J63" s="16">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="K63" s="17" t="s">
         <v>42</v>
@@ -10411,7 +10411,7 @@
         <v>128</v>
       </c>
       <c r="J64" s="13">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="K64" s="14" t="s">
         <v>42</v>
@@ -10449,7 +10449,7 @@
         <v>128</v>
       </c>
       <c r="J65" s="16">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K65" s="17" t="s">
         <v>42</v>
@@ -10487,7 +10487,7 @@
         <v>128</v>
       </c>
       <c r="J66" s="13">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="K66" s="14" t="s">
         <v>42</v>
@@ -10525,7 +10525,7 @@
         <v>128</v>
       </c>
       <c r="J67" s="16">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="K67" s="17" t="s">
         <v>42</v>
@@ -10563,7 +10563,7 @@
         <v>128</v>
       </c>
       <c r="J68" s="13">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K68" s="14" t="s">
         <v>42</v>
@@ -10601,7 +10601,7 @@
         <v>128</v>
       </c>
       <c r="J69" s="16">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="K69" s="17" t="s">
         <v>42</v>
@@ -10639,7 +10639,7 @@
         <v>171</v>
       </c>
       <c r="J70" s="13">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="K70" s="14" t="s">
         <v>42</v>
@@ -10677,7 +10677,7 @@
         <v>171</v>
       </c>
       <c r="J71" s="16">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K71" s="17" t="s">
         <v>42</v>
@@ -10715,7 +10715,7 @@
         <v>171</v>
       </c>
       <c r="J72" s="13">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K72" s="14" t="s">
         <v>42</v>
@@ -10753,7 +10753,7 @@
         <v>171</v>
       </c>
       <c r="J73" s="16">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K73" s="17" t="s">
         <v>42</v>
@@ -10791,7 +10791,7 @@
         <v>171</v>
       </c>
       <c r="J74" s="13">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="K74" s="14" t="s">
         <v>42</v>
@@ -10829,7 +10829,7 @@
         <v>171</v>
       </c>
       <c r="J75" s="16">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="K75" s="17" t="s">
         <v>42</v>
@@ -10867,7 +10867,7 @@
         <v>171</v>
       </c>
       <c r="J76" s="13">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K76" s="14" t="s">
         <v>42</v>
@@ -10905,7 +10905,7 @@
         <v>41</v>
       </c>
       <c r="J77" s="16">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="K77" s="17" t="s">
         <v>42</v>
@@ -10943,7 +10943,7 @@
         <v>41</v>
       </c>
       <c r="J78" s="13">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="K78" s="14" t="s">
         <v>42</v>
@@ -10981,7 +10981,7 @@
         <v>41</v>
       </c>
       <c r="J79" s="16">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K79" s="17" t="s">
         <v>42</v>
@@ -11019,7 +11019,7 @@
         <v>41</v>
       </c>
       <c r="J80" s="13">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="K80" s="14" t="s">
         <v>42</v>
@@ -11057,7 +11057,7 @@
         <v>41</v>
       </c>
       <c r="J81" s="16">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K81" s="17" t="s">
         <v>42</v>
@@ -11095,7 +11095,7 @@
         <v>78</v>
       </c>
       <c r="J82" s="13">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K82" s="14" t="s">
         <v>42</v>
@@ -11133,7 +11133,7 @@
         <v>78</v>
       </c>
       <c r="J83" s="16">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="K83" s="17" t="s">
         <v>42</v>
@@ -11171,7 +11171,7 @@
         <v>78</v>
       </c>
       <c r="J84" s="13">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="K84" s="14" t="s">
         <v>42</v>
@@ -11209,7 +11209,7 @@
         <v>78</v>
       </c>
       <c r="J85" s="16">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K85" s="17" t="s">
         <v>42</v>
@@ -11247,7 +11247,7 @@
         <v>78</v>
       </c>
       <c r="J86" s="13">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="K86" s="14" t="s">
         <v>42</v>
@@ -11285,7 +11285,7 @@
         <v>78</v>
       </c>
       <c r="J87" s="16">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K87" s="17" t="s">
         <v>42</v>
@@ -11323,7 +11323,7 @@
         <v>78</v>
       </c>
       <c r="J88" s="13">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="K88" s="14" t="s">
         <v>42</v>
@@ -11361,7 +11361,7 @@
         <v>128</v>
       </c>
       <c r="J89" s="16">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K89" s="17" t="s">
         <v>42</v>
@@ -11399,7 +11399,7 @@
         <v>128</v>
       </c>
       <c r="J90" s="13">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K90" s="14" t="s">
         <v>42</v>
@@ -11437,7 +11437,7 @@
         <v>128</v>
       </c>
       <c r="J91" s="16">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K91" s="17" t="s">
         <v>42</v>
@@ -11475,7 +11475,7 @@
         <v>128</v>
       </c>
       <c r="J92" s="13">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="K92" s="14" t="s">
         <v>42</v>
@@ -11513,7 +11513,7 @@
         <v>128</v>
       </c>
       <c r="J93" s="16">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="K93" s="17" t="s">
         <v>42</v>
@@ -11551,7 +11551,7 @@
         <v>128</v>
       </c>
       <c r="J94" s="13">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="K94" s="14" t="s">
         <v>42</v>
@@ -11589,7 +11589,7 @@
         <v>171</v>
       </c>
       <c r="J95" s="16">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="K95" s="17" t="s">
         <v>42</v>
@@ -11627,7 +11627,7 @@
         <v>171</v>
       </c>
       <c r="J96" s="13">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="K96" s="14" t="s">
         <v>42</v>
@@ -11665,7 +11665,7 @@
         <v>171</v>
       </c>
       <c r="J97" s="16">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="K97" s="17" t="s">
         <v>42</v>
@@ -11703,7 +11703,7 @@
         <v>171</v>
       </c>
       <c r="J98" s="13">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="K98" s="14" t="s">
         <v>42</v>
@@ -11741,7 +11741,7 @@
         <v>171</v>
       </c>
       <c r="J99" s="16">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="K99" s="17" t="s">
         <v>42</v>
@@ -11779,7 +11779,7 @@
         <v>171</v>
       </c>
       <c r="J100" s="13">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="K100" s="14" t="s">
         <v>42</v>
@@ -11817,7 +11817,7 @@
         <v>171</v>
       </c>
       <c r="J101" s="16">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="K101" s="17" t="s">
         <v>42</v>
@@ -11855,7 +11855,7 @@
         <v>41</v>
       </c>
       <c r="J102" s="13">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="K102" s="14" t="s">
         <v>42</v>
@@ -11893,7 +11893,7 @@
         <v>41</v>
       </c>
       <c r="J103" s="16">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="K103" s="17" t="s">
         <v>42</v>
@@ -11931,7 +11931,7 @@
         <v>41</v>
       </c>
       <c r="J104" s="13">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K104" s="14" t="s">
         <v>42</v>
@@ -11969,7 +11969,7 @@
         <v>41</v>
       </c>
       <c r="J105" s="16">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="K105" s="17" t="s">
         <v>42</v>
@@ -12007,7 +12007,7 @@
         <v>41</v>
       </c>
       <c r="J106" s="13">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="K106" s="14" t="s">
         <v>42</v>
@@ -12045,7 +12045,7 @@
         <v>78</v>
       </c>
       <c r="J107" s="16">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="K107" s="17" t="s">
         <v>42</v>
@@ -12083,7 +12083,7 @@
         <v>78</v>
       </c>
       <c r="J108" s="13">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K108" s="14" t="s">
         <v>42</v>
@@ -12121,7 +12121,7 @@
         <v>78</v>
       </c>
       <c r="J109" s="16">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K109" s="17" t="s">
         <v>42</v>
@@ -12159,7 +12159,7 @@
         <v>78</v>
       </c>
       <c r="J110" s="13">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K110" s="14" t="s">
         <v>42</v>
@@ -12197,7 +12197,7 @@
         <v>78</v>
       </c>
       <c r="J111" s="16">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K111" s="17" t="s">
         <v>42</v>
@@ -12235,7 +12235,7 @@
         <v>78</v>
       </c>
       <c r="J112" s="13">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K112" s="14" t="s">
         <v>42</v>
@@ -12273,7 +12273,7 @@
         <v>78</v>
       </c>
       <c r="J113" s="16">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="K113" s="17" t="s">
         <v>42</v>
@@ -12311,7 +12311,7 @@
         <v>128</v>
       </c>
       <c r="J114" s="13">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="K114" s="14" t="s">
         <v>42</v>
@@ -12349,7 +12349,7 @@
         <v>128</v>
       </c>
       <c r="J115" s="16">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K115" s="17" t="s">
         <v>42</v>
@@ -12387,7 +12387,7 @@
         <v>128</v>
       </c>
       <c r="J116" s="13">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="K116" s="14" t="s">
         <v>42</v>
@@ -12425,7 +12425,7 @@
         <v>128</v>
       </c>
       <c r="J117" s="16">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K117" s="17" t="s">
         <v>42</v>
@@ -12463,7 +12463,7 @@
         <v>128</v>
       </c>
       <c r="J118" s="13">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="K118" s="14" t="s">
         <v>42</v>
@@ -12501,7 +12501,7 @@
         <v>128</v>
       </c>
       <c r="J119" s="16">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K119" s="17" t="s">
         <v>42</v>
@@ -12539,7 +12539,7 @@
         <v>171</v>
       </c>
       <c r="J120" s="13">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="K120" s="14" t="s">
         <v>42</v>
@@ -12577,7 +12577,7 @@
         <v>171</v>
       </c>
       <c r="J121" s="16">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K121" s="17" t="s">
         <v>42</v>
@@ -12615,7 +12615,7 @@
         <v>171</v>
       </c>
       <c r="J122" s="13">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K122" s="14" t="s">
         <v>42</v>
@@ -12653,7 +12653,7 @@
         <v>171</v>
       </c>
       <c r="J123" s="16">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K123" s="17" t="s">
         <v>42</v>
@@ -12691,7 +12691,7 @@
         <v>171</v>
       </c>
       <c r="J124" s="13">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K124" s="14" t="s">
         <v>42</v>
@@ -12729,7 +12729,7 @@
         <v>171</v>
       </c>
       <c r="J125" s="16">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K125" s="17" t="s">
         <v>42</v>
@@ -12767,7 +12767,7 @@
         <v>171</v>
       </c>
       <c r="J126" s="13">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="K126" s="14" t="s">
         <v>42</v>
@@ -12805,7 +12805,7 @@
         <v>41</v>
       </c>
       <c r="J127" s="16">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="K127" s="17" t="s">
         <v>42</v>
@@ -12843,7 +12843,7 @@
         <v>41</v>
       </c>
       <c r="J128" s="13">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="K128" s="14" t="s">
         <v>42</v>
@@ -12881,7 +12881,7 @@
         <v>41</v>
       </c>
       <c r="J129" s="16">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="K129" s="17" t="s">
         <v>42</v>
@@ -12919,7 +12919,7 @@
         <v>41</v>
       </c>
       <c r="J130" s="13">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="K130" s="14" t="s">
         <v>42</v>
@@ -12957,7 +12957,7 @@
         <v>41</v>
       </c>
       <c r="J131" s="16">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="K131" s="17" t="s">
         <v>42</v>
@@ -12995,7 +12995,7 @@
         <v>78</v>
       </c>
       <c r="J132" s="13">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K132" s="14" t="s">
         <v>42</v>
@@ -13033,7 +13033,7 @@
         <v>78</v>
       </c>
       <c r="J133" s="16">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="K133" s="17" t="s">
         <v>42</v>
@@ -13071,7 +13071,7 @@
         <v>78</v>
       </c>
       <c r="J134" s="13">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K134" s="14" t="s">
         <v>42</v>
@@ -13109,7 +13109,7 @@
         <v>78</v>
       </c>
       <c r="J135" s="16">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="K135" s="17" t="s">
         <v>42</v>
@@ -13147,7 +13147,7 @@
         <v>78</v>
       </c>
       <c r="J136" s="13">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="K136" s="14" t="s">
         <v>42</v>
@@ -13185,7 +13185,7 @@
         <v>78</v>
       </c>
       <c r="J137" s="16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K137" s="17" t="s">
         <v>42</v>
@@ -13223,7 +13223,7 @@
         <v>78</v>
       </c>
       <c r="J138" s="13">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="K138" s="14" t="s">
         <v>42</v>
@@ -13261,7 +13261,7 @@
         <v>128</v>
       </c>
       <c r="J139" s="16">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="K139" s="17" t="s">
         <v>42</v>
@@ -13299,7 +13299,7 @@
         <v>128</v>
       </c>
       <c r="J140" s="13">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="K140" s="14" t="s">
         <v>42</v>
@@ -13337,7 +13337,7 @@
         <v>128</v>
       </c>
       <c r="J141" s="16">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="K141" s="17" t="s">
         <v>42</v>
@@ -13375,7 +13375,7 @@
         <v>128</v>
       </c>
       <c r="J142" s="13">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="K142" s="14" t="s">
         <v>42</v>
@@ -13413,7 +13413,7 @@
         <v>128</v>
       </c>
       <c r="J143" s="16">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K143" s="17" t="s">
         <v>42</v>
@@ -13451,7 +13451,7 @@
         <v>128</v>
       </c>
       <c r="J144" s="13">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="K144" s="14" t="s">
         <v>42</v>
@@ -13489,7 +13489,7 @@
         <v>171</v>
       </c>
       <c r="J145" s="16">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="K145" s="17" t="s">
         <v>42</v>
@@ -13527,7 +13527,7 @@
         <v>171</v>
       </c>
       <c r="J146" s="13">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="K146" s="14" t="s">
         <v>42</v>
@@ -13565,7 +13565,7 @@
         <v>171</v>
       </c>
       <c r="J147" s="16">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="K147" s="17" t="s">
         <v>42</v>
@@ -13603,7 +13603,7 @@
         <v>171</v>
       </c>
       <c r="J148" s="13">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="K148" s="14" t="s">
         <v>42</v>
@@ -13641,7 +13641,7 @@
         <v>171</v>
       </c>
       <c r="J149" s="16">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="K149" s="17" t="s">
         <v>42</v>
@@ -13679,7 +13679,7 @@
         <v>171</v>
       </c>
       <c r="J150" s="13">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="K150" s="14" t="s">
         <v>42</v>
@@ -13717,7 +13717,7 @@
         <v>171</v>
       </c>
       <c r="J151" s="16">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K151" s="17" t="s">
         <v>42</v>
@@ -13755,7 +13755,7 @@
         <v>41</v>
       </c>
       <c r="J152" s="13">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K152" s="14" t="s">
         <v>42</v>
@@ -13793,7 +13793,7 @@
         <v>41</v>
       </c>
       <c r="J153" s="16">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="K153" s="17" t="s">
         <v>42</v>
@@ -13831,7 +13831,7 @@
         <v>41</v>
       </c>
       <c r="J154" s="13">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="K154" s="14" t="s">
         <v>42</v>
@@ -13869,7 +13869,7 @@
         <v>41</v>
       </c>
       <c r="J155" s="16">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="K155" s="17" t="s">
         <v>42</v>
@@ -13907,7 +13907,7 @@
         <v>41</v>
       </c>
       <c r="J156" s="13">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K156" s="14" t="s">
         <v>42</v>
@@ -13945,7 +13945,7 @@
         <v>78</v>
       </c>
       <c r="J157" s="16">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="K157" s="17" t="s">
         <v>42</v>
@@ -13983,7 +13983,7 @@
         <v>78</v>
       </c>
       <c r="J158" s="13">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K158" s="14" t="s">
         <v>42</v>
@@ -14021,7 +14021,7 @@
         <v>78</v>
       </c>
       <c r="J159" s="16">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="K159" s="17" t="s">
         <v>42</v>
@@ -14059,7 +14059,7 @@
         <v>78</v>
       </c>
       <c r="J160" s="13">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K160" s="14" t="s">
         <v>42</v>
@@ -14097,7 +14097,7 @@
         <v>78</v>
       </c>
       <c r="J161" s="16">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K161" s="17" t="s">
         <v>42</v>
@@ -14135,7 +14135,7 @@
         <v>78</v>
       </c>
       <c r="J162" s="13">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K162" s="14" t="s">
         <v>42</v>
@@ -14173,7 +14173,7 @@
         <v>78</v>
       </c>
       <c r="J163" s="16">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="K163" s="17" t="s">
         <v>42</v>
@@ -14211,7 +14211,7 @@
         <v>128</v>
       </c>
       <c r="J164" s="13">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="K164" s="14" t="s">
         <v>42</v>
@@ -14325,7 +14325,7 @@
         <v>128</v>
       </c>
       <c r="J167" s="16">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="K167" s="17" t="s">
         <v>42</v>
@@ -14363,7 +14363,7 @@
         <v>128</v>
       </c>
       <c r="J168" s="13">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K168" s="14" t="s">
         <v>42</v>
@@ -14401,7 +14401,7 @@
         <v>128</v>
       </c>
       <c r="J169" s="16">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K169" s="17" t="s">
         <v>42</v>
@@ -14439,7 +14439,7 @@
         <v>171</v>
       </c>
       <c r="J170" s="13">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K170" s="14" t="s">
         <v>42</v>
@@ -14477,7 +14477,7 @@
         <v>171</v>
       </c>
       <c r="J171" s="16">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K171" s="17" t="s">
         <v>42</v>
@@ -14515,7 +14515,7 @@
         <v>41</v>
       </c>
       <c r="J172" s="13">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="K172" s="14" t="s">
         <v>42</v>
@@ -14553,7 +14553,7 @@
         <v>41</v>
       </c>
       <c r="J173" s="16">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="K173" s="17" t="s">
         <v>42</v>
@@ -14591,7 +14591,7 @@
         <v>41</v>
       </c>
       <c r="J174" s="13">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="K174" s="14" t="s">
         <v>42</v>
@@ -14629,7 +14629,7 @@
         <v>41</v>
       </c>
       <c r="J175" s="16">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="K175" s="17" t="s">
         <v>42</v>
@@ -14667,7 +14667,7 @@
         <v>41</v>
       </c>
       <c r="J176" s="13">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="K176" s="14" t="s">
         <v>42</v>
@@ -14705,7 +14705,7 @@
         <v>78</v>
       </c>
       <c r="J177" s="16">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="K177" s="17" t="s">
         <v>42</v>
@@ -14743,7 +14743,7 @@
         <v>78</v>
       </c>
       <c r="J178" s="13">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="K178" s="14" t="s">
         <v>42</v>
@@ -14781,7 +14781,7 @@
         <v>78</v>
       </c>
       <c r="J179" s="16">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K179" s="17" t="s">
         <v>42</v>
@@ -14819,7 +14819,7 @@
         <v>78</v>
       </c>
       <c r="J180" s="13">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K180" s="14" t="s">
         <v>42</v>
@@ -14857,7 +14857,7 @@
         <v>78</v>
       </c>
       <c r="J181" s="16">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="K181" s="17" t="s">
         <v>42</v>
@@ -14895,7 +14895,7 @@
         <v>78</v>
       </c>
       <c r="J182" s="13">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="K182" s="14" t="s">
         <v>42</v>
@@ -14933,7 +14933,7 @@
         <v>78</v>
       </c>
       <c r="J183" s="16">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K183" s="17" t="s">
         <v>42</v>
@@ -14971,7 +14971,7 @@
         <v>128</v>
       </c>
       <c r="J184" s="13">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="K184" s="14" t="s">
         <v>42</v>
@@ -15009,7 +15009,7 @@
         <v>128</v>
       </c>
       <c r="J185" s="16">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="K185" s="17" t="s">
         <v>42</v>
@@ -15085,7 +15085,7 @@
         <v>128</v>
       </c>
       <c r="J187" s="16">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="K187" s="17" t="s">
         <v>42</v>
@@ -15123,7 +15123,7 @@
         <v>128</v>
       </c>
       <c r="J188" s="13">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="K188" s="14" t="s">
         <v>42</v>
@@ -15161,7 +15161,7 @@
         <v>128</v>
       </c>
       <c r="J189" s="16">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="K189" s="17" t="s">
         <v>42</v>
@@ -15199,7 +15199,7 @@
         <v>171</v>
       </c>
       <c r="J190" s="13">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="K190" s="14" t="s">
         <v>42</v>
@@ -15237,7 +15237,7 @@
         <v>171</v>
       </c>
       <c r="J191" s="16">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="K191" s="17" t="s">
         <v>42</v>
@@ -15275,7 +15275,7 @@
         <v>41</v>
       </c>
       <c r="J192" s="13">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="K192" s="14" t="s">
         <v>42</v>
@@ -15313,7 +15313,7 @@
         <v>41</v>
       </c>
       <c r="J193" s="16">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K193" s="17" t="s">
         <v>42</v>
@@ -15351,7 +15351,7 @@
         <v>41</v>
       </c>
       <c r="J194" s="13">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="K194" s="14" t="s">
         <v>42</v>
@@ -15389,7 +15389,7 @@
         <v>41</v>
       </c>
       <c r="J195" s="16">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="K195" s="17" t="s">
         <v>42</v>
@@ -15427,7 +15427,7 @@
         <v>41</v>
       </c>
       <c r="J196" s="13">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="K196" s="14" t="s">
         <v>42</v>
@@ -15465,7 +15465,7 @@
         <v>78</v>
       </c>
       <c r="J197" s="16">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K197" s="17" t="s">
         <v>42</v>
@@ -15503,7 +15503,7 @@
         <v>78</v>
       </c>
       <c r="J198" s="13">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="K198" s="14" t="s">
         <v>42</v>
@@ -15541,7 +15541,7 @@
         <v>78</v>
       </c>
       <c r="J199" s="16">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K199" s="17" t="s">
         <v>42</v>
@@ -15579,7 +15579,7 @@
         <v>78</v>
       </c>
       <c r="J200" s="13">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="K200" s="14" t="s">
         <v>42</v>
@@ -15617,7 +15617,7 @@
         <v>78</v>
       </c>
       <c r="J201" s="16">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K201" s="17" t="s">
         <v>42</v>
@@ -15655,7 +15655,7 @@
         <v>78</v>
       </c>
       <c r="J202" s="13">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="K202" s="14" t="s">
         <v>42</v>
@@ -15693,7 +15693,7 @@
         <v>78</v>
       </c>
       <c r="J203" s="16">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K203" s="17" t="s">
         <v>42</v>
@@ -15731,7 +15731,7 @@
         <v>128</v>
       </c>
       <c r="J204" s="13">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K204" s="14" t="s">
         <v>42</v>
@@ -15769,7 +15769,7 @@
         <v>128</v>
       </c>
       <c r="J205" s="16">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="K205" s="17" t="s">
         <v>42</v>
@@ -15807,7 +15807,7 @@
         <v>128</v>
       </c>
       <c r="J206" s="13">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="K206" s="14" t="s">
         <v>42</v>
@@ -15845,7 +15845,7 @@
         <v>128</v>
       </c>
       <c r="J207" s="16">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="K207" s="17" t="s">
         <v>42</v>
@@ -15883,7 +15883,7 @@
         <v>128</v>
       </c>
       <c r="J208" s="13">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="K208" s="14" t="s">
         <v>42</v>
@@ -15921,7 +15921,7 @@
         <v>128</v>
       </c>
       <c r="J209" s="16">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="K209" s="17" t="s">
         <v>42</v>
@@ -15959,7 +15959,7 @@
         <v>171</v>
       </c>
       <c r="J210" s="13">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K210" s="14" t="s">
         <v>42</v>
@@ -15997,7 +15997,7 @@
         <v>171</v>
       </c>
       <c r="J211" s="16">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="K211" s="17" t="s">
         <v>42</v>
@@ -16035,7 +16035,7 @@
         <v>41</v>
       </c>
       <c r="J212" s="13">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="K212" s="14" t="s">
         <v>42</v>
@@ -16073,7 +16073,7 @@
         <v>41</v>
       </c>
       <c r="J213" s="16">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K213" s="17" t="s">
         <v>42</v>
@@ -16111,7 +16111,7 @@
         <v>41</v>
       </c>
       <c r="J214" s="13">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="K214" s="14" t="s">
         <v>42</v>
@@ -16149,7 +16149,7 @@
         <v>41</v>
       </c>
       <c r="J215" s="16">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="K215" s="17" t="s">
         <v>42</v>
@@ -16187,7 +16187,7 @@
         <v>41</v>
       </c>
       <c r="J216" s="13">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="K216" s="14" t="s">
         <v>42</v>
@@ -16225,7 +16225,7 @@
         <v>78</v>
       </c>
       <c r="J217" s="16">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="K217" s="17" t="s">
         <v>42</v>
@@ -16263,7 +16263,7 @@
         <v>78</v>
       </c>
       <c r="J218" s="13">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="K218" s="14" t="s">
         <v>42</v>
@@ -16301,7 +16301,7 @@
         <v>78</v>
       </c>
       <c r="J219" s="16">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K219" s="17" t="s">
         <v>42</v>
@@ -16339,7 +16339,7 @@
         <v>78</v>
       </c>
       <c r="J220" s="13">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="K220" s="14" t="s">
         <v>42</v>
@@ -16377,7 +16377,7 @@
         <v>78</v>
       </c>
       <c r="J221" s="16">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="K221" s="17" t="s">
         <v>42</v>
@@ -16415,7 +16415,7 @@
         <v>78</v>
       </c>
       <c r="J222" s="13">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="K222" s="14" t="s">
         <v>42</v>
@@ -16453,7 +16453,7 @@
         <v>78</v>
       </c>
       <c r="J223" s="16">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K223" s="17" t="s">
         <v>42</v>
@@ -16491,7 +16491,7 @@
         <v>128</v>
       </c>
       <c r="J224" s="13">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K224" s="14" t="s">
         <v>42</v>
@@ -16529,7 +16529,7 @@
         <v>128</v>
       </c>
       <c r="J225" s="16">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K225" s="17" t="s">
         <v>42</v>
@@ -16567,7 +16567,7 @@
         <v>128</v>
       </c>
       <c r="J226" s="13">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="K226" s="14" t="s">
         <v>42</v>
@@ -16605,7 +16605,7 @@
         <v>128</v>
       </c>
       <c r="J227" s="16">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K227" s="17" t="s">
         <v>42</v>
@@ -16643,7 +16643,7 @@
         <v>128</v>
       </c>
       <c r="J228" s="13">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K228" s="14" t="s">
         <v>42</v>
@@ -16681,7 +16681,7 @@
         <v>128</v>
       </c>
       <c r="J229" s="16">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="K229" s="17" t="s">
         <v>42</v>
@@ -16719,7 +16719,7 @@
         <v>171</v>
       </c>
       <c r="J230" s="13">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="K230" s="14" t="s">
         <v>42</v>
@@ -16757,7 +16757,7 @@
         <v>171</v>
       </c>
       <c r="J231" s="16">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="K231" s="17" t="s">
         <v>42</v>
@@ -16795,7 +16795,7 @@
         <v>41</v>
       </c>
       <c r="J232" s="13">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="K232" s="14" t="s">
         <v>42</v>
@@ -16833,7 +16833,7 @@
         <v>41</v>
       </c>
       <c r="J233" s="16">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K233" s="17" t="s">
         <v>42</v>
@@ -16871,7 +16871,7 @@
         <v>41</v>
       </c>
       <c r="J234" s="13">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="K234" s="14" t="s">
         <v>42</v>
@@ -16909,7 +16909,7 @@
         <v>41</v>
       </c>
       <c r="J235" s="16">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="K235" s="17" t="s">
         <v>42</v>
@@ -16947,7 +16947,7 @@
         <v>41</v>
       </c>
       <c r="J236" s="13">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="K236" s="14" t="s">
         <v>42</v>
@@ -16985,7 +16985,7 @@
         <v>78</v>
       </c>
       <c r="J237" s="16">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="K237" s="17" t="s">
         <v>42</v>
@@ -17023,7 +17023,7 @@
         <v>78</v>
       </c>
       <c r="J238" s="13">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K238" s="14" t="s">
         <v>42</v>
@@ -17061,7 +17061,7 @@
         <v>78</v>
       </c>
       <c r="J239" s="16">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="K239" s="17" t="s">
         <v>42</v>
@@ -17099,7 +17099,7 @@
         <v>78</v>
       </c>
       <c r="J240" s="13">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="K240" s="14" t="s">
         <v>42</v>
@@ -17137,7 +17137,7 @@
         <v>78</v>
       </c>
       <c r="J241" s="16">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="K241" s="17" t="s">
         <v>42</v>
@@ -17175,7 +17175,7 @@
         <v>78</v>
       </c>
       <c r="J242" s="13">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="K242" s="14" t="s">
         <v>42</v>
@@ -17213,7 +17213,7 @@
         <v>78</v>
       </c>
       <c r="J243" s="16">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="K243" s="17" t="s">
         <v>42</v>
@@ -17251,7 +17251,7 @@
         <v>128</v>
       </c>
       <c r="J244" s="13">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K244" s="14" t="s">
         <v>42</v>
@@ -17289,7 +17289,7 @@
         <v>128</v>
       </c>
       <c r="J245" s="16">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="K245" s="17" t="s">
         <v>42</v>
@@ -17327,7 +17327,7 @@
         <v>128</v>
       </c>
       <c r="J246" s="13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K246" s="14" t="s">
         <v>42</v>
@@ -17365,7 +17365,7 @@
         <v>128</v>
       </c>
       <c r="J247" s="16">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="K247" s="17" t="s">
         <v>42</v>
@@ -17403,7 +17403,7 @@
         <v>128</v>
       </c>
       <c r="J248" s="13">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K248" s="14" t="s">
         <v>42</v>
@@ -17441,7 +17441,7 @@
         <v>128</v>
       </c>
       <c r="J249" s="16">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="K249" s="17" t="s">
         <v>42</v>
@@ -17479,7 +17479,7 @@
         <v>171</v>
       </c>
       <c r="J250" s="13">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="K250" s="14" t="s">
         <v>42</v>
@@ -17517,7 +17517,7 @@
         <v>171</v>
       </c>
       <c r="J251" s="16">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="K251" s="17" t="s">
         <v>42</v>
@@ -17555,7 +17555,7 @@
         <v>41</v>
       </c>
       <c r="J252" s="13">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K252" s="14" t="s">
         <v>42</v>
@@ -17593,7 +17593,7 @@
         <v>41</v>
       </c>
       <c r="J253" s="16">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="K253" s="17" t="s">
         <v>42</v>
@@ -17631,7 +17631,7 @@
         <v>41</v>
       </c>
       <c r="J254" s="13">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="K254" s="14" t="s">
         <v>42</v>
@@ -17669,7 +17669,7 @@
         <v>41</v>
       </c>
       <c r="J255" s="16">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K255" s="17" t="s">
         <v>42</v>
@@ -17707,7 +17707,7 @@
         <v>41</v>
       </c>
       <c r="J256" s="13">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="K256" s="14" t="s">
         <v>42</v>
@@ -17745,7 +17745,7 @@
         <v>78</v>
       </c>
       <c r="J257" s="16">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="K257" s="17" t="s">
         <v>42</v>
@@ -17783,7 +17783,7 @@
         <v>78</v>
       </c>
       <c r="J258" s="13">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="K258" s="14" t="s">
         <v>42</v>
@@ -17821,7 +17821,7 @@
         <v>78</v>
       </c>
       <c r="J259" s="16">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K259" s="17" t="s">
         <v>42</v>
@@ -17859,7 +17859,7 @@
         <v>78</v>
       </c>
       <c r="J260" s="13">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K260" s="14" t="s">
         <v>42</v>
@@ -17897,7 +17897,7 @@
         <v>78</v>
       </c>
       <c r="J261" s="16">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="K261" s="17" t="s">
         <v>42</v>
@@ -17935,7 +17935,7 @@
         <v>78</v>
       </c>
       <c r="J262" s="13">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="K262" s="14" t="s">
         <v>42</v>
@@ -17973,7 +17973,7 @@
         <v>78</v>
       </c>
       <c r="J263" s="16">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="K263" s="17" t="s">
         <v>42</v>
@@ -18011,7 +18011,7 @@
         <v>128</v>
       </c>
       <c r="J264" s="13">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K264" s="14" t="s">
         <v>42</v>
@@ -18049,7 +18049,7 @@
         <v>128</v>
       </c>
       <c r="J265" s="16">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="K265" s="17" t="s">
         <v>42</v>
@@ -18087,7 +18087,7 @@
         <v>128</v>
       </c>
       <c r="J266" s="13">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="K266" s="14" t="s">
         <v>42</v>
@@ -18125,7 +18125,7 @@
         <v>78</v>
       </c>
       <c r="J267" s="16">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="K267" s="17" t="s">
         <v>42</v>
@@ -18163,7 +18163,7 @@
         <v>78</v>
       </c>
       <c r="J268" s="13">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K268" s="14" t="s">
         <v>42</v>
@@ -18201,7 +18201,7 @@
         <v>78</v>
       </c>
       <c r="J269" s="16">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="K269" s="17" t="s">
         <v>42</v>
@@ -18239,7 +18239,7 @@
         <v>78</v>
       </c>
       <c r="J270" s="13">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K270" s="14" t="s">
         <v>42</v>
@@ -18277,7 +18277,7 @@
         <v>78</v>
       </c>
       <c r="J271" s="16">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K271" s="17" t="s">
         <v>42</v>
@@ -18315,7 +18315,7 @@
         <v>78</v>
       </c>
       <c r="J272" s="13">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="K272" s="14" t="s">
         <v>42</v>
@@ -18353,7 +18353,7 @@
         <v>128</v>
       </c>
       <c r="J273" s="16">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="K273" s="17" t="s">
         <v>42</v>
@@ -18391,7 +18391,7 @@
         <v>128</v>
       </c>
       <c r="J274" s="13">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="K274" s="14" t="s">
         <v>42</v>
@@ -18429,7 +18429,7 @@
         <v>128</v>
       </c>
       <c r="J275" s="16">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="K275" s="17" t="s">
         <v>42</v>
@@ -18467,7 +18467,7 @@
         <v>128</v>
       </c>
       <c r="J276" s="13">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="K276" s="14" t="s">
         <v>42</v>
@@ -18505,7 +18505,7 @@
         <v>128</v>
       </c>
       <c r="J277" s="16">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="K277" s="17" t="s">
         <v>42</v>
@@ -18543,7 +18543,7 @@
         <v>128</v>
       </c>
       <c r="J278" s="13">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="K278" s="14" t="s">
         <v>42</v>
@@ -18581,7 +18581,7 @@
         <v>128</v>
       </c>
       <c r="J279" s="16">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="K279" s="17" t="s">
         <v>42</v>
@@ -18619,7 +18619,7 @@
         <v>128</v>
       </c>
       <c r="J280" s="13">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="K280" s="14" t="s">
         <v>42</v>
@@ -18657,7 +18657,7 @@
         <v>128</v>
       </c>
       <c r="J281" s="16">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="K281" s="17" t="s">
         <v>42</v>
@@ -18695,7 +18695,7 @@
         <v>128</v>
       </c>
       <c r="J282" s="13">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K282" s="14" t="s">
         <v>42</v>
@@ -18733,7 +18733,7 @@
         <v>128</v>
       </c>
       <c r="J283" s="16">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="K283" s="17" t="s">
         <v>42</v>
@@ -18771,7 +18771,7 @@
         <v>128</v>
       </c>
       <c r="J284" s="13">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K284" s="14" t="s">
         <v>42</v>
@@ -18809,7 +18809,7 @@
         <v>128</v>
       </c>
       <c r="J285" s="16">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K285" s="17" t="s">
         <v>42</v>
@@ -18847,7 +18847,7 @@
         <v>128</v>
       </c>
       <c r="J286" s="13">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="K286" s="14" t="s">
         <v>42</v>
@@ -18885,7 +18885,7 @@
         <v>78</v>
       </c>
       <c r="J287" s="16">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="K287" s="17" t="s">
         <v>42</v>
@@ -18923,7 +18923,7 @@
         <v>78</v>
       </c>
       <c r="J288" s="13">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K288" s="14" t="s">
         <v>42</v>
@@ -18961,7 +18961,7 @@
         <v>78</v>
       </c>
       <c r="J289" s="16">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K289" s="17" t="s">
         <v>42</v>
@@ -18999,7 +18999,7 @@
         <v>78</v>
       </c>
       <c r="J290" s="13">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K290" s="14" t="s">
         <v>42</v>
@@ -19037,7 +19037,7 @@
         <v>78</v>
       </c>
       <c r="J291" s="16">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K291" s="17" t="s">
         <v>42</v>
@@ -19075,7 +19075,7 @@
         <v>78</v>
       </c>
       <c r="J292" s="13">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="K292" s="14" t="s">
         <v>42</v>
@@ -19113,7 +19113,7 @@
         <v>128</v>
       </c>
       <c r="J293" s="16">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="K293" s="17" t="s">
         <v>42</v>
@@ -19151,7 +19151,7 @@
         <v>128</v>
       </c>
       <c r="J294" s="13">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="K294" s="14" t="s">
         <v>42</v>
@@ -19189,7 +19189,7 @@
         <v>128</v>
       </c>
       <c r="J295" s="16">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K295" s="17" t="s">
         <v>42</v>
@@ -19265,7 +19265,7 @@
         <v>128</v>
       </c>
       <c r="J297" s="16">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K297" s="17" t="s">
         <v>42</v>
@@ -19303,7 +19303,7 @@
         <v>128</v>
       </c>
       <c r="J298" s="13">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K298" s="14" t="s">
         <v>42</v>
@@ -19341,7 +19341,7 @@
         <v>128</v>
       </c>
       <c r="J299" s="16">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K299" s="17" t="s">
         <v>42</v>
@@ -19379,7 +19379,7 @@
         <v>128</v>
       </c>
       <c r="J300" s="13">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K300" s="14" t="s">
         <v>42</v>
@@ -19417,7 +19417,7 @@
         <v>128</v>
       </c>
       <c r="J301" s="16">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="K301" s="17" t="s">
         <v>42</v>
@@ -19455,7 +19455,7 @@
         <v>128</v>
       </c>
       <c r="J302" s="13">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K302" s="14" t="s">
         <v>42</v>
@@ -19493,7 +19493,7 @@
         <v>128</v>
       </c>
       <c r="J303" s="16">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="K303" s="17" t="s">
         <v>42</v>
@@ -19531,7 +19531,7 @@
         <v>128</v>
       </c>
       <c r="J304" s="13">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K304" s="14" t="s">
         <v>42</v>
@@ -19569,7 +19569,7 @@
         <v>128</v>
       </c>
       <c r="J305" s="16">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K305" s="17" t="s">
         <v>42</v>
@@ -19607,7 +19607,7 @@
         <v>128</v>
       </c>
       <c r="J306" s="13">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="K306" s="14" t="s">
         <v>42</v>
@@ -19645,7 +19645,7 @@
         <v>78</v>
       </c>
       <c r="J307" s="16">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="K307" s="17" t="s">
         <v>42</v>
@@ -19683,7 +19683,7 @@
         <v>78</v>
       </c>
       <c r="J308" s="13">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="K308" s="14" t="s">
         <v>42</v>
@@ -19721,7 +19721,7 @@
         <v>78</v>
       </c>
       <c r="J309" s="16">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="K309" s="17" t="s">
         <v>42</v>
@@ -19759,7 +19759,7 @@
         <v>78</v>
       </c>
       <c r="J310" s="13">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K310" s="14" t="s">
         <v>42</v>
@@ -19797,7 +19797,7 @@
         <v>78</v>
       </c>
       <c r="J311" s="16">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="K311" s="17" t="s">
         <v>42</v>
@@ -19835,7 +19835,7 @@
         <v>78</v>
       </c>
       <c r="J312" s="13">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="K312" s="14" t="s">
         <v>42</v>
@@ -19873,7 +19873,7 @@
         <v>128</v>
       </c>
       <c r="J313" s="16">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="K313" s="17" t="s">
         <v>42</v>
@@ -19911,7 +19911,7 @@
         <v>128</v>
       </c>
       <c r="J314" s="13">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="K314" s="14" t="s">
         <v>42</v>
@@ -19949,7 +19949,7 @@
         <v>128</v>
       </c>
       <c r="J315" s="16">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="K315" s="17" t="s">
         <v>42</v>
@@ -19987,7 +19987,7 @@
         <v>128</v>
       </c>
       <c r="J316" s="13">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K316" s="14" t="s">
         <v>42</v>
@@ -20063,7 +20063,7 @@
         <v>128</v>
       </c>
       <c r="J318" s="13">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K318" s="14" t="s">
         <v>42</v>
@@ -20101,7 +20101,7 @@
         <v>128</v>
       </c>
       <c r="J319" s="16">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K319" s="17" t="s">
         <v>42</v>
@@ -20139,7 +20139,7 @@
         <v>128</v>
       </c>
       <c r="J320" s="13">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K320" s="14" t="s">
         <v>42</v>
@@ -20177,7 +20177,7 @@
         <v>128</v>
       </c>
       <c r="J321" s="16">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K321" s="17" t="s">
         <v>42</v>
@@ -20215,7 +20215,7 @@
         <v>128</v>
       </c>
       <c r="J322" s="13">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="K322" s="14" t="s">
         <v>42</v>
@@ -20253,7 +20253,7 @@
         <v>128</v>
       </c>
       <c r="J323" s="16">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="K323" s="17" t="s">
         <v>42</v>
@@ -20329,7 +20329,7 @@
         <v>128</v>
       </c>
       <c r="J325" s="16">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K325" s="17" t="s">
         <v>42</v>
@@ -20367,7 +20367,7 @@
         <v>128</v>
       </c>
       <c r="J326" s="13">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K326" s="14" t="s">
         <v>42</v>
@@ -20405,7 +20405,7 @@
         <v>78</v>
       </c>
       <c r="J327" s="16">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="K327" s="17" t="s">
         <v>42</v>
@@ -20443,7 +20443,7 @@
         <v>78</v>
       </c>
       <c r="J328" s="13">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K328" s="14" t="s">
         <v>42</v>
@@ -20481,7 +20481,7 @@
         <v>78</v>
       </c>
       <c r="J329" s="16">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="K329" s="17" t="s">
         <v>42</v>
@@ -20519,7 +20519,7 @@
         <v>78</v>
       </c>
       <c r="J330" s="13">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K330" s="14" t="s">
         <v>42</v>
@@ -20557,7 +20557,7 @@
         <v>78</v>
       </c>
       <c r="J331" s="16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K331" s="17" t="s">
         <v>42</v>
@@ -20595,7 +20595,7 @@
         <v>78</v>
       </c>
       <c r="J332" s="13">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K332" s="14" t="s">
         <v>42</v>
@@ -20633,7 +20633,7 @@
         <v>128</v>
       </c>
       <c r="J333" s="16">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K333" s="17" t="s">
         <v>42</v>
@@ -20671,7 +20671,7 @@
         <v>128</v>
       </c>
       <c r="J334" s="13">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K334" s="14" t="s">
         <v>42</v>
@@ -20709,7 +20709,7 @@
         <v>128</v>
       </c>
       <c r="J335" s="16">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K335" s="17" t="s">
         <v>42</v>
@@ -20747,7 +20747,7 @@
         <v>128</v>
       </c>
       <c r="J336" s="13">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K336" s="14" t="s">
         <v>42</v>
@@ -20785,7 +20785,7 @@
         <v>128</v>
       </c>
       <c r="J337" s="16">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K337" s="17" t="s">
         <v>42</v>
@@ -20823,7 +20823,7 @@
         <v>128</v>
       </c>
       <c r="J338" s="13">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="K338" s="14" t="s">
         <v>42</v>
@@ -20861,7 +20861,7 @@
         <v>128</v>
       </c>
       <c r="J339" s="16">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="K339" s="17" t="s">
         <v>42</v>
@@ -20899,7 +20899,7 @@
         <v>128</v>
       </c>
       <c r="J340" s="13">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="K340" s="14" t="s">
         <v>42</v>
@@ -20937,7 +20937,7 @@
         <v>128</v>
       </c>
       <c r="J341" s="16">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K341" s="17" t="s">
         <v>42</v>
@@ -20975,7 +20975,7 @@
         <v>128</v>
       </c>
       <c r="J342" s="13">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="K342" s="14" t="s">
         <v>42</v>
@@ -21013,7 +21013,7 @@
         <v>128</v>
       </c>
       <c r="J343" s="16">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K343" s="17" t="s">
         <v>42</v>
@@ -21051,7 +21051,7 @@
         <v>128</v>
       </c>
       <c r="J344" s="13">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K344" s="14" t="s">
         <v>42</v>
@@ -21089,7 +21089,7 @@
         <v>128</v>
       </c>
       <c r="J345" s="16">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="K345" s="17" t="s">
         <v>42</v>
@@ -21127,7 +21127,7 @@
         <v>128</v>
       </c>
       <c r="J346" s="13">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K346" s="14" t="s">
         <v>42</v>
@@ -21165,7 +21165,7 @@
         <v>78</v>
       </c>
       <c r="J347" s="16">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="K347" s="17" t="s">
         <v>42</v>
@@ -21203,7 +21203,7 @@
         <v>78</v>
       </c>
       <c r="J348" s="13">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="K348" s="14" t="s">
         <v>42</v>
@@ -21241,7 +21241,7 @@
         <v>78</v>
       </c>
       <c r="J349" s="16">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="K349" s="17" t="s">
         <v>42</v>
@@ -21279,7 +21279,7 @@
         <v>78</v>
       </c>
       <c r="J350" s="13">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K350" s="14" t="s">
         <v>42</v>
@@ -21317,7 +21317,7 @@
         <v>78</v>
       </c>
       <c r="J351" s="16">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K351" s="17" t="s">
         <v>42</v>
@@ -21355,7 +21355,7 @@
         <v>78</v>
       </c>
       <c r="J352" s="13">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K352" s="14" t="s">
         <v>42</v>
@@ -21393,7 +21393,7 @@
         <v>128</v>
       </c>
       <c r="J353" s="16">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K353" s="17" t="s">
         <v>42</v>
@@ -21431,7 +21431,7 @@
         <v>128</v>
       </c>
       <c r="J354" s="13">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="K354" s="14" t="s">
         <v>42</v>
@@ -21507,7 +21507,7 @@
         <v>128</v>
       </c>
       <c r="J356" s="13">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="K356" s="14" t="s">
         <v>42</v>
@@ -21545,7 +21545,7 @@
         <v>128</v>
       </c>
       <c r="J357" s="16">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K357" s="17" t="s">
         <v>42</v>
@@ -21583,7 +21583,7 @@
         <v>128</v>
       </c>
       <c r="J358" s="13">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="K358" s="14" t="s">
         <v>42</v>
@@ -21621,7 +21621,7 @@
         <v>128</v>
       </c>
       <c r="J359" s="16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K359" s="17" t="s">
         <v>42</v>
@@ -21659,7 +21659,7 @@
         <v>128</v>
       </c>
       <c r="J360" s="13">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K360" s="14" t="s">
         <v>42</v>
@@ -21697,7 +21697,7 @@
         <v>128</v>
       </c>
       <c r="J361" s="16">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="K361" s="17" t="s">
         <v>42</v>
@@ -21735,7 +21735,7 @@
         <v>128</v>
       </c>
       <c r="J362" s="13">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K362" s="14" t="s">
         <v>42</v>
@@ -21773,7 +21773,7 @@
         <v>128</v>
       </c>
       <c r="J363" s="16">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="K363" s="17" t="s">
         <v>42</v>
@@ -21811,7 +21811,7 @@
         <v>128</v>
       </c>
       <c r="J364" s="13">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="K364" s="14" t="s">
         <v>42</v>
@@ -21849,7 +21849,7 @@
         <v>128</v>
       </c>
       <c r="J365" s="16">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K365" s="17" t="s">
         <v>42</v>
@@ -21887,7 +21887,7 @@
         <v>128</v>
       </c>
       <c r="J366" s="13">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K366" s="14" t="s">
         <v>42</v>
